--- a/Financial Analysis/NKE.xlsx
+++ b/Financial Analysis/NKE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810BC291-7CEE-4B78-A430-C6C47DC27397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA916C6-11FF-4EC0-93A3-6F5C463100E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{979F10BC-B7A7-4127-A37D-ADC4ED82FE8E}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="75">
   <si>
     <t>NKE</t>
   </si>
@@ -238,7 +238,19 @@
     <t>Q425</t>
   </si>
   <si>
-    <t>Slightly overvalued</t>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>Overvalued</t>
   </si>
 </sst>
 </file>
@@ -339,16 +351,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
+      <xdr:rowOff>99060</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -363,7 +375,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="24307800" y="0"/>
+          <a:off x="25024080" y="7620"/>
           <a:ext cx="0" cy="6126480"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -389,13 +401,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>43</xdr:col>
+      <xdr:col>47</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>43</xdr:col>
+      <xdr:col>47</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
@@ -762,17 +774,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="6">
-        <v>58.29</v>
+        <v>74.23</v>
       </c>
       <c r="E3" s="4">
-        <v>45772</v>
+        <v>45909</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45773</v>
+        <v>45909</v>
       </c>
       <c r="G3" s="4">
-        <v>45834</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -780,11 +792,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <f>1476</f>
-        <v>1476</v>
+        <f>1476.9</f>
+        <v>1476.9</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -793,7 +805,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>86036.04</v>
+        <v>109630.28700000001</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -835,7 +847,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>84603.04</v>
+        <v>108197.28700000001</v>
       </c>
     </row>
   </sheetData>
@@ -846,18 +858,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CBA6230-E0E0-4BDE-A713-8F9F20EAD05E}">
-  <dimension ref="B1:FI27"/>
+  <dimension ref="B1:FM27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="34" width="10.5546875" customWidth="1"/>
-    <col min="36" max="54" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="8.88671875" customWidth="1"/>
-    <col min="56" max="56" width="12" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="16.5546875" customWidth="1"/>
+    <col min="3" max="38" width="10.5546875" customWidth="1"/>
+    <col min="40" max="58" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="8.88671875" customWidth="1"/>
+    <col min="60" max="60" width="12" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="16.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:165" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:169" x14ac:dyDescent="0.3">
       <c r="C1" s="2">
         <v>42978</v>
       </c>
@@ -954,65 +966,77 @@
       <c r="AH1" s="2">
         <v>45808</v>
       </c>
+      <c r="AI1" s="2">
+        <v>45900</v>
+      </c>
       <c r="AJ1" s="2">
+        <v>45991</v>
+      </c>
+      <c r="AK1" s="2">
+        <v>46081</v>
+      </c>
+      <c r="AL1" s="2">
+        <v>46173</v>
+      </c>
+      <c r="AN1" s="2">
         <v>42886</v>
       </c>
-      <c r="AK1" s="2">
+      <c r="AO1" s="2">
         <v>43251</v>
       </c>
-      <c r="AL1" s="2">
+      <c r="AP1" s="2">
         <v>43616</v>
       </c>
-      <c r="AM1" s="2">
+      <c r="AQ1" s="2">
         <v>43982</v>
       </c>
-      <c r="AN1" s="2">
+      <c r="AR1" s="2">
         <v>44347</v>
       </c>
-      <c r="AO1" s="2">
+      <c r="AS1" s="2">
         <v>44712</v>
       </c>
-      <c r="AP1" s="2">
+      <c r="AT1" s="2">
         <v>45077</v>
       </c>
-      <c r="AQ1" s="2">
+      <c r="AU1" s="2">
         <v>45443</v>
       </c>
-      <c r="AR1" s="2">
+      <c r="AV1" s="2">
         <v>45808</v>
       </c>
-      <c r="AS1" s="2">
+      <c r="AW1" s="2">
         <v>46173</v>
       </c>
-      <c r="AT1" s="2">
+      <c r="AX1" s="2">
         <v>46538</v>
       </c>
-      <c r="AU1" s="2">
+      <c r="AY1" s="2">
         <v>46904</v>
       </c>
-      <c r="AV1" s="2">
+      <c r="AZ1" s="2">
         <v>47269</v>
       </c>
-      <c r="AW1" s="2">
+      <c r="BA1" s="2">
         <v>47634</v>
       </c>
-      <c r="AX1" s="2">
+      <c r="BB1" s="2">
         <v>47999</v>
       </c>
-      <c r="AY1" s="2">
+      <c r="BC1" s="2">
         <v>48365</v>
       </c>
-      <c r="AZ1" s="2">
+      <c r="BD1" s="2">
         <v>48730</v>
       </c>
-      <c r="BA1" s="2">
+      <c r="BE1" s="2">
         <v>49095</v>
       </c>
-      <c r="BB1" s="2">
+      <c r="BF1" s="2">
         <v>49460</v>
       </c>
     </row>
-    <row r="2" spans="2:165" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:169" x14ac:dyDescent="0.3">
       <c r="C2" s="7" t="s">
         <v>35</v>
       </c>
@@ -1109,65 +1133,77 @@
       <c r="AH2" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="AJ2">
+      <c r="AI2" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ2" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK2" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AL2" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AN2">
         <v>2017</v>
       </c>
-      <c r="AK2">
+      <c r="AO2">
         <v>2018</v>
       </c>
-      <c r="AL2">
+      <c r="AP2">
         <v>2019</v>
       </c>
-      <c r="AM2">
+      <c r="AQ2">
         <v>2020</v>
       </c>
-      <c r="AN2">
+      <c r="AR2">
         <v>2021</v>
       </c>
-      <c r="AO2">
+      <c r="AS2">
         <v>2022</v>
       </c>
-      <c r="AP2">
+      <c r="AT2">
         <v>2023</v>
       </c>
-      <c r="AQ2">
+      <c r="AU2">
         <v>2024</v>
       </c>
-      <c r="AR2">
+      <c r="AV2">
         <v>2025</v>
       </c>
-      <c r="AS2">
+      <c r="AW2">
         <v>2026</v>
       </c>
-      <c r="AT2">
+      <c r="AX2">
         <v>2027</v>
       </c>
-      <c r="AU2">
+      <c r="AY2">
         <v>2028</v>
       </c>
-      <c r="AV2">
+      <c r="AZ2">
         <v>2029</v>
       </c>
-      <c r="AW2">
+      <c r="BA2">
         <v>2030</v>
       </c>
-      <c r="AX2">
+      <c r="BB2">
         <v>2031</v>
       </c>
-      <c r="AY2">
+      <c r="BC2">
         <v>2032</v>
       </c>
-      <c r="AZ2">
+      <c r="BD2">
         <v>2033</v>
       </c>
-      <c r="BA2">
+      <c r="BE2">
         <v>2034</v>
       </c>
-      <c r="BB2">
+      <c r="BF2">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="2:165" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:169" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
@@ -1265,86 +1301,87 @@
         <v>11269</v>
       </c>
       <c r="AH3" s="9">
-        <f>AD3*0.93</f>
-        <v>11723.58</v>
-      </c>
-      <c r="AJ3" s="9">
+        <f>AV3-AG3-AF3-AE3</f>
+        <v>11097</v>
+      </c>
+      <c r="AI3" s="9"/>
+      <c r="AJ3" s="9"/>
+      <c r="AK3" s="9"/>
+      <c r="AL3" s="9"/>
+      <c r="AN3" s="9">
         <v>34350</v>
       </c>
-      <c r="AK3" s="9">
+      <c r="AO3" s="9">
         <f>SUM(C3:F3)</f>
         <v>36397</v>
       </c>
-      <c r="AL3" s="9">
+      <c r="AP3" s="9">
         <f>SUM(G3:J3)</f>
         <v>39117</v>
       </c>
-      <c r="AM3" s="9">
+      <c r="AQ3" s="9">
         <f>SUM(K3:N3)</f>
         <v>37403</v>
       </c>
-      <c r="AN3" s="9">
+      <c r="AR3" s="9">
         <f>SUM(O3:R3)</f>
         <v>44538</v>
       </c>
-      <c r="AO3" s="9">
+      <c r="AS3" s="9">
         <f>SUM(S3:V3)</f>
         <v>46710</v>
       </c>
-      <c r="AP3" s="9">
+      <c r="AT3" s="9">
         <f>SUM(W3:Z3)</f>
         <v>51217</v>
       </c>
-      <c r="AQ3" s="9">
+      <c r="AU3" s="9">
         <f>SUM(AA3:AD3)</f>
         <v>51362</v>
       </c>
-      <c r="AR3" s="9">
-        <f>SUM(AE3:AH3)</f>
-        <v>46935.58</v>
-      </c>
-      <c r="AS3" s="9">
-        <f>AR3*1.02</f>
-        <v>47874.291600000004</v>
-      </c>
-      <c r="AT3" s="9">
-        <f>AS3*1.01</f>
-        <v>48353.034516000007</v>
-      </c>
-      <c r="AU3" s="9">
-        <f t="shared" ref="AU3:BB3" si="0">AT3*1.01</f>
-        <v>48836.564861160005</v>
-      </c>
       <c r="AV3" s="9">
-        <f t="shared" si="0"/>
-        <v>49324.930509771606</v>
+        <v>46309</v>
       </c>
       <c r="AW3" s="9">
-        <f t="shared" si="0"/>
-        <v>49818.17981486932</v>
+        <v>45820</v>
       </c>
       <c r="AX3" s="9">
-        <f t="shared" si="0"/>
-        <v>50316.361613018016</v>
+        <v>48080</v>
       </c>
       <c r="AY3" s="9">
-        <f t="shared" si="0"/>
-        <v>50819.525229148196</v>
+        <f>AX3*1.03</f>
+        <v>49522.400000000001</v>
       </c>
       <c r="AZ3" s="9">
-        <f t="shared" si="0"/>
-        <v>51327.720481439675</v>
+        <f t="shared" ref="AZ3:BF3" si="0">AY3*1.01</f>
+        <v>50017.624000000003</v>
       </c>
       <c r="BA3" s="9">
         <f t="shared" si="0"/>
-        <v>51840.997686254072</v>
+        <v>50517.800240000004</v>
       </c>
       <c r="BB3" s="9">
         <f t="shared" si="0"/>
-        <v>52359.40766311661</v>
+        <v>51022.978242400008</v>
+      </c>
+      <c r="BC3" s="9">
+        <f t="shared" si="0"/>
+        <v>51533.208024824009</v>
+      </c>
+      <c r="BD3" s="9">
+        <f t="shared" si="0"/>
+        <v>52048.54010507225</v>
+      </c>
+      <c r="BE3" s="9">
+        <f t="shared" si="0"/>
+        <v>52569.025506122976</v>
+      </c>
+      <c r="BF3" s="9">
+        <f t="shared" si="0"/>
+        <v>53094.715761184205</v>
       </c>
     </row>
-    <row r="4" spans="2:165" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:169" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>24</v>
       </c>
@@ -1442,295 +1479,302 @@
         <v>6594</v>
       </c>
       <c r="AH4" s="5">
-        <f t="shared" ref="AH4" si="1">AH3-AH5</f>
-        <v>6330.7331999999997</v>
-      </c>
-      <c r="AJ4" s="5">
+        <f>AV4-AG4-AF4-AE4</f>
+        <v>6628</v>
+      </c>
+      <c r="AI4" s="5"/>
+      <c r="AJ4" s="5"/>
+      <c r="AK4" s="5"/>
+      <c r="AL4" s="5"/>
+      <c r="AN4" s="5">
         <v>19038</v>
       </c>
-      <c r="AK4" s="5">
+      <c r="AO4" s="5">
         <f>SUM(C4:F4)</f>
         <v>20441</v>
       </c>
-      <c r="AL4" s="5">
+      <c r="AP4" s="5">
         <f>SUM(G4:J4)</f>
         <v>21643</v>
       </c>
-      <c r="AM4" s="5">
+      <c r="AQ4" s="5">
         <f>SUM(K4:N4)</f>
         <v>21162</v>
       </c>
-      <c r="AN4" s="5">
+      <c r="AR4" s="5">
         <f>SUM(O4:R4)</f>
         <v>24576</v>
       </c>
-      <c r="AO4" s="5">
+      <c r="AS4" s="5">
         <f>SUM(S4:V4)</f>
         <v>25231</v>
       </c>
-      <c r="AP4" s="5">
+      <c r="AT4" s="5">
         <f>SUM(W4:Z4)</f>
         <v>28925</v>
       </c>
-      <c r="AQ4" s="5">
+      <c r="AU4" s="5">
         <f>SUM(AA4:AD4)</f>
         <v>28475</v>
       </c>
-      <c r="AR4" s="5">
-        <f>SUM(AE4:AH4)</f>
-        <v>26221.733199999999</v>
-      </c>
-      <c r="AS4" s="5">
-        <f t="shared" ref="AS4:AX4" si="2">AS3-AS5</f>
-        <v>25852.117464000003</v>
-      </c>
-      <c r="AT4" s="5">
+      <c r="AV4" s="5">
+        <v>26519</v>
+      </c>
+      <c r="AW4" s="5">
+        <f t="shared" ref="AW4:BB4" si="1">AW3-AW5</f>
+        <v>25201</v>
+      </c>
+      <c r="AX4" s="5">
+        <f t="shared" si="1"/>
+        <v>25963.200000000001</v>
+      </c>
+      <c r="AY4" s="5">
+        <f t="shared" si="1"/>
+        <v>26742.096000000001</v>
+      </c>
+      <c r="AZ4" s="5">
+        <f t="shared" si="1"/>
+        <v>27009.516960000001</v>
+      </c>
+      <c r="BA4" s="5">
+        <f t="shared" si="1"/>
+        <v>27279.612129600002</v>
+      </c>
+      <c r="BB4" s="5">
+        <f t="shared" si="1"/>
+        <v>27552.408250896002</v>
+      </c>
+      <c r="BC4" s="5">
+        <f t="shared" ref="BC4:BF4" si="2">BC3-BC5</f>
+        <v>27827.932333404962</v>
+      </c>
+      <c r="BD4" s="5">
         <f t="shared" si="2"/>
-        <v>26110.638638640005</v>
-      </c>
-      <c r="AU4" s="5">
+        <v>28106.211656739015</v>
+      </c>
+      <c r="BE4" s="5">
         <f t="shared" si="2"/>
-        <v>26371.745025026401</v>
-      </c>
-      <c r="AV4" s="5">
+        <v>28387.273773306406</v>
+      </c>
+      <c r="BF4" s="5">
         <f t="shared" si="2"/>
-        <v>26635.462475276665</v>
-      </c>
-      <c r="AW4" s="5">
-        <f t="shared" si="2"/>
-        <v>26901.817100029431</v>
-      </c>
-      <c r="AX4" s="5">
-        <f t="shared" si="2"/>
-        <v>27170.835271029729</v>
-      </c>
-      <c r="AY4" s="5">
-        <f t="shared" ref="AY4:BB4" si="3">AY3-AY5</f>
-        <v>27442.543623740024</v>
-      </c>
-      <c r="AZ4" s="5">
-        <f t="shared" si="3"/>
-        <v>27716.969059977422</v>
-      </c>
-      <c r="BA4" s="5">
-        <f t="shared" si="3"/>
-        <v>27994.138750577196</v>
-      </c>
-      <c r="BB4" s="5">
-        <f t="shared" si="3"/>
-        <v>28274.080138082969</v>
+        <v>28671.146511039471</v>
       </c>
     </row>
-    <row r="5" spans="2:165" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:169" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="9">
-        <f t="shared" ref="C5:S5" si="4">C3-C4</f>
+        <f t="shared" ref="C5:S5" si="3">C3-C4</f>
         <v>3962</v>
       </c>
       <c r="D5" s="9">
+        <f t="shared" si="3"/>
+        <v>3678</v>
+      </c>
+      <c r="E5" s="9">
+        <f t="shared" si="3"/>
+        <v>3938</v>
+      </c>
+      <c r="F5" s="9">
+        <f t="shared" si="3"/>
+        <v>4378</v>
+      </c>
+      <c r="G5" s="9">
+        <f t="shared" si="3"/>
+        <v>4397</v>
+      </c>
+      <c r="H5" s="9">
+        <f t="shared" si="3"/>
+        <v>4105</v>
+      </c>
+      <c r="I5" s="9">
+        <f t="shared" si="3"/>
+        <v>4339</v>
+      </c>
+      <c r="J5" s="9">
+        <f t="shared" si="3"/>
+        <v>4633</v>
+      </c>
+      <c r="K5" s="9">
+        <f t="shared" si="3"/>
+        <v>4871</v>
+      </c>
+      <c r="L5" s="9">
+        <f t="shared" si="3"/>
+        <v>4544</v>
+      </c>
+      <c r="M5" s="9">
+        <f t="shared" si="3"/>
+        <v>4473</v>
+      </c>
+      <c r="N5" s="9">
+        <f t="shared" si="3"/>
+        <v>2353</v>
+      </c>
+      <c r="O5" s="9">
+        <f t="shared" si="3"/>
+        <v>4741</v>
+      </c>
+      <c r="P5" s="9">
+        <f t="shared" si="3"/>
+        <v>4847</v>
+      </c>
+      <c r="Q5" s="9">
+        <f t="shared" si="3"/>
+        <v>4719</v>
+      </c>
+      <c r="R5" s="9">
+        <f t="shared" si="3"/>
+        <v>5655</v>
+      </c>
+      <c r="S5" s="9">
+        <f t="shared" si="3"/>
+        <v>5696</v>
+      </c>
+      <c r="T5" s="9">
+        <f t="shared" ref="T5:U5" si="4">T3-T4</f>
+        <v>5213</v>
+      </c>
+      <c r="U5" s="9">
         <f t="shared" si="4"/>
-        <v>3678</v>
-      </c>
-      <c r="E5" s="9">
-        <f t="shared" si="4"/>
-        <v>3938</v>
-      </c>
-      <c r="F5" s="9">
-        <f t="shared" si="4"/>
-        <v>4378</v>
-      </c>
-      <c r="G5" s="9">
-        <f t="shared" si="4"/>
-        <v>4397</v>
-      </c>
-      <c r="H5" s="9">
-        <f t="shared" si="4"/>
-        <v>4105</v>
-      </c>
-      <c r="I5" s="9">
-        <f t="shared" si="4"/>
-        <v>4339</v>
-      </c>
-      <c r="J5" s="9">
-        <f t="shared" si="4"/>
-        <v>4633</v>
-      </c>
-      <c r="K5" s="9">
-        <f t="shared" si="4"/>
-        <v>4871</v>
-      </c>
-      <c r="L5" s="9">
-        <f t="shared" si="4"/>
-        <v>4544</v>
-      </c>
-      <c r="M5" s="9">
-        <f t="shared" si="4"/>
-        <v>4473</v>
-      </c>
-      <c r="N5" s="9">
-        <f t="shared" si="4"/>
-        <v>2353</v>
-      </c>
-      <c r="O5" s="9">
-        <f t="shared" si="4"/>
-        <v>4741</v>
-      </c>
-      <c r="P5" s="9">
-        <f t="shared" si="4"/>
-        <v>4847</v>
-      </c>
-      <c r="Q5" s="9">
-        <f t="shared" si="4"/>
-        <v>4719</v>
-      </c>
-      <c r="R5" s="9">
-        <f t="shared" si="4"/>
-        <v>5655</v>
-      </c>
-      <c r="S5" s="9">
-        <f t="shared" si="4"/>
-        <v>5696</v>
-      </c>
-      <c r="T5" s="9">
-        <f t="shared" ref="T5:U5" si="5">T3-T4</f>
-        <v>5213</v>
-      </c>
-      <c r="U5" s="9">
+        <v>5067</v>
+      </c>
+      <c r="V5" s="9">
+        <f t="shared" ref="V5:W5" si="5">V3-V4</f>
+        <v>5503</v>
+      </c>
+      <c r="W5" s="9">
         <f t="shared" si="5"/>
-        <v>5067</v>
-      </c>
-      <c r="V5" s="9">
-        <f t="shared" ref="V5:W5" si="6">V3-V4</f>
-        <v>5503</v>
-      </c>
-      <c r="W5" s="9">
-        <f t="shared" si="6"/>
         <v>5615</v>
       </c>
       <c r="X5" s="9">
-        <f t="shared" ref="X5" si="7">X3-X4</f>
+        <f t="shared" ref="X5" si="6">X3-X4</f>
         <v>5711</v>
       </c>
       <c r="Y5" s="9">
-        <f t="shared" ref="Y5:AA5" si="8">Y3-Y4</f>
+        <f t="shared" ref="Y5:AA5" si="7">Y3-Y4</f>
         <v>5371</v>
       </c>
       <c r="Z5" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>5595</v>
       </c>
       <c r="AA5" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>5720</v>
       </c>
       <c r="AB5" s="9">
-        <f t="shared" ref="AB5" si="9">AB3-AB4</f>
+        <f t="shared" ref="AB5" si="8">AB3-AB4</f>
         <v>5971</v>
       </c>
       <c r="AC5" s="9">
-        <f t="shared" ref="AC5:AG5" si="10">AC3-AC4</f>
+        <f t="shared" ref="AC5:AG5" si="9">AC3-AC4</f>
         <v>5562</v>
       </c>
       <c r="AD5" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>5634</v>
       </c>
       <c r="AE5" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>5257</v>
       </c>
       <c r="AF5" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>5389</v>
       </c>
       <c r="AG5" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>4675</v>
       </c>
       <c r="AH5" s="9">
         <f>AH3*0.46</f>
-        <v>5392.8468000000003</v>
-      </c>
-      <c r="AJ5" s="9">
-        <f>AJ3-AJ4</f>
-        <v>15312</v>
-      </c>
-      <c r="AK5" s="9">
-        <f>AK3-AK4</f>
-        <v>15956</v>
-      </c>
-      <c r="AL5" s="9">
-        <f>AL3-AL4</f>
-        <v>17474</v>
-      </c>
-      <c r="AM5" s="9">
-        <f>AM3-AM4</f>
-        <v>16241</v>
-      </c>
+        <v>5104.62</v>
+      </c>
+      <c r="AI5" s="9"/>
+      <c r="AJ5" s="9"/>
+      <c r="AK5" s="9"/>
+      <c r="AL5" s="9"/>
       <c r="AN5" s="9">
         <f>AN3-AN4</f>
+        <v>15312</v>
+      </c>
+      <c r="AO5" s="9">
+        <f>AO3-AO4</f>
+        <v>15956</v>
+      </c>
+      <c r="AP5" s="9">
+        <f>AP3-AP4</f>
+        <v>17474</v>
+      </c>
+      <c r="AQ5" s="9">
+        <f>AQ3-AQ4</f>
+        <v>16241</v>
+      </c>
+      <c r="AR5" s="9">
+        <f>AR3-AR4</f>
         <v>19962</v>
       </c>
-      <c r="AO5" s="9">
-        <f t="shared" ref="AO5:AR5" si="11">AO3-AO4</f>
+      <c r="AS5" s="9">
+        <f t="shared" ref="AS5:AV5" si="10">AS3-AS4</f>
         <v>21479</v>
       </c>
-      <c r="AP5" s="9">
+      <c r="AT5" s="9">
+        <f t="shared" si="10"/>
+        <v>22292</v>
+      </c>
+      <c r="AU5" s="9">
+        <f t="shared" si="10"/>
+        <v>22887</v>
+      </c>
+      <c r="AV5" s="9">
+        <f t="shared" si="10"/>
+        <v>19790</v>
+      </c>
+      <c r="AW5" s="9">
+        <f>AW3*0.45</f>
+        <v>20619</v>
+      </c>
+      <c r="AX5" s="9">
+        <f t="shared" ref="AX5:BF5" si="11">AX3*0.46</f>
+        <v>22116.799999999999</v>
+      </c>
+      <c r="AY5" s="9">
         <f t="shared" si="11"/>
-        <v>22292</v>
-      </c>
-      <c r="AQ5" s="9">
+        <v>22780.304</v>
+      </c>
+      <c r="AZ5" s="9">
         <f t="shared" si="11"/>
-        <v>22887</v>
-      </c>
-      <c r="AR5" s="9">
+        <v>23008.107040000003</v>
+      </c>
+      <c r="BA5" s="9">
         <f t="shared" si="11"/>
-        <v>20713.846800000003</v>
-      </c>
-      <c r="AS5" s="9">
-        <f>AS3*0.46</f>
-        <v>22022.174136000001</v>
-      </c>
-      <c r="AT5" s="9">
-        <f t="shared" ref="AT5:BB5" si="12">AT3*0.46</f>
-        <v>22242.395877360002</v>
-      </c>
-      <c r="AU5" s="9">
-        <f t="shared" si="12"/>
-        <v>22464.819836133604</v>
-      </c>
-      <c r="AV5" s="9">
-        <f t="shared" si="12"/>
-        <v>22689.468034494941</v>
-      </c>
-      <c r="AW5" s="9">
-        <f t="shared" si="12"/>
-        <v>22916.362714839888</v>
-      </c>
-      <c r="AX5" s="9">
-        <f t="shared" si="12"/>
-        <v>23145.526341988287</v>
-      </c>
-      <c r="AY5" s="9">
-        <f t="shared" si="12"/>
-        <v>23376.981605408171</v>
-      </c>
-      <c r="AZ5" s="9">
-        <f t="shared" si="12"/>
-        <v>23610.751421462253</v>
-      </c>
-      <c r="BA5" s="9">
-        <f t="shared" si="12"/>
-        <v>23846.858935676875</v>
+        <v>23238.188110400002</v>
       </c>
       <c r="BB5" s="9">
-        <f t="shared" si="12"/>
-        <v>24085.327525033641</v>
+        <f t="shared" si="11"/>
+        <v>23470.569991504006</v>
+      </c>
+      <c r="BC5" s="9">
+        <f t="shared" si="11"/>
+        <v>23705.275691419047</v>
+      </c>
+      <c r="BD5" s="9">
+        <f t="shared" si="11"/>
+        <v>23942.328448333235</v>
+      </c>
+      <c r="BE5" s="9">
+        <f t="shared" si="11"/>
+        <v>24181.75173281657</v>
+      </c>
+      <c r="BF5" s="9">
+        <f t="shared" si="11"/>
+        <v>24423.569250144734</v>
       </c>
     </row>
-    <row r="6" spans="2:165" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:169" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>27</v>
       </c>
@@ -1828,86 +1872,89 @@
         <v>1088</v>
       </c>
       <c r="AH6" s="5">
-        <f>AH3*0.09</f>
-        <v>1055.1222</v>
-      </c>
-      <c r="AJ6" s="5">
+        <f t="shared" ref="AH6:AH7" si="12">AV6-AG6-AF6-AE6</f>
+        <v>1253</v>
+      </c>
+      <c r="AI6" s="5"/>
+      <c r="AJ6" s="5"/>
+      <c r="AK6" s="5"/>
+      <c r="AL6" s="5"/>
+      <c r="AN6" s="5">
         <v>3341</v>
       </c>
-      <c r="AK6" s="5">
+      <c r="AO6" s="5">
         <f>SUM(C6:F6)</f>
         <v>3577</v>
       </c>
-      <c r="AL6" s="5">
+      <c r="AP6" s="5">
         <f>SUM(G6:J6)</f>
         <v>3753</v>
       </c>
-      <c r="AM6" s="5">
+      <c r="AQ6" s="5">
         <f>SUM(K6:N6)</f>
         <v>3592</v>
       </c>
-      <c r="AN6" s="5">
+      <c r="AR6" s="5">
         <f>SUM(O6:R6)</f>
         <v>3114</v>
       </c>
-      <c r="AO6" s="5">
+      <c r="AS6" s="5">
         <f>SUM(S6:V6)</f>
         <v>3850</v>
       </c>
-      <c r="AP6" s="5">
+      <c r="AT6" s="5">
         <f>SUM(W6:Z6)</f>
         <v>4060</v>
       </c>
-      <c r="AQ6" s="5">
+      <c r="AU6" s="5">
         <f>SUM(AA6:AD6)</f>
         <v>4285</v>
       </c>
-      <c r="AR6" s="5">
-        <f>SUM(AE6:AH6)</f>
-        <v>4491.1221999999998</v>
-      </c>
-      <c r="AS6" s="5">
-        <f>AS3*0.09</f>
-        <v>4308.6862440000004</v>
-      </c>
-      <c r="AT6" s="5">
-        <f t="shared" ref="AT6:BB6" si="13">AT3*0.09</f>
-        <v>4351.7731064400004</v>
-      </c>
-      <c r="AU6" s="5">
-        <f t="shared" si="13"/>
-        <v>4395.2908375043999</v>
-      </c>
       <c r="AV6" s="5">
-        <f t="shared" si="13"/>
-        <v>4439.2437458794448</v>
+        <v>4689</v>
       </c>
       <c r="AW6" s="5">
-        <f t="shared" si="13"/>
-        <v>4483.6361833382389</v>
+        <f>AW3*0.09</f>
+        <v>4123.8</v>
       </c>
       <c r="AX6" s="5">
-        <f t="shared" si="13"/>
-        <v>4528.4725451716213</v>
+        <f t="shared" ref="AX6:BF6" si="13">AX3*0.09</f>
+        <v>4327.2</v>
       </c>
       <c r="AY6" s="5">
         <f t="shared" si="13"/>
-        <v>4573.7572706233377</v>
+        <v>4457.0159999999996</v>
       </c>
       <c r="AZ6" s="5">
         <f t="shared" si="13"/>
-        <v>4619.4948433295704</v>
+        <v>4501.5861599999998</v>
       </c>
       <c r="BA6" s="5">
         <f t="shared" si="13"/>
-        <v>4665.6897917628667</v>
+        <v>4546.6020216000006</v>
       </c>
       <c r="BB6" s="5">
         <f t="shared" si="13"/>
-        <v>4712.3466896804948</v>
+        <v>4592.0680418160009</v>
+      </c>
+      <c r="BC6" s="5">
+        <f t="shared" si="13"/>
+        <v>4637.9887222341604</v>
+      </c>
+      <c r="BD6" s="5">
+        <f t="shared" si="13"/>
+        <v>4684.3686094565028</v>
+      </c>
+      <c r="BE6" s="5">
+        <f t="shared" si="13"/>
+        <v>4731.2122955510677</v>
+      </c>
+      <c r="BF6" s="5">
+        <f t="shared" si="13"/>
+        <v>4778.5244185065785</v>
       </c>
     </row>
-    <row r="7" spans="2:165" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:169" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>26</v>
       </c>
@@ -2005,86 +2052,89 @@
         <v>2799</v>
       </c>
       <c r="AH7" s="5">
-        <f>AD7*1.02</f>
-        <v>3056.94</v>
-      </c>
-      <c r="AJ7" s="5">
+        <f t="shared" si="12"/>
+        <v>2895</v>
+      </c>
+      <c r="AI7" s="5"/>
+      <c r="AJ7" s="5"/>
+      <c r="AK7" s="5"/>
+      <c r="AL7" s="5"/>
+      <c r="AN7" s="5">
         <v>7222</v>
       </c>
-      <c r="AK7" s="5">
+      <c r="AO7" s="5">
         <f>SUM(C7:F7)</f>
         <v>7934</v>
       </c>
-      <c r="AL7" s="5">
+      <c r="AP7" s="5">
         <f>SUM(G7:J7)</f>
         <v>8949</v>
       </c>
-      <c r="AM7" s="5">
+      <c r="AQ7" s="5">
         <f>SUM(K7:N7)</f>
         <v>9534</v>
       </c>
-      <c r="AN7" s="5">
+      <c r="AR7" s="5">
         <f>SUM(O7:R7)</f>
         <v>9911</v>
       </c>
-      <c r="AO7" s="5">
+      <c r="AS7" s="5">
         <f>SUM(S7:V7)</f>
         <v>10954</v>
       </c>
-      <c r="AP7" s="5">
+      <c r="AT7" s="5">
         <f>SUM(W7:Z7)</f>
         <v>12317</v>
       </c>
-      <c r="AQ7" s="5">
+      <c r="AU7" s="5">
         <f>SUM(AA7:AD7)</f>
         <v>12291</v>
       </c>
-      <c r="AR7" s="5">
-        <f>SUM(AE7:AH7)</f>
-        <v>11560.94</v>
-      </c>
-      <c r="AS7" s="5">
-        <f>AR7*0.99</f>
-        <v>11445.330600000001</v>
-      </c>
-      <c r="AT7" s="5">
-        <f>AS7*1.01</f>
-        <v>11559.783906000001</v>
-      </c>
-      <c r="AU7" s="5">
-        <f>AT7*1.01</f>
-        <v>11675.38174506</v>
-      </c>
       <c r="AV7" s="5">
-        <f t="shared" ref="AV7:BB7" si="14">AU7*1.01</f>
-        <v>11792.135562510601</v>
+        <v>11399</v>
       </c>
       <c r="AW7" s="5">
-        <f t="shared" si="14"/>
-        <v>11910.056918135706</v>
+        <f>AV7*0.99</f>
+        <v>11285.01</v>
       </c>
       <c r="AX7" s="5">
-        <f t="shared" si="14"/>
-        <v>12029.157487317063</v>
+        <f>AW7*1.01</f>
+        <v>11397.8601</v>
       </c>
       <c r="AY7" s="5">
-        <f t="shared" si="14"/>
-        <v>12149.449062190233</v>
+        <f>AX7*1.01</f>
+        <v>11511.838701000001</v>
       </c>
       <c r="AZ7" s="5">
-        <f t="shared" si="14"/>
-        <v>12270.943552812136</v>
+        <f t="shared" ref="AZ7:BF7" si="14">AY7*1.01</f>
+        <v>11626.95708801</v>
       </c>
       <c r="BA7" s="5">
         <f t="shared" si="14"/>
-        <v>12393.652988340256</v>
+        <v>11743.2266588901</v>
       </c>
       <c r="BB7" s="5">
         <f t="shared" si="14"/>
-        <v>12517.589518223658</v>
+        <v>11860.658925479001</v>
+      </c>
+      <c r="BC7" s="5">
+        <f t="shared" si="14"/>
+        <v>11979.265514733792</v>
+      </c>
+      <c r="BD7" s="5">
+        <f t="shared" si="14"/>
+        <v>12099.058169881129</v>
+      </c>
+      <c r="BE7" s="5">
+        <f t="shared" si="14"/>
+        <v>12220.048751579941</v>
+      </c>
+      <c r="BF7" s="5">
+        <f t="shared" si="14"/>
+        <v>12342.249239095741</v>
       </c>
     </row>
-    <row r="8" spans="2:165" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:169" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>28</v>
       </c>
@@ -2214,86 +2264,90 @@
       </c>
       <c r="AH8" s="9">
         <f t="shared" si="22"/>
-        <v>1280.7846000000004</v>
-      </c>
-      <c r="AJ8" s="9">
-        <f>AJ5-AJ6-AJ7</f>
-        <v>4749</v>
-      </c>
-      <c r="AK8" s="9">
-        <f>AK5-AK6-AK7</f>
-        <v>4445</v>
-      </c>
-      <c r="AL8" s="9">
-        <f>AL5-AL6-AL7</f>
-        <v>4772</v>
-      </c>
-      <c r="AM8" s="9">
-        <f>AM5-AM6-AM7</f>
-        <v>3115</v>
-      </c>
+        <v>956.61999999999989</v>
+      </c>
+      <c r="AI8" s="9"/>
+      <c r="AJ8" s="9"/>
+      <c r="AK8" s="9"/>
+      <c r="AL8" s="9"/>
       <c r="AN8" s="9">
         <f>AN5-AN6-AN7</f>
+        <v>4749</v>
+      </c>
+      <c r="AO8" s="9">
+        <f>AO5-AO6-AO7</f>
+        <v>4445</v>
+      </c>
+      <c r="AP8" s="9">
+        <f>AP5-AP6-AP7</f>
+        <v>4772</v>
+      </c>
+      <c r="AQ8" s="9">
+        <f>AQ5-AQ6-AQ7</f>
+        <v>3115</v>
+      </c>
+      <c r="AR8" s="9">
+        <f>AR5-AR6-AR7</f>
         <v>6937</v>
       </c>
-      <c r="AO8" s="9">
-        <f t="shared" ref="AO8:AX8" si="23">AO5-AO6-AO7</f>
+      <c r="AS8" s="9">
+        <f t="shared" ref="AS8:BB8" si="23">AS5-AS6-AS7</f>
         <v>6675</v>
       </c>
-      <c r="AP8" s="9">
+      <c r="AT8" s="9">
         <f t="shared" si="23"/>
         <v>5915</v>
       </c>
-      <c r="AQ8" s="9">
+      <c r="AU8" s="9">
         <f t="shared" si="23"/>
         <v>6311</v>
       </c>
-      <c r="AR8" s="9">
-        <f t="shared" si="23"/>
-        <v>4661.7846000000027</v>
-      </c>
-      <c r="AS8" s="9">
-        <f t="shared" si="23"/>
-        <v>6268.1572919999999</v>
-      </c>
-      <c r="AT8" s="9">
-        <f t="shared" si="23"/>
-        <v>6330.8388649200024</v>
-      </c>
-      <c r="AU8" s="9">
-        <f t="shared" si="23"/>
-        <v>6394.1472535692046</v>
-      </c>
       <c r="AV8" s="9">
         <f t="shared" si="23"/>
-        <v>6458.0887261048956</v>
+        <v>3702</v>
       </c>
       <c r="AW8" s="9">
         <f t="shared" si="23"/>
-        <v>6522.6696133659425</v>
+        <v>5210.1900000000005</v>
       </c>
       <c r="AX8" s="9">
         <f t="shared" si="23"/>
-        <v>6587.8963094996016</v>
+        <v>6391.7398999999987</v>
       </c>
       <c r="AY8" s="9">
-        <f t="shared" ref="AY8:BB8" si="24">AY5-AY6-AY7</f>
-        <v>6653.7752725946011</v>
+        <f t="shared" si="23"/>
+        <v>6811.4492989999999</v>
       </c>
       <c r="AZ8" s="9">
+        <f t="shared" si="23"/>
+        <v>6879.5637919900037</v>
+      </c>
+      <c r="BA8" s="9">
+        <f t="shared" si="23"/>
+        <v>6948.3594299099022</v>
+      </c>
+      <c r="BB8" s="9">
+        <f t="shared" si="23"/>
+        <v>7017.8430242090035</v>
+      </c>
+      <c r="BC8" s="9">
+        <f t="shared" ref="BC8:BF8" si="24">BC5-BC6-BC7</f>
+        <v>7088.0214544510945</v>
+      </c>
+      <c r="BD8" s="9">
         <f t="shared" si="24"/>
-        <v>6720.3130253205491</v>
-      </c>
-      <c r="BA8" s="9">
+        <v>7158.9016689956043</v>
+      </c>
+      <c r="BE8" s="9">
         <f t="shared" si="24"/>
-        <v>6787.5161555737523</v>
-      </c>
-      <c r="BB8" s="9">
+        <v>7230.4906856855614</v>
+      </c>
+      <c r="BF8" s="9">
         <f t="shared" si="24"/>
-        <v>6855.3913171294898</v>
+        <v>7302.7955925424139</v>
       </c>
     </row>
-    <row r="9" spans="2:165" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:169" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>29</v>
       </c>
@@ -2391,86 +2445,89 @@
         <v>-18</v>
       </c>
       <c r="AH9" s="5">
-        <f t="shared" ref="AH9" si="25">AD9*1.05</f>
-        <v>-55.650000000000006</v>
-      </c>
-      <c r="AJ9" s="5">
+        <f t="shared" ref="AH9:AH10" si="25">AV9-AG9-AF9-AE9</f>
+        <v>-22</v>
+      </c>
+      <c r="AI9" s="5"/>
+      <c r="AJ9" s="5"/>
+      <c r="AK9" s="5"/>
+      <c r="AL9" s="5"/>
+      <c r="AN9" s="5">
         <v>59</v>
       </c>
-      <c r="AK9" s="5">
+      <c r="AO9" s="5">
         <f>SUM(C9:F9)</f>
         <v>53</v>
       </c>
-      <c r="AL9" s="5">
+      <c r="AP9" s="5">
         <f>SUM(G9:J9)</f>
         <v>49</v>
       </c>
-      <c r="AM9" s="5">
+      <c r="AQ9" s="5">
         <f>SUM(K9:N9)</f>
         <v>89</v>
       </c>
-      <c r="AN9" s="5">
+      <c r="AR9" s="5">
         <f>SUM(O9:R9)</f>
         <v>262</v>
       </c>
-      <c r="AO9" s="5">
+      <c r="AS9" s="5">
         <f>SUM(S9:V9)</f>
         <v>205</v>
       </c>
-      <c r="AP9" s="5">
+      <c r="AT9" s="5">
         <f>SUM(W9:Z9)</f>
         <v>-6</v>
       </c>
-      <c r="AQ9" s="5">
+      <c r="AU9" s="5">
         <f>SUM(AA9:AD9)</f>
         <v>-161</v>
       </c>
-      <c r="AR9" s="5">
-        <f>SUM(AE9:AH9)</f>
-        <v>-140.65</v>
-      </c>
-      <c r="AS9" s="5">
-        <f t="shared" ref="AS9:BB9" si="26">AR9*1.01</f>
-        <v>-142.0565</v>
-      </c>
-      <c r="AT9" s="5">
-        <f t="shared" si="26"/>
-        <v>-143.47706500000001</v>
-      </c>
-      <c r="AU9" s="5">
-        <f t="shared" si="26"/>
-        <v>-144.91183565</v>
-      </c>
       <c r="AV9" s="5">
-        <f t="shared" si="26"/>
-        <v>-146.36095400650001</v>
+        <v>-107</v>
       </c>
       <c r="AW9" s="5">
-        <f t="shared" si="26"/>
-        <v>-147.824563546565</v>
+        <f t="shared" ref="AW9:BF9" si="26">AV9*1.01</f>
+        <v>-108.07000000000001</v>
       </c>
       <c r="AX9" s="5">
         <f t="shared" si="26"/>
-        <v>-149.30280918203064</v>
+        <v>-109.15070000000001</v>
       </c>
       <c r="AY9" s="5">
         <f t="shared" si="26"/>
-        <v>-150.79583727385096</v>
+        <v>-110.24220700000002</v>
       </c>
       <c r="AZ9" s="5">
         <f t="shared" si="26"/>
-        <v>-152.30379564658946</v>
+        <v>-111.34462907000002</v>
       </c>
       <c r="BA9" s="5">
         <f t="shared" si="26"/>
-        <v>-153.82683360305535</v>
+        <v>-112.45807536070002</v>
       </c>
       <c r="BB9" s="5">
         <f t="shared" si="26"/>
-        <v>-155.36510193908589</v>
+        <v>-113.58265611430703</v>
+      </c>
+      <c r="BC9" s="5">
+        <f t="shared" si="26"/>
+        <v>-114.7184826754501</v>
+      </c>
+      <c r="BD9" s="5">
+        <f t="shared" si="26"/>
+        <v>-115.8656675022046</v>
+      </c>
+      <c r="BE9" s="5">
+        <f t="shared" si="26"/>
+        <v>-117.02432417722665</v>
+      </c>
+      <c r="BF9" s="5">
+        <f t="shared" si="26"/>
+        <v>-118.19456741899891</v>
       </c>
     </row>
-    <row r="10" spans="2:165" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:169" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>30</v>
       </c>
@@ -2568,85 +2625,89 @@
         <v>-38</v>
       </c>
       <c r="AH10" s="5">
-        <v>-50</v>
-      </c>
-      <c r="AJ10" s="5">
+        <f t="shared" si="25"/>
+        <v>25</v>
+      </c>
+      <c r="AI10" s="5"/>
+      <c r="AJ10" s="5"/>
+      <c r="AK10" s="5"/>
+      <c r="AL10" s="5"/>
+      <c r="AN10" s="5">
         <v>-196</v>
       </c>
-      <c r="AK10" s="5">
+      <c r="AO10" s="5">
         <f>SUM(C10:F10)</f>
         <v>66</v>
       </c>
-      <c r="AL10" s="5">
+      <c r="AP10" s="5">
         <f>SUM(G10:J10)</f>
         <v>-78</v>
       </c>
-      <c r="AM10" s="5">
+      <c r="AQ10" s="5">
         <f>SUM(K10:N10)</f>
         <v>139</v>
       </c>
-      <c r="AN10" s="5">
+      <c r="AR10" s="5">
         <f>SUM(O10:R10)</f>
         <v>14</v>
       </c>
-      <c r="AO10" s="5">
+      <c r="AS10" s="5">
         <f>SUM(S10:V10)</f>
         <v>-181</v>
       </c>
-      <c r="AP10" s="5">
+      <c r="AT10" s="5">
         <f>SUM(W10:Z10)</f>
         <v>-280</v>
       </c>
-      <c r="AQ10" s="5">
+      <c r="AU10" s="5">
         <f>SUM(AA10:AD10)</f>
         <v>-228</v>
       </c>
-      <c r="AR10" s="5">
-        <f>SUM(AE10:AH10)</f>
-        <v>-151</v>
-      </c>
-      <c r="AS10" s="5">
-        <f>AR10*1.01</f>
-        <v>-152.51</v>
-      </c>
-      <c r="AT10" s="5">
-        <f t="shared" ref="AT10:BB10" si="27">AS10*1.01</f>
-        <v>-154.0351</v>
-      </c>
-      <c r="AU10" s="5">
-        <f t="shared" si="27"/>
-        <v>-155.57545100000002</v>
-      </c>
       <c r="AV10" s="5">
-        <f t="shared" si="27"/>
-        <v>-157.13120551000003</v>
+        <v>-76</v>
       </c>
       <c r="AW10" s="5">
-        <f t="shared" si="27"/>
-        <v>-158.70251756510004</v>
+        <f>AV10*1.01</f>
+        <v>-76.760000000000005</v>
       </c>
       <c r="AX10" s="5">
-        <f t="shared" si="27"/>
-        <v>-160.28954274075105</v>
+        <f t="shared" ref="AX10:BF10" si="27">AW10*1.01</f>
+        <v>-77.527600000000007</v>
       </c>
       <c r="AY10" s="5">
         <f t="shared" si="27"/>
-        <v>-161.89243816815855</v>
+        <v>-78.302876000000012</v>
       </c>
       <c r="AZ10" s="5">
         <f t="shared" si="27"/>
-        <v>-163.51136254984013</v>
+        <v>-79.08590476000002</v>
       </c>
       <c r="BA10" s="5">
         <f t="shared" si="27"/>
-        <v>-165.14647617533853</v>
+        <v>-79.876763807600014</v>
       </c>
       <c r="BB10" s="5">
         <f t="shared" si="27"/>
-        <v>-166.79794093709191</v>
+        <v>-80.675531445676015</v>
+      </c>
+      <c r="BC10" s="5">
+        <f t="shared" si="27"/>
+        <v>-81.48228676013278</v>
+      </c>
+      <c r="BD10" s="5">
+        <f t="shared" si="27"/>
+        <v>-82.297109627734102</v>
+      </c>
+      <c r="BE10" s="5">
+        <f t="shared" si="27"/>
+        <v>-83.120080724011444</v>
+      </c>
+      <c r="BF10" s="5">
+        <f t="shared" si="27"/>
+        <v>-83.951281531251553</v>
       </c>
     </row>
-    <row r="11" spans="2:165" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:169" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>31</v>
       </c>
@@ -2776,86 +2837,90 @@
       </c>
       <c r="AH11" s="9">
         <f t="shared" si="35"/>
-        <v>1386.4346000000005</v>
-      </c>
-      <c r="AJ11" s="9">
-        <f>AJ8-AJ9-AJ10</f>
-        <v>4886</v>
-      </c>
-      <c r="AK11" s="9">
-        <f>AK8-AK9-AK10</f>
-        <v>4326</v>
-      </c>
-      <c r="AL11" s="9">
-        <f>AL8-AL9-AL10</f>
-        <v>4801</v>
-      </c>
-      <c r="AM11" s="9">
-        <f>AM8-AM9-AM10</f>
-        <v>2887</v>
-      </c>
+        <v>953.61999999999989</v>
+      </c>
+      <c r="AI11" s="9"/>
+      <c r="AJ11" s="9"/>
+      <c r="AK11" s="9"/>
+      <c r="AL11" s="9"/>
       <c r="AN11" s="9">
         <f>AN8-AN9-AN10</f>
+        <v>4886</v>
+      </c>
+      <c r="AO11" s="9">
+        <f>AO8-AO9-AO10</f>
+        <v>4326</v>
+      </c>
+      <c r="AP11" s="9">
+        <f>AP8-AP9-AP10</f>
+        <v>4801</v>
+      </c>
+      <c r="AQ11" s="9">
+        <f>AQ8-AQ9-AQ10</f>
+        <v>2887</v>
+      </c>
+      <c r="AR11" s="9">
+        <f>AR8-AR9-AR10</f>
         <v>6661</v>
       </c>
-      <c r="AO11" s="9">
-        <f t="shared" ref="AO11:AX11" si="36">AO8-AO9-AO10</f>
+      <c r="AS11" s="9">
+        <f t="shared" ref="AS11:BB11" si="36">AS8-AS9-AS10</f>
         <v>6651</v>
       </c>
-      <c r="AP11" s="9">
+      <c r="AT11" s="9">
         <f t="shared" si="36"/>
         <v>6201</v>
       </c>
-      <c r="AQ11" s="9">
+      <c r="AU11" s="9">
         <f t="shared" si="36"/>
         <v>6700</v>
       </c>
-      <c r="AR11" s="9">
-        <f t="shared" si="36"/>
-        <v>4953.4346000000023</v>
-      </c>
-      <c r="AS11" s="9">
-        <f t="shared" si="36"/>
-        <v>6562.7237919999998</v>
-      </c>
-      <c r="AT11" s="9">
-        <f t="shared" si="36"/>
-        <v>6628.3510299200025</v>
-      </c>
-      <c r="AU11" s="9">
-        <f t="shared" si="36"/>
-        <v>6694.6345402192046</v>
-      </c>
       <c r="AV11" s="9">
         <f t="shared" si="36"/>
-        <v>6761.5808856213953</v>
+        <v>3885</v>
       </c>
       <c r="AW11" s="9">
         <f t="shared" si="36"/>
-        <v>6829.1966944776068</v>
+        <v>5395.02</v>
       </c>
       <c r="AX11" s="9">
         <f t="shared" si="36"/>
-        <v>6897.4886614223833</v>
+        <v>6578.4181999999992</v>
       </c>
       <c r="AY11" s="9">
-        <f t="shared" ref="AY11:BB11" si="37">AY8-AY9-AY10</f>
-        <v>6966.4635480366105</v>
+        <f t="shared" si="36"/>
+        <v>6999.9943819999999</v>
       </c>
       <c r="AZ11" s="9">
+        <f t="shared" si="36"/>
+        <v>7069.9943258200037</v>
+      </c>
+      <c r="BA11" s="9">
+        <f t="shared" si="36"/>
+        <v>7140.6942690782016</v>
+      </c>
+      <c r="BB11" s="9">
+        <f t="shared" si="36"/>
+        <v>7212.1012117689861</v>
+      </c>
+      <c r="BC11" s="9">
+        <f t="shared" ref="BC11:BF11" si="37">BC8-BC9-BC10</f>
+        <v>7284.2222238866771</v>
+      </c>
+      <c r="BD11" s="9">
         <f t="shared" si="37"/>
-        <v>7036.1281835169784</v>
-      </c>
-      <c r="BA11" s="9">
+        <v>7357.0644461255433</v>
+      </c>
+      <c r="BE11" s="9">
         <f t="shared" si="37"/>
-        <v>7106.489465352146</v>
-      </c>
-      <c r="BB11" s="9">
+        <v>7430.6350905867994</v>
+      </c>
+      <c r="BF11" s="9">
         <f t="shared" si="37"/>
-        <v>7177.5543600056671</v>
+        <v>7504.941441492665</v>
       </c>
     </row>
-    <row r="12" spans="2:165" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:169" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>32</v>
       </c>
@@ -2953,739 +3018,746 @@
         <v>50</v>
       </c>
       <c r="AH12" s="5">
-        <f t="shared" ref="AH12" si="38">AH11*0.17</f>
-        <v>235.69388200000012</v>
-      </c>
-      <c r="AJ12" s="5">
+        <f>AV12-AG12-AF12-AE12</f>
+        <v>107</v>
+      </c>
+      <c r="AI12" s="5"/>
+      <c r="AJ12" s="5"/>
+      <c r="AK12" s="5"/>
+      <c r="AL12" s="5"/>
+      <c r="AN12" s="5">
         <v>646</v>
       </c>
-      <c r="AK12" s="5">
+      <c r="AO12" s="5">
         <f>SUM(C12:F12)</f>
         <v>2392</v>
       </c>
-      <c r="AL12" s="5">
+      <c r="AP12" s="5">
         <f>SUM(G12:J12)</f>
         <v>772</v>
       </c>
-      <c r="AM12" s="5">
+      <c r="AQ12" s="5">
         <f>SUM(K12:N12)</f>
         <v>348</v>
       </c>
-      <c r="AN12" s="5">
+      <c r="AR12" s="5">
         <f>SUM(O12:R12)</f>
         <v>934</v>
       </c>
-      <c r="AO12" s="5">
+      <c r="AS12" s="5">
         <f>SUM(S12:V12)</f>
         <v>605</v>
       </c>
-      <c r="AP12" s="5">
+      <c r="AT12" s="5">
         <f>SUM(W12:Z12)</f>
         <v>1131</v>
       </c>
-      <c r="AQ12" s="5">
+      <c r="AU12" s="5">
         <f>SUM(AA12:AD12)</f>
         <v>1000</v>
       </c>
-      <c r="AR12" s="5">
-        <f>SUM(AE12:AH12)</f>
-        <v>794.69388200000014</v>
-      </c>
-      <c r="AS12" s="5">
-        <f>AS11*0.17</f>
-        <v>1115.66304464</v>
-      </c>
-      <c r="AT12" s="5">
-        <f t="shared" ref="AT12:BB12" si="39">AT11*0.17</f>
-        <v>1126.8196750864006</v>
-      </c>
-      <c r="AU12" s="5">
-        <f t="shared" si="39"/>
-        <v>1138.0878718372649</v>
-      </c>
       <c r="AV12" s="5">
-        <f t="shared" si="39"/>
-        <v>1149.4687505556374</v>
+        <v>666</v>
       </c>
       <c r="AW12" s="5">
-        <f t="shared" si="39"/>
-        <v>1160.9634380611933</v>
+        <f>AW11*0.17</f>
+        <v>917.15340000000015</v>
       </c>
       <c r="AX12" s="5">
-        <f t="shared" si="39"/>
-        <v>1172.5730724418052</v>
+        <f t="shared" ref="AX12:BF12" si="38">AX11*0.17</f>
+        <v>1118.3310939999999</v>
       </c>
       <c r="AY12" s="5">
-        <f t="shared" si="39"/>
-        <v>1184.2988031662239</v>
+        <f t="shared" si="38"/>
+        <v>1189.99904494</v>
       </c>
       <c r="AZ12" s="5">
-        <f t="shared" si="39"/>
-        <v>1196.1417911978865</v>
+        <f t="shared" si="38"/>
+        <v>1201.8990353894008</v>
       </c>
       <c r="BA12" s="5">
-        <f t="shared" si="39"/>
-        <v>1208.103209109865</v>
+        <f t="shared" si="38"/>
+        <v>1213.9180257432943</v>
       </c>
       <c r="BB12" s="5">
-        <f t="shared" si="39"/>
-        <v>1220.1842412009635</v>
+        <f t="shared" si="38"/>
+        <v>1226.0572060007278</v>
+      </c>
+      <c r="BC12" s="5">
+        <f t="shared" si="38"/>
+        <v>1238.3177780607352</v>
+      </c>
+      <c r="BD12" s="5">
+        <f t="shared" si="38"/>
+        <v>1250.7009558413424</v>
+      </c>
+      <c r="BE12" s="5">
+        <f t="shared" si="38"/>
+        <v>1263.2079653997559</v>
+      </c>
+      <c r="BF12" s="5">
+        <f t="shared" si="38"/>
+        <v>1275.8400450537531</v>
       </c>
     </row>
-    <row r="13" spans="2:165" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:169" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C13" s="9">
-        <f t="shared" ref="C13:S13" si="40">C11-C12</f>
+        <f t="shared" ref="C13:S13" si="39">C11-C12</f>
         <v>950</v>
       </c>
       <c r="D13" s="9">
+        <f t="shared" si="39"/>
+        <v>767</v>
+      </c>
+      <c r="E13" s="9">
+        <f t="shared" si="39"/>
+        <v>-920</v>
+      </c>
+      <c r="F13" s="9">
+        <f t="shared" si="39"/>
+        <v>1137</v>
+      </c>
+      <c r="G13" s="9">
+        <f t="shared" si="39"/>
+        <v>1092</v>
+      </c>
+      <c r="H13" s="9">
+        <f t="shared" si="39"/>
+        <v>847</v>
+      </c>
+      <c r="I13" s="9">
+        <f t="shared" si="39"/>
+        <v>1101</v>
+      </c>
+      <c r="J13" s="9">
+        <f t="shared" si="39"/>
+        <v>989</v>
+      </c>
+      <c r="K13" s="9">
+        <f t="shared" si="39"/>
+        <v>1367</v>
+      </c>
+      <c r="L13" s="9">
+        <f t="shared" si="39"/>
+        <v>1115</v>
+      </c>
+      <c r="M13" s="9">
+        <f t="shared" si="39"/>
+        <v>847</v>
+      </c>
+      <c r="N13" s="9">
+        <f t="shared" si="39"/>
+        <v>-790</v>
+      </c>
+      <c r="O13" s="9">
+        <f t="shared" si="39"/>
+        <v>1518</v>
+      </c>
+      <c r="P13" s="9">
+        <f t="shared" si="39"/>
+        <v>1251</v>
+      </c>
+      <c r="Q13" s="9">
+        <f t="shared" si="39"/>
+        <v>1449</v>
+      </c>
+      <c r="R13" s="9">
+        <f t="shared" si="39"/>
+        <v>1509</v>
+      </c>
+      <c r="S13" s="9">
+        <f t="shared" si="39"/>
+        <v>1874</v>
+      </c>
+      <c r="T13" s="9">
+        <f t="shared" ref="T13:U13" si="40">T11-T12</f>
+        <v>1337</v>
+      </c>
+      <c r="U13" s="9">
         <f t="shared" si="40"/>
-        <v>767</v>
-      </c>
-      <c r="E13" s="9">
-        <f t="shared" si="40"/>
-        <v>-920</v>
-      </c>
-      <c r="F13" s="9">
-        <f t="shared" si="40"/>
-        <v>1137</v>
-      </c>
-      <c r="G13" s="9">
-        <f t="shared" si="40"/>
-        <v>1092</v>
-      </c>
-      <c r="H13" s="9">
-        <f t="shared" si="40"/>
-        <v>847</v>
-      </c>
-      <c r="I13" s="9">
-        <f t="shared" si="40"/>
-        <v>1101</v>
-      </c>
-      <c r="J13" s="9">
-        <f t="shared" si="40"/>
-        <v>989</v>
-      </c>
-      <c r="K13" s="9">
-        <f t="shared" si="40"/>
-        <v>1367</v>
-      </c>
-      <c r="L13" s="9">
-        <f t="shared" si="40"/>
-        <v>1115</v>
-      </c>
-      <c r="M13" s="9">
-        <f t="shared" si="40"/>
-        <v>847</v>
-      </c>
-      <c r="N13" s="9">
-        <f t="shared" si="40"/>
-        <v>-790</v>
-      </c>
-      <c r="O13" s="9">
-        <f t="shared" si="40"/>
-        <v>1518</v>
-      </c>
-      <c r="P13" s="9">
-        <f t="shared" si="40"/>
-        <v>1251</v>
-      </c>
-      <c r="Q13" s="9">
-        <f t="shared" si="40"/>
-        <v>1449</v>
-      </c>
-      <c r="R13" s="9">
-        <f t="shared" si="40"/>
-        <v>1509</v>
-      </c>
-      <c r="S13" s="9">
-        <f t="shared" si="40"/>
-        <v>1874</v>
-      </c>
-      <c r="T13" s="9">
-        <f t="shared" ref="T13:U13" si="41">T11-T12</f>
-        <v>1337</v>
-      </c>
-      <c r="U13" s="9">
+        <v>1396</v>
+      </c>
+      <c r="V13" s="9">
+        <f t="shared" ref="V13:W13" si="41">V11-V12</f>
+        <v>1439</v>
+      </c>
+      <c r="W13" s="9">
         <f t="shared" si="41"/>
-        <v>1396</v>
-      </c>
-      <c r="V13" s="9">
-        <f t="shared" ref="V13:W13" si="42">V11-V12</f>
-        <v>1439</v>
-      </c>
-      <c r="W13" s="9">
-        <f t="shared" si="42"/>
         <v>1468</v>
       </c>
       <c r="X13" s="9">
-        <f t="shared" ref="X13" si="43">X11-X12</f>
+        <f t="shared" ref="X13" si="42">X11-X12</f>
         <v>1331</v>
       </c>
       <c r="Y13" s="9">
-        <f t="shared" ref="Y13:AA13" si="44">Y11-Y12</f>
+        <f t="shared" ref="Y13:AA13" si="43">Y11-Y12</f>
         <v>1240</v>
       </c>
       <c r="Z13" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>1031</v>
       </c>
       <c r="AA13" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>1450</v>
       </c>
       <c r="AB13" s="9">
-        <f t="shared" ref="AB13" si="45">AB11-AB12</f>
+        <f t="shared" ref="AB13" si="44">AB11-AB12</f>
         <v>1578</v>
       </c>
       <c r="AC13" s="9">
-        <f t="shared" ref="AC13:AD13" si="46">AC11-AC12</f>
+        <f t="shared" ref="AC13:AD13" si="45">AC11-AC12</f>
         <v>1172</v>
       </c>
       <c r="AD13" s="9">
+        <f t="shared" si="45"/>
+        <v>1500</v>
+      </c>
+      <c r="AE13" s="9">
+        <f t="shared" ref="AE13:AH13" si="46">AE11-AE12</f>
+        <v>1051</v>
+      </c>
+      <c r="AF13" s="9">
         <f t="shared" si="46"/>
-        <v>1500</v>
-      </c>
-      <c r="AE13" s="9">
-        <f t="shared" ref="AE13:AH13" si="47">AE11-AE12</f>
-        <v>1051</v>
-      </c>
-      <c r="AF13" s="9">
-        <f t="shared" si="47"/>
         <v>1163</v>
       </c>
       <c r="AG13" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>794</v>
       </c>
       <c r="AH13" s="9">
-        <f t="shared" si="47"/>
-        <v>1150.7407180000005</v>
-      </c>
-      <c r="AJ13" s="9">
-        <f>AJ11-AJ12</f>
-        <v>4240</v>
-      </c>
-      <c r="AK13" s="9">
-        <f>AK11-AK12</f>
-        <v>1934</v>
-      </c>
-      <c r="AL13" s="9">
-        <f>AL11-AL12</f>
-        <v>4029</v>
-      </c>
-      <c r="AM13" s="9">
-        <f>AM11-AM12</f>
-        <v>2539</v>
-      </c>
+        <f t="shared" si="46"/>
+        <v>846.61999999999989</v>
+      </c>
+      <c r="AI13" s="9"/>
+      <c r="AJ13" s="9"/>
+      <c r="AK13" s="9"/>
+      <c r="AL13" s="9"/>
       <c r="AN13" s="9">
         <f>AN11-AN12</f>
+        <v>4240</v>
+      </c>
+      <c r="AO13" s="9">
+        <f>AO11-AO12</f>
+        <v>1934</v>
+      </c>
+      <c r="AP13" s="9">
+        <f>AP11-AP12</f>
+        <v>4029</v>
+      </c>
+      <c r="AQ13" s="9">
+        <f>AQ11-AQ12</f>
+        <v>2539</v>
+      </c>
+      <c r="AR13" s="9">
+        <f>AR11-AR12</f>
         <v>5727</v>
       </c>
-      <c r="AO13" s="9">
-        <f t="shared" ref="AO13:AX13" si="48">AO11-AO12</f>
+      <c r="AS13" s="9">
+        <f t="shared" ref="AS13:BB13" si="47">AS11-AS12</f>
         <v>6046</v>
       </c>
-      <c r="AP13" s="9">
+      <c r="AT13" s="9">
+        <f t="shared" si="47"/>
+        <v>5070</v>
+      </c>
+      <c r="AU13" s="9">
+        <f t="shared" si="47"/>
+        <v>5700</v>
+      </c>
+      <c r="AV13" s="9">
+        <f t="shared" si="47"/>
+        <v>3219</v>
+      </c>
+      <c r="AW13" s="9">
+        <f t="shared" si="47"/>
+        <v>4477.8666000000003</v>
+      </c>
+      <c r="AX13" s="9">
+        <f t="shared" si="47"/>
+        <v>5460.087105999999</v>
+      </c>
+      <c r="AY13" s="9">
+        <f t="shared" si="47"/>
+        <v>5809.9953370599997</v>
+      </c>
+      <c r="AZ13" s="9">
+        <f t="shared" si="47"/>
+        <v>5868.0952904306032</v>
+      </c>
+      <c r="BA13" s="9">
+        <f t="shared" si="47"/>
+        <v>5926.7762433349071</v>
+      </c>
+      <c r="BB13" s="9">
+        <f t="shared" si="47"/>
+        <v>5986.0440057682581</v>
+      </c>
+      <c r="BC13" s="9">
+        <f t="shared" ref="BC13:BF13" si="48">BC11-BC12</f>
+        <v>6045.9044458259414</v>
+      </c>
+      <c r="BD13" s="9">
         <f t="shared" si="48"/>
-        <v>5070</v>
-      </c>
-      <c r="AQ13" s="9">
+        <v>6106.3634902842005</v>
+      </c>
+      <c r="BE13" s="9">
         <f t="shared" si="48"/>
-        <v>5700</v>
-      </c>
-      <c r="AR13" s="9">
+        <v>6167.4271251870432</v>
+      </c>
+      <c r="BF13" s="9">
         <f t="shared" si="48"/>
-        <v>4158.7407180000018</v>
-      </c>
-      <c r="AS13" s="9">
-        <f t="shared" si="48"/>
-        <v>5447.0607473599994</v>
-      </c>
-      <c r="AT13" s="9">
-        <f t="shared" si="48"/>
-        <v>5501.5313548336017</v>
-      </c>
-      <c r="AU13" s="9">
-        <f t="shared" si="48"/>
-        <v>5556.5466683819395</v>
-      </c>
-      <c r="AV13" s="9">
-        <f t="shared" si="48"/>
-        <v>5612.1121350657577</v>
-      </c>
-      <c r="AW13" s="9">
-        <f t="shared" si="48"/>
-        <v>5668.2332564164135</v>
-      </c>
-      <c r="AX13" s="9">
-        <f t="shared" si="48"/>
-        <v>5724.9155889805779</v>
-      </c>
-      <c r="AY13" s="9">
-        <f t="shared" ref="AY13:BB13" si="49">AY11-AY12</f>
-        <v>5782.1647448703861</v>
-      </c>
-      <c r="AZ13" s="9">
-        <f t="shared" si="49"/>
-        <v>5839.9863923190915</v>
-      </c>
-      <c r="BA13" s="9">
-        <f t="shared" si="49"/>
-        <v>5898.386256242281</v>
-      </c>
-      <c r="BB13" s="9">
-        <f t="shared" si="49"/>
-        <v>5957.3701188047035</v>
-      </c>
-      <c r="BC13" s="1">
-        <f>BB13*(1+$BE$19)</f>
-        <v>5897.7964176166561</v>
-      </c>
-      <c r="BD13" s="1">
-        <f t="shared" ref="BD13:DO13" si="50">BC13*(1+$BE$19)</f>
-        <v>5838.8184534404891</v>
-      </c>
-      <c r="BE13" s="1">
+        <v>6229.1013964389122</v>
+      </c>
+      <c r="BG13" s="1">
+        <f>BF13*(1+$BI$19)</f>
+        <v>6166.8103824745231</v>
+      </c>
+      <c r="BH13" s="1">
+        <f t="shared" ref="BH13:DS13" si="49">BG13*(1+$BI$19)</f>
+        <v>6105.1422786497778</v>
+      </c>
+      <c r="BI13" s="1">
+        <f t="shared" si="49"/>
+        <v>6044.09085586328</v>
+      </c>
+      <c r="BJ13" s="1">
+        <f t="shared" si="49"/>
+        <v>5983.649947304647</v>
+      </c>
+      <c r="BK13" s="1">
+        <f t="shared" si="49"/>
+        <v>5923.8134478316006</v>
+      </c>
+      <c r="BL13" s="1">
+        <f t="shared" si="49"/>
+        <v>5864.5753133532844</v>
+      </c>
+      <c r="BM13" s="1">
+        <f t="shared" si="49"/>
+        <v>5805.9295602197517</v>
+      </c>
+      <c r="BN13" s="1">
+        <f t="shared" si="49"/>
+        <v>5747.8702646175543</v>
+      </c>
+      <c r="BO13" s="1">
+        <f t="shared" si="49"/>
+        <v>5690.3915619713789</v>
+      </c>
+      <c r="BP13" s="1">
+        <f t="shared" si="49"/>
+        <v>5633.4876463516648</v>
+      </c>
+      <c r="BQ13" s="1">
+        <f t="shared" si="49"/>
+        <v>5577.1527698881482</v>
+      </c>
+      <c r="BR13" s="1">
+        <f t="shared" si="49"/>
+        <v>5521.3812421892662</v>
+      </c>
+      <c r="BS13" s="1">
+        <f t="shared" si="49"/>
+        <v>5466.1674297673735</v>
+      </c>
+      <c r="BT13" s="1">
+        <f t="shared" si="49"/>
+        <v>5411.5057554696996</v>
+      </c>
+      <c r="BU13" s="1">
+        <f t="shared" si="49"/>
+        <v>5357.3906979150024</v>
+      </c>
+      <c r="BV13" s="1">
+        <f t="shared" si="49"/>
+        <v>5303.8167909358526</v>
+      </c>
+      <c r="BW13" s="1">
+        <f t="shared" si="49"/>
+        <v>5250.7786230264937</v>
+      </c>
+      <c r="BX13" s="1">
+        <f t="shared" si="49"/>
+        <v>5198.2708367962287</v>
+      </c>
+      <c r="BY13" s="1">
+        <f t="shared" si="49"/>
+        <v>5146.2881284282666</v>
+      </c>
+      <c r="BZ13" s="1">
+        <f t="shared" si="49"/>
+        <v>5094.8252471439837</v>
+      </c>
+      <c r="CA13" s="1">
+        <f t="shared" si="49"/>
+        <v>5043.8769946725442</v>
+      </c>
+      <c r="CB13" s="1">
+        <f t="shared" si="49"/>
+        <v>4993.4382247258191</v>
+      </c>
+      <c r="CC13" s="1">
+        <f t="shared" si="49"/>
+        <v>4943.5038424785607</v>
+      </c>
+      <c r="CD13" s="1">
+        <f t="shared" si="49"/>
+        <v>4894.0688040537752</v>
+      </c>
+      <c r="CE13" s="1">
+        <f t="shared" si="49"/>
+        <v>4845.1281160132376</v>
+      </c>
+      <c r="CF13" s="1">
+        <f t="shared" si="49"/>
+        <v>4796.676834853105</v>
+      </c>
+      <c r="CG13" s="1">
+        <f t="shared" si="49"/>
+        <v>4748.7100665045737</v>
+      </c>
+      <c r="CH13" s="1">
+        <f t="shared" si="49"/>
+        <v>4701.2229658395281</v>
+      </c>
+      <c r="CI13" s="1">
+        <f t="shared" si="49"/>
+        <v>4654.2107361811331</v>
+      </c>
+      <c r="CJ13" s="1">
+        <f t="shared" si="49"/>
+        <v>4607.6686288193214</v>
+      </c>
+      <c r="CK13" s="1">
+        <f t="shared" si="49"/>
+        <v>4561.5919425311286</v>
+      </c>
+      <c r="CL13" s="1">
+        <f t="shared" si="49"/>
+        <v>4515.9760231058171</v>
+      </c>
+      <c r="CM13" s="1">
+        <f t="shared" si="49"/>
+        <v>4470.8162628747586</v>
+      </c>
+      <c r="CN13" s="1">
+        <f t="shared" si="49"/>
+        <v>4426.1081002460114</v>
+      </c>
+      <c r="CO13" s="1">
+        <f t="shared" si="49"/>
+        <v>4381.8470192435516</v>
+      </c>
+      <c r="CP13" s="1">
+        <f t="shared" si="49"/>
+        <v>4338.028549051116</v>
+      </c>
+      <c r="CQ13" s="1">
+        <f t="shared" si="49"/>
+        <v>4294.6482635606044</v>
+      </c>
+      <c r="CR13" s="1">
+        <f t="shared" si="49"/>
+        <v>4251.7017809249983</v>
+      </c>
+      <c r="CS13" s="1">
+        <f t="shared" si="49"/>
+        <v>4209.184763115748</v>
+      </c>
+      <c r="CT13" s="1">
+        <f t="shared" si="49"/>
+        <v>4167.0929154845908</v>
+      </c>
+      <c r="CU13" s="1">
+        <f t="shared" si="49"/>
+        <v>4125.4219863297449</v>
+      </c>
+      <c r="CV13" s="1">
+        <f t="shared" si="49"/>
+        <v>4084.1677664664476</v>
+      </c>
+      <c r="CW13" s="1">
+        <f t="shared" si="49"/>
+        <v>4043.326088801783</v>
+      </c>
+      <c r="CX13" s="1">
+        <f t="shared" si="49"/>
+        <v>4002.8928279137654</v>
+      </c>
+      <c r="CY13" s="1">
+        <f t="shared" si="49"/>
+        <v>3962.8638996346276</v>
+      </c>
+      <c r="CZ13" s="1">
+        <f t="shared" si="49"/>
+        <v>3923.2352606382815</v>
+      </c>
+      <c r="DA13" s="1">
+        <f t="shared" si="49"/>
+        <v>3884.0029080318986</v>
+      </c>
+      <c r="DB13" s="1">
+        <f t="shared" si="49"/>
+        <v>3845.1628789515798</v>
+      </c>
+      <c r="DC13" s="1">
+        <f t="shared" si="49"/>
+        <v>3806.7112501620641</v>
+      </c>
+      <c r="DD13" s="1">
+        <f t="shared" si="49"/>
+        <v>3768.6441376604434</v>
+      </c>
+      <c r="DE13" s="1">
+        <f t="shared" si="49"/>
+        <v>3730.9576962838391</v>
+      </c>
+      <c r="DF13" s="1">
+        <f t="shared" si="49"/>
+        <v>3693.6481193210006</v>
+      </c>
+      <c r="DG13" s="1">
+        <f t="shared" si="49"/>
+        <v>3656.7116381277906</v>
+      </c>
+      <c r="DH13" s="1">
+        <f t="shared" si="49"/>
+        <v>3620.1445217465125</v>
+      </c>
+      <c r="DI13" s="1">
+        <f t="shared" si="49"/>
+        <v>3583.9430765290472</v>
+      </c>
+      <c r="DJ13" s="1">
+        <f t="shared" si="49"/>
+        <v>3548.1036457637565</v>
+      </c>
+      <c r="DK13" s="1">
+        <f t="shared" si="49"/>
+        <v>3512.6226093061191</v>
+      </c>
+      <c r="DL13" s="1">
+        <f t="shared" si="49"/>
+        <v>3477.4963832130579</v>
+      </c>
+      <c r="DM13" s="1">
+        <f t="shared" si="49"/>
+        <v>3442.7214193809273</v>
+      </c>
+      <c r="DN13" s="1">
+        <f t="shared" si="49"/>
+        <v>3408.2942051871178</v>
+      </c>
+      <c r="DO13" s="1">
+        <f t="shared" si="49"/>
+        <v>3374.2112631352466</v>
+      </c>
+      <c r="DP13" s="1">
+        <f t="shared" si="49"/>
+        <v>3340.4691505038941</v>
+      </c>
+      <c r="DQ13" s="1">
+        <f t="shared" si="49"/>
+        <v>3307.0644589988551</v>
+      </c>
+      <c r="DR13" s="1">
+        <f t="shared" si="49"/>
+        <v>3273.9938144088665</v>
+      </c>
+      <c r="DS13" s="1">
+        <f t="shared" si="49"/>
+        <v>3241.2538762647778</v>
+      </c>
+      <c r="DT13" s="1">
+        <f t="shared" ref="DT13:FM13" si="50">DS13*(1+$BI$19)</f>
+        <v>3208.84133750213</v>
+      </c>
+      <c r="DU13" s="1">
         <f t="shared" si="50"/>
-        <v>5780.4302689060842</v>
-      </c>
-      <c r="BF13" s="1">
+        <v>3176.7529241271086</v>
+      </c>
+      <c r="DV13" s="1">
         <f t="shared" si="50"/>
-        <v>5722.6259662170232</v>
-      </c>
-      <c r="BG13" s="1">
+        <v>3144.9853948858376</v>
+      </c>
+      <c r="DW13" s="1">
         <f t="shared" si="50"/>
-        <v>5665.3997065548529</v>
-      </c>
-      <c r="BH13" s="1">
+        <v>3113.535540936979</v>
+      </c>
+      <c r="DX13" s="1">
         <f t="shared" si="50"/>
-        <v>5608.7457094893043</v>
-      </c>
-      <c r="BI13" s="1">
+        <v>3082.4001855276092</v>
+      </c>
+      <c r="DY13" s="1">
         <f t="shared" si="50"/>
-        <v>5552.6582523944116</v>
-      </c>
-      <c r="BJ13" s="1">
+        <v>3051.5761836723332</v>
+      </c>
+      <c r="DZ13" s="1">
         <f t="shared" si="50"/>
-        <v>5497.1316698704677</v>
-      </c>
-      <c r="BK13" s="1">
+        <v>3021.0604218356098</v>
+      </c>
+      <c r="EA13" s="1">
         <f t="shared" si="50"/>
-        <v>5442.1603531717628</v>
-      </c>
-      <c r="BL13" s="1">
+        <v>2990.8498176172538</v>
+      </c>
+      <c r="EB13" s="1">
         <f t="shared" si="50"/>
-        <v>5387.7387496400452</v>
-      </c>
-      <c r="BM13" s="1">
+        <v>2960.9413194410813</v>
+      </c>
+      <c r="EC13" s="1">
         <f t="shared" si="50"/>
-        <v>5333.8613621436443</v>
-      </c>
-      <c r="BN13" s="1">
+        <v>2931.3319062466703</v>
+      </c>
+      <c r="ED13" s="1">
         <f t="shared" si="50"/>
-        <v>5280.5227485222076</v>
-      </c>
-      <c r="BO13" s="1">
+        <v>2902.0185871842036</v>
+      </c>
+      <c r="EE13" s="1">
         <f t="shared" si="50"/>
-        <v>5227.7175210369851</v>
-      </c>
-      <c r="BP13" s="1">
+        <v>2872.9984013123617</v>
+      </c>
+      <c r="EF13" s="1">
         <f t="shared" si="50"/>
-        <v>5175.4403458266152</v>
-      </c>
-      <c r="BQ13" s="1">
+        <v>2844.2684172992381</v>
+      </c>
+      <c r="EG13" s="1">
         <f t="shared" si="50"/>
-        <v>5123.6859423683491</v>
-      </c>
-      <c r="BR13" s="1">
+        <v>2815.8257331262457</v>
+      </c>
+      <c r="EH13" s="1">
         <f t="shared" si="50"/>
-        <v>5072.4490829446659</v>
-      </c>
-      <c r="BS13" s="1">
+        <v>2787.6674757949831</v>
+      </c>
+      <c r="EI13" s="1">
         <f t="shared" si="50"/>
-        <v>5021.7245921152189</v>
-      </c>
-      <c r="BT13" s="1">
+        <v>2759.7908010370334</v>
+      </c>
+      <c r="EJ13" s="1">
         <f t="shared" si="50"/>
-        <v>4971.5073461940665</v>
-      </c>
-      <c r="BU13" s="1">
+        <v>2732.1928930266631</v>
+      </c>
+      <c r="EK13" s="1">
         <f t="shared" si="50"/>
-        <v>4921.7922727321256</v>
-      </c>
-      <c r="BV13" s="1">
+        <v>2704.8709640963966</v>
+      </c>
+      <c r="EL13" s="1">
         <f t="shared" si="50"/>
-        <v>4872.5743500048047</v>
-      </c>
-      <c r="BW13" s="1">
+        <v>2677.8222544554328</v>
+      </c>
+      <c r="EM13" s="1">
         <f t="shared" si="50"/>
-        <v>4823.8486065047564</v>
-      </c>
-      <c r="BX13" s="1">
+        <v>2651.0440319108784</v>
+      </c>
+      <c r="EN13" s="1">
         <f t="shared" si="50"/>
-        <v>4775.6101204397091</v>
-      </c>
-      <c r="BY13" s="1">
+        <v>2624.5335915917694</v>
+      </c>
+      <c r="EO13" s="1">
         <f t="shared" si="50"/>
-        <v>4727.8540192353121</v>
-      </c>
-      <c r="BZ13" s="1">
+        <v>2598.2882556758518</v>
+      </c>
+      <c r="EP13" s="1">
         <f t="shared" si="50"/>
-        <v>4680.5754790429592</v>
-      </c>
-      <c r="CA13" s="1">
+        <v>2572.3053731190935</v>
+      </c>
+      <c r="EQ13" s="1">
         <f t="shared" si="50"/>
-        <v>4633.7697242525292</v>
-      </c>
-      <c r="CB13" s="1">
+        <v>2546.5823193879023</v>
+      </c>
+      <c r="ER13" s="1">
         <f t="shared" si="50"/>
-        <v>4587.4320270100043</v>
-      </c>
-      <c r="CC13" s="1">
+        <v>2521.1164961940231</v>
+      </c>
+      <c r="ES13" s="1">
         <f t="shared" si="50"/>
-        <v>4541.5577067399045</v>
-      </c>
-      <c r="CD13" s="1">
+        <v>2495.905331232083</v>
+      </c>
+      <c r="ET13" s="1">
         <f t="shared" si="50"/>
-        <v>4496.1421296725057</v>
-      </c>
-      <c r="CE13" s="1">
+        <v>2470.946277919762</v>
+      </c>
+      <c r="EU13" s="1">
         <f t="shared" si="50"/>
-        <v>4451.1807083757803</v>
-      </c>
-      <c r="CF13" s="1">
+        <v>2446.2368151405644</v>
+      </c>
+      <c r="EV13" s="1">
         <f t="shared" si="50"/>
-        <v>4406.6689012920224</v>
-      </c>
-      <c r="CG13" s="1">
+        <v>2421.7744469891586</v>
+      </c>
+      <c r="EW13" s="1">
         <f t="shared" si="50"/>
-        <v>4362.6022122791019</v>
-      </c>
-      <c r="CH13" s="1">
+        <v>2397.5567025192672</v>
+      </c>
+      <c r="EX13" s="1">
         <f t="shared" si="50"/>
-        <v>4318.9761901563106</v>
-      </c>
-      <c r="CI13" s="1">
+        <v>2373.5811354940747</v>
+      </c>
+      <c r="EY13" s="1">
         <f t="shared" si="50"/>
-        <v>4275.7864282547471</v>
-      </c>
-      <c r="CJ13" s="1">
+        <v>2349.8453241391339</v>
+      </c>
+      <c r="EZ13" s="1">
         <f t="shared" si="50"/>
-        <v>4233.0285639721997</v>
-      </c>
-      <c r="CK13" s="1">
+        <v>2326.3468708977425</v>
+      </c>
+      <c r="FA13" s="1">
         <f t="shared" si="50"/>
-        <v>4190.6982783324775</v>
-      </c>
-      <c r="CL13" s="1">
+        <v>2303.0834021887649</v>
+      </c>
+      <c r="FB13" s="1">
         <f t="shared" si="50"/>
-        <v>4148.7912955491529</v>
-      </c>
-      <c r="CM13" s="1">
+        <v>2280.0525681668773</v>
+      </c>
+      <c r="FC13" s="1">
         <f t="shared" si="50"/>
-        <v>4107.3033825936609</v>
-      </c>
-      <c r="CN13" s="1">
+        <v>2257.2520424852087</v>
+      </c>
+      <c r="FD13" s="1">
         <f t="shared" si="50"/>
-        <v>4066.2303487677241</v>
-      </c>
-      <c r="CO13" s="1">
+        <v>2234.6795220603567</v>
+      </c>
+      <c r="FE13" s="1">
         <f t="shared" si="50"/>
-        <v>4025.5680452800466</v>
-      </c>
-      <c r="CP13" s="1">
+        <v>2212.3327268397529</v>
+      </c>
+      <c r="FF13" s="1">
         <f t="shared" si="50"/>
-        <v>3985.3123648272463</v>
-      </c>
-      <c r="CQ13" s="1">
+        <v>2190.2093995713553</v>
+      </c>
+      <c r="FG13" s="1">
         <f t="shared" si="50"/>
-        <v>3945.4592411789736</v>
-      </c>
-      <c r="CR13" s="1">
+        <v>2168.3073055756417</v>
+      </c>
+      <c r="FH13" s="1">
         <f t="shared" si="50"/>
-        <v>3906.0046487671839</v>
-      </c>
-      <c r="CS13" s="1">
+        <v>2146.6242325198855</v>
+      </c>
+      <c r="FI13" s="1">
         <f t="shared" si="50"/>
-        <v>3866.9446022795119</v>
-      </c>
-      <c r="CT13" s="1">
+        <v>2125.1579901946866</v>
+      </c>
+      <c r="FJ13" s="1">
         <f t="shared" si="50"/>
-        <v>3828.2751562567169</v>
-      </c>
-      <c r="CU13" s="1">
+        <v>2103.9064102927396</v>
+      </c>
+      <c r="FK13" s="1">
         <f t="shared" si="50"/>
-        <v>3789.9924046941496</v>
-      </c>
-      <c r="CV13" s="1">
+        <v>2082.867346189812</v>
+      </c>
+      <c r="FL13" s="1">
         <f t="shared" si="50"/>
-        <v>3752.092480647208</v>
-      </c>
-      <c r="CW13" s="1">
+        <v>2062.0386727279138</v>
+      </c>
+      <c r="FM13" s="1">
         <f t="shared" si="50"/>
-        <v>3714.571555840736</v>
-      </c>
-      <c r="CX13" s="1">
-        <f t="shared" si="50"/>
-        <v>3677.4258402823284</v>
-      </c>
-      <c r="CY13" s="1">
-        <f t="shared" si="50"/>
-        <v>3640.6515818795051</v>
-      </c>
-      <c r="CZ13" s="1">
-        <f t="shared" si="50"/>
-        <v>3604.2450660607101</v>
-      </c>
-      <c r="DA13" s="1">
-        <f t="shared" si="50"/>
-        <v>3568.2026154001028</v>
-      </c>
-      <c r="DB13" s="1">
-        <f t="shared" si="50"/>
-        <v>3532.5205892461017</v>
-      </c>
-      <c r="DC13" s="1">
-        <f t="shared" si="50"/>
-        <v>3497.1953833536409</v>
-      </c>
-      <c r="DD13" s="1">
-        <f t="shared" si="50"/>
-        <v>3462.2234295201042</v>
-      </c>
-      <c r="DE13" s="1">
-        <f t="shared" si="50"/>
-        <v>3427.6011952249032</v>
-      </c>
-      <c r="DF13" s="1">
-        <f t="shared" si="50"/>
-        <v>3393.3251832726542</v>
-      </c>
-      <c r="DG13" s="1">
-        <f t="shared" si="50"/>
-        <v>3359.3919314399277</v>
-      </c>
-      <c r="DH13" s="1">
-        <f t="shared" si="50"/>
-        <v>3325.7980121255282</v>
-      </c>
-      <c r="DI13" s="1">
-        <f t="shared" si="50"/>
-        <v>3292.5400320042727</v>
-      </c>
-      <c r="DJ13" s="1">
-        <f t="shared" si="50"/>
-        <v>3259.6146316842301</v>
-      </c>
-      <c r="DK13" s="1">
-        <f t="shared" si="50"/>
-        <v>3227.0184853673877</v>
-      </c>
-      <c r="DL13" s="1">
-        <f t="shared" si="50"/>
-        <v>3194.7483005137137</v>
-      </c>
-      <c r="DM13" s="1">
-        <f t="shared" si="50"/>
-        <v>3162.8008175085765</v>
-      </c>
-      <c r="DN13" s="1">
-        <f t="shared" si="50"/>
-        <v>3131.1728093334909</v>
-      </c>
-      <c r="DO13" s="1">
-        <f t="shared" si="50"/>
-        <v>3099.8610812401562</v>
-      </c>
-      <c r="DP13" s="1">
-        <f t="shared" ref="DP13:FI13" si="51">DO13*(1+$BE$19)</f>
-        <v>3068.8624704277545</v>
-      </c>
-      <c r="DQ13" s="1">
-        <f t="shared" si="51"/>
-        <v>3038.1738457234769</v>
-      </c>
-      <c r="DR13" s="1">
-        <f t="shared" si="51"/>
-        <v>3007.7921072662421</v>
-      </c>
-      <c r="DS13" s="1">
-        <f t="shared" si="51"/>
-        <v>2977.7141861935797</v>
-      </c>
-      <c r="DT13" s="1">
-        <f t="shared" si="51"/>
-        <v>2947.9370443316438</v>
-      </c>
-      <c r="DU13" s="1">
-        <f t="shared" si="51"/>
-        <v>2918.4576738883275</v>
-      </c>
-      <c r="DV13" s="1">
-        <f t="shared" si="51"/>
-        <v>2889.2730971494443</v>
-      </c>
-      <c r="DW13" s="1">
-        <f t="shared" si="51"/>
-        <v>2860.3803661779498</v>
-      </c>
-      <c r="DX13" s="1">
-        <f t="shared" si="51"/>
-        <v>2831.7765625161701</v>
-      </c>
-      <c r="DY13" s="1">
-        <f t="shared" si="51"/>
-        <v>2803.4587968910082</v>
-      </c>
-      <c r="DZ13" s="1">
-        <f t="shared" si="51"/>
-        <v>2775.4242089220979</v>
-      </c>
-      <c r="EA13" s="1">
-        <f t="shared" si="51"/>
-        <v>2747.669966832877</v>
-      </c>
-      <c r="EB13" s="1">
-        <f t="shared" si="51"/>
-        <v>2720.1932671645482</v>
-      </c>
-      <c r="EC13" s="1">
-        <f t="shared" si="51"/>
-        <v>2692.9913344929028</v>
-      </c>
-      <c r="ED13" s="1">
-        <f t="shared" si="51"/>
-        <v>2666.0614211479738</v>
-      </c>
-      <c r="EE13" s="1">
-        <f t="shared" si="51"/>
-        <v>2639.4008069364941</v>
-      </c>
-      <c r="EF13" s="1">
-        <f t="shared" si="51"/>
-        <v>2613.006798867129</v>
-      </c>
-      <c r="EG13" s="1">
-        <f t="shared" si="51"/>
-        <v>2586.8767308784577</v>
-      </c>
-      <c r="EH13" s="1">
-        <f t="shared" si="51"/>
-        <v>2561.0079635696729</v>
-      </c>
-      <c r="EI13" s="1">
-        <f t="shared" si="51"/>
-        <v>2535.3978839339761</v>
-      </c>
-      <c r="EJ13" s="1">
-        <f t="shared" si="51"/>
-        <v>2510.0439050946366</v>
-      </c>
-      <c r="EK13" s="1">
-        <f t="shared" si="51"/>
-        <v>2484.94346604369</v>
-      </c>
-      <c r="EL13" s="1">
-        <f t="shared" si="51"/>
-        <v>2460.094031383253</v>
-      </c>
-      <c r="EM13" s="1">
-        <f t="shared" si="51"/>
-        <v>2435.4930910694206</v>
-      </c>
-      <c r="EN13" s="1">
-        <f t="shared" si="51"/>
-        <v>2411.1381601587264</v>
-      </c>
-      <c r="EO13" s="1">
-        <f t="shared" si="51"/>
-        <v>2387.0267785571391</v>
-      </c>
-      <c r="EP13" s="1">
-        <f t="shared" si="51"/>
-        <v>2363.1565107715678</v>
-      </c>
-      <c r="EQ13" s="1">
-        <f t="shared" si="51"/>
-        <v>2339.5249456638521</v>
-      </c>
-      <c r="ER13" s="1">
-        <f t="shared" si="51"/>
-        <v>2316.1296962072138</v>
-      </c>
-      <c r="ES13" s="1">
-        <f t="shared" si="51"/>
-        <v>2292.9683992451414</v>
-      </c>
-      <c r="ET13" s="1">
-        <f t="shared" si="51"/>
-        <v>2270.0387152526901</v>
-      </c>
-      <c r="EU13" s="1">
-        <f t="shared" si="51"/>
-        <v>2247.3383281001629</v>
-      </c>
-      <c r="EV13" s="1">
-        <f t="shared" si="51"/>
-        <v>2224.8649448191613</v>
-      </c>
-      <c r="EW13" s="1">
-        <f t="shared" si="51"/>
-        <v>2202.6162953709695</v>
-      </c>
-      <c r="EX13" s="1">
-        <f t="shared" si="51"/>
-        <v>2180.5901324172596</v>
-      </c>
-      <c r="EY13" s="1">
-        <f t="shared" si="51"/>
-        <v>2158.7842310930869</v>
-      </c>
-      <c r="EZ13" s="1">
-        <f t="shared" si="51"/>
-        <v>2137.1963887821562</v>
-      </c>
-      <c r="FA13" s="1">
-        <f t="shared" si="51"/>
-        <v>2115.8244248943347</v>
-      </c>
-      <c r="FB13" s="1">
-        <f t="shared" si="51"/>
-        <v>2094.6661806453913</v>
-      </c>
-      <c r="FC13" s="1">
-        <f t="shared" si="51"/>
-        <v>2073.7195188389373</v>
-      </c>
-      <c r="FD13" s="1">
-        <f t="shared" si="51"/>
-        <v>2052.9823236505481</v>
-      </c>
-      <c r="FE13" s="1">
-        <f t="shared" si="51"/>
-        <v>2032.4525004140426</v>
-      </c>
-      <c r="FF13" s="1">
-        <f t="shared" si="51"/>
-        <v>2012.1279754099021</v>
-      </c>
-      <c r="FG13" s="1">
-        <f t="shared" si="51"/>
-        <v>1992.006695655803</v>
-      </c>
-      <c r="FH13" s="1">
-        <f t="shared" si="51"/>
-        <v>1972.086628699245</v>
-      </c>
-      <c r="FI13" s="1">
-        <f t="shared" si="51"/>
-        <v>1952.3657624122525</v>
+        <v>2041.4182860006347</v>
       </c>
     </row>
-    <row r="14" spans="2:165" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:169" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>2</v>
       </c>
@@ -3784,21 +3856,13 @@
         <v>1476</v>
       </c>
       <c r="AH14" s="5">
-        <f>1476</f>
-        <v>1476</v>
-      </c>
-      <c r="AJ14" s="5">
-        <v>1580</v>
-      </c>
-      <c r="AK14" s="5">
-        <v>1580</v>
-      </c>
-      <c r="AL14" s="5">
-        <v>1580</v>
-      </c>
-      <c r="AM14" s="5">
-        <v>1580</v>
-      </c>
+        <f>1476.9</f>
+        <v>1476.9</v>
+      </c>
+      <c r="AI14" s="5"/>
+      <c r="AJ14" s="5"/>
+      <c r="AK14" s="5"/>
+      <c r="AL14" s="5"/>
       <c r="AN14" s="5">
         <v>1580</v>
       </c>
@@ -3809,43 +3873,66 @@
         <v>1580</v>
       </c>
       <c r="AQ14" s="5">
+        <v>1580</v>
+      </c>
+      <c r="AR14" s="5">
+        <v>1580</v>
+      </c>
+      <c r="AS14" s="5">
+        <v>1580</v>
+      </c>
+      <c r="AT14" s="5">
+        <v>1580</v>
+      </c>
+      <c r="AU14" s="5">
         <v>1509.4</v>
       </c>
-      <c r="AR14" s="5">
-        <v>1508</v>
-      </c>
-      <c r="AS14" s="5">
-        <v>1508</v>
-      </c>
-      <c r="AT14" s="5">
-        <v>1508</v>
-      </c>
-      <c r="AU14" s="5">
-        <v>1508</v>
-      </c>
       <c r="AV14" s="5">
-        <v>1508</v>
+        <f t="shared" ref="AV14:BF14" si="51">1476.9</f>
+        <v>1476.9</v>
       </c>
       <c r="AW14" s="5">
-        <v>1508</v>
+        <f t="shared" si="51"/>
+        <v>1476.9</v>
       </c>
       <c r="AX14" s="5">
-        <v>1508</v>
+        <f t="shared" si="51"/>
+        <v>1476.9</v>
       </c>
       <c r="AY14" s="5">
-        <v>1508</v>
+        <f t="shared" si="51"/>
+        <v>1476.9</v>
       </c>
       <c r="AZ14" s="5">
-        <v>1508</v>
+        <f t="shared" si="51"/>
+        <v>1476.9</v>
       </c>
       <c r="BA14" s="5">
-        <v>1508</v>
+        <f t="shared" si="51"/>
+        <v>1476.9</v>
       </c>
       <c r="BB14" s="5">
-        <v>1508</v>
+        <f t="shared" si="51"/>
+        <v>1476.9</v>
+      </c>
+      <c r="BC14" s="5">
+        <f t="shared" si="51"/>
+        <v>1476.9</v>
+      </c>
+      <c r="BD14" s="5">
+        <f t="shared" si="51"/>
+        <v>1476.9</v>
+      </c>
+      <c r="BE14" s="5">
+        <f t="shared" si="51"/>
+        <v>1476.9</v>
+      </c>
+      <c r="BF14" s="5">
+        <f t="shared" si="51"/>
+        <v>1476.9</v>
       </c>
     </row>
-    <row r="15" spans="2:165" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:169" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>34</v>
       </c>
@@ -3975,86 +4062,90 @@
       </c>
       <c r="AH15" s="8">
         <f t="shared" si="59"/>
-        <v>0.77963463279132827</v>
-      </c>
-      <c r="AJ15" s="8">
-        <f>AJ13/AJ14</f>
-        <v>2.6835443037974684</v>
-      </c>
-      <c r="AK15" s="8">
-        <f>AK13/AK14</f>
-        <v>1.2240506329113925</v>
-      </c>
-      <c r="AL15" s="8">
-        <f>AL13/AL14</f>
-        <v>2.5499999999999998</v>
-      </c>
-      <c r="AM15" s="8">
-        <f>AM13/AM14</f>
-        <v>1.6069620253164556</v>
-      </c>
+        <v>0.57324124856117531</v>
+      </c>
+      <c r="AI15" s="8"/>
+      <c r="AJ15" s="8"/>
+      <c r="AK15" s="8"/>
+      <c r="AL15" s="8"/>
       <c r="AN15" s="8">
         <f>AN13/AN14</f>
+        <v>2.6835443037974684</v>
+      </c>
+      <c r="AO15" s="8">
+        <f>AO13/AO14</f>
+        <v>1.2240506329113925</v>
+      </c>
+      <c r="AP15" s="8">
+        <f>AP13/AP14</f>
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="AQ15" s="8">
+        <f>AQ13/AQ14</f>
+        <v>1.6069620253164556</v>
+      </c>
+      <c r="AR15" s="8">
+        <f>AR13/AR14</f>
         <v>3.6246835443037977</v>
       </c>
-      <c r="AO15" s="8">
-        <f t="shared" ref="AO15:AX15" si="60">AO13/AO14</f>
+      <c r="AS15" s="8">
+        <f t="shared" ref="AS15:BB15" si="60">AS13/AS14</f>
         <v>3.8265822784810126</v>
       </c>
-      <c r="AP15" s="8">
+      <c r="AT15" s="8">
         <f t="shared" si="60"/>
         <v>3.2088607594936707</v>
       </c>
-      <c r="AQ15" s="8">
+      <c r="AU15" s="8">
         <f t="shared" si="60"/>
         <v>3.7763349675367692</v>
       </c>
-      <c r="AR15" s="8">
-        <f t="shared" si="60"/>
-        <v>2.7577856220159163</v>
-      </c>
-      <c r="AS15" s="8">
-        <f t="shared" si="60"/>
-        <v>3.6121092489124664</v>
-      </c>
-      <c r="AT15" s="8">
-        <f t="shared" si="60"/>
-        <v>3.6482303414015926</v>
-      </c>
-      <c r="AU15" s="8">
-        <f t="shared" si="60"/>
-        <v>3.6847126448156096</v>
-      </c>
       <c r="AV15" s="8">
         <f t="shared" si="60"/>
-        <v>3.7215597712637649</v>
+        <v>2.1795653057079014</v>
       </c>
       <c r="AW15" s="8">
         <f t="shared" si="60"/>
-        <v>3.7587753689764014</v>
+        <v>3.0319362177534024</v>
       </c>
       <c r="AX15" s="8">
         <f t="shared" si="60"/>
-        <v>3.7963631226661656</v>
+        <v>3.6969917435168247</v>
       </c>
       <c r="AY15" s="8">
-        <f t="shared" ref="AY15:BB15" si="61">AY13/AY14</f>
-        <v>3.834326753892829</v>
+        <f t="shared" si="60"/>
+        <v>3.9339124768501588</v>
       </c>
       <c r="AZ15" s="8">
+        <f t="shared" si="60"/>
+        <v>3.9732516016186628</v>
+      </c>
+      <c r="BA15" s="8">
+        <f t="shared" si="60"/>
+        <v>4.012984117634848</v>
+      </c>
+      <c r="BB15" s="8">
+        <f t="shared" si="60"/>
+        <v>4.0531139588111973</v>
+      </c>
+      <c r="BC15" s="8">
+        <f t="shared" ref="BC15:BF15" si="61">BC13/BC14</f>
+        <v>4.0936450983993105</v>
+      </c>
+      <c r="BD15" s="8">
         <f t="shared" si="61"/>
-        <v>3.8726700214317584</v>
-      </c>
-      <c r="BA15" s="8">
+        <v>4.1345815493833031</v>
+      </c>
+      <c r="BE15" s="8">
         <f t="shared" si="61"/>
-        <v>3.9113967216460748</v>
-      </c>
-      <c r="BB15" s="8">
+        <v>4.1759273648771362</v>
+      </c>
+      <c r="BF15" s="8">
         <f t="shared" si="61"/>
-        <v>3.9505106888625354</v>
+        <v>4.2176866385259064</v>
       </c>
     </row>
-    <row r="17" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>39</v>
       </c>
@@ -4172,83 +4263,87 @@
       </c>
       <c r="AH17" s="10">
         <f t="shared" ref="AH17" si="68">AH3/AD3-1</f>
-        <v>-6.9999999999999951E-2</v>
-      </c>
+        <v>-0.11970490242741549</v>
+      </c>
+      <c r="AI17" s="10"/>
       <c r="AJ17" s="10"/>
-      <c r="AK17" s="10">
-        <f>AK3/AJ3-1</f>
+      <c r="AK17" s="10"/>
+      <c r="AL17" s="10"/>
+      <c r="AN17" s="10"/>
+      <c r="AO17" s="10">
+        <f>AO3/AN3-1</f>
         <v>5.95924308588065E-2</v>
       </c>
-      <c r="AL17" s="10">
-        <f>AL3/AK3-1</f>
+      <c r="AP17" s="10">
+        <f>AP3/AO3-1</f>
         <v>7.4731433909388079E-2</v>
       </c>
-      <c r="AM17" s="10">
-        <f t="shared" ref="AM17:AX17" si="69">AM3/AL3-1</f>
+      <c r="AQ17" s="10">
+        <f t="shared" ref="AQ17:BB17" si="69">AQ3/AP3-1</f>
         <v>-4.3817266150267153E-2</v>
       </c>
-      <c r="AN17" s="10">
+      <c r="AR17" s="10">
         <f t="shared" si="69"/>
         <v>0.19076009945726269</v>
       </c>
-      <c r="AO17" s="10">
+      <c r="AS17" s="10">
         <f t="shared" si="69"/>
         <v>4.8767344739323759E-2</v>
       </c>
-      <c r="AP17" s="10">
+      <c r="AT17" s="10">
         <f t="shared" si="69"/>
         <v>9.6488974523656568E-2</v>
       </c>
-      <c r="AQ17" s="10">
+      <c r="AU17" s="10">
         <f t="shared" si="69"/>
         <v>2.8310912392370824E-3</v>
       </c>
-      <c r="AR17" s="10">
+      <c r="AV17" s="10">
         <f t="shared" si="69"/>
-        <v>-8.618083407966981E-2</v>
-      </c>
-      <c r="AS17" s="10">
+        <v>-9.8380125384525563E-2</v>
+      </c>
+      <c r="AW17" s="10">
         <f t="shared" si="69"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AT17" s="10">
+        <v>-1.0559502472521576E-2</v>
+      </c>
+      <c r="AX17" s="10">
+        <f t="shared" si="69"/>
+        <v>4.9323439546049785E-2</v>
+      </c>
+      <c r="AY17" s="10">
+        <f t="shared" si="69"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AZ17" s="10">
         <f t="shared" si="69"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AU17" s="10">
+      <c r="BA17" s="10">
         <f t="shared" si="69"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AV17" s="10">
+      <c r="BB17" s="10">
         <f t="shared" si="69"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AW17" s="10">
-        <f t="shared" si="69"/>
+      <c r="BC17" s="10">
+        <f t="shared" ref="BC17" si="70">BC3/BB3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AX17" s="10">
-        <f t="shared" si="69"/>
+      <c r="BD17" s="10">
+        <f t="shared" ref="BD17" si="71">BD3/BC3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AY17" s="10">
-        <f t="shared" ref="AY17" si="70">AY3/AX3-1</f>
+      <c r="BE17" s="10">
+        <f t="shared" ref="BE17" si="72">BE3/BD3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AZ17" s="10">
-        <f t="shared" ref="AZ17" si="71">AZ3/AY3-1</f>
+      <c r="BF17" s="10">
+        <f t="shared" ref="BF17" si="73">BF3/BE3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BA17" s="10">
-        <f t="shared" ref="BA17" si="72">BA3/AZ3-1</f>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="BB17" s="10">
-        <f t="shared" ref="BB17" si="73">BB3/BA3-1</f>
-        <v>1.0000000000000009E-2</v>
-      </c>
     </row>
-    <row r="18" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>40</v>
       </c>
@@ -4378,86 +4473,90 @@
       </c>
       <c r="AH18" s="10">
         <f t="shared" si="82"/>
-        <v>0.46</v>
-      </c>
-      <c r="AJ18" s="10">
-        <f t="shared" ref="AJ18" si="83">AJ5/AJ3</f>
+        <v>0.45999999999999996</v>
+      </c>
+      <c r="AI18" s="10"/>
+      <c r="AJ18" s="10"/>
+      <c r="AK18" s="10"/>
+      <c r="AL18" s="10"/>
+      <c r="AN18" s="10">
+        <f t="shared" ref="AN18" si="83">AN5/AN3</f>
         <v>0.445764192139738</v>
       </c>
-      <c r="AK18" s="10">
-        <f t="shared" ref="AK18" si="84">AK5/AK3</f>
+      <c r="AO18" s="10">
+        <f t="shared" ref="AO18" si="84">AO5/AO3</f>
         <v>0.43838777921257244</v>
       </c>
-      <c r="AL18" s="10">
-        <f t="shared" ref="AL18:AX18" si="85">AL5/AL3</f>
+      <c r="AP18" s="10">
+        <f t="shared" ref="AP18:BB18" si="85">AP5/AP3</f>
         <v>0.44671114860546568</v>
       </c>
-      <c r="AM18" s="10">
+      <c r="AQ18" s="10">
         <f t="shared" si="85"/>
         <v>0.43421650669732376</v>
       </c>
-      <c r="AN18" s="10">
+      <c r="AR18" s="10">
         <f t="shared" si="85"/>
         <v>0.44820153576721</v>
       </c>
-      <c r="AO18" s="10">
+      <c r="AS18" s="10">
         <f t="shared" si="85"/>
         <v>0.45983729394134021</v>
       </c>
-      <c r="AP18" s="10">
+      <c r="AT18" s="10">
         <f t="shared" si="85"/>
         <v>0.43524610969014194</v>
       </c>
-      <c r="AQ18" s="10">
+      <c r="AU18" s="10">
         <f t="shared" si="85"/>
         <v>0.44560180678322497</v>
       </c>
-      <c r="AR18" s="10">
-        <f t="shared" si="85"/>
-        <v>0.44132504168479442</v>
-      </c>
-      <c r="AS18" s="10">
-        <f t="shared" si="85"/>
-        <v>0.45999999999999996</v>
-      </c>
-      <c r="AT18" s="10">
-        <f t="shared" si="85"/>
-        <v>0.45999999999999996</v>
-      </c>
-      <c r="AU18" s="10">
-        <f t="shared" si="85"/>
-        <v>0.46</v>
-      </c>
       <c r="AV18" s="10">
         <f t="shared" si="85"/>
-        <v>0.46</v>
+        <v>0.42734673605562634</v>
       </c>
       <c r="AW18" s="10">
         <f t="shared" si="85"/>
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="AX18" s="10">
         <f t="shared" si="85"/>
         <v>0.45999999999999996</v>
       </c>
       <c r="AY18" s="10">
-        <f t="shared" ref="AY18:BB18" si="86">AY5/AY3</f>
+        <f t="shared" si="85"/>
+        <v>0.45999999999999996</v>
+      </c>
+      <c r="AZ18" s="10">
+        <f t="shared" si="85"/>
         <v>0.46</v>
       </c>
-      <c r="AZ18" s="10">
-        <f t="shared" si="86"/>
+      <c r="BA18" s="10">
+        <f t="shared" si="85"/>
+        <v>0.46</v>
+      </c>
+      <c r="BB18" s="10">
+        <f t="shared" si="85"/>
+        <v>0.46</v>
+      </c>
+      <c r="BC18" s="10">
+        <f t="shared" ref="BC18:BF18" si="86">BC5/BC3</f>
         <v>0.46000000000000008</v>
       </c>
-      <c r="BA18" s="10">
+      <c r="BD18" s="10">
         <f t="shared" si="86"/>
         <v>0.46</v>
       </c>
-      <c r="BB18" s="10">
+      <c r="BE18" s="10">
         <f t="shared" si="86"/>
         <v>0.46</v>
       </c>
+      <c r="BF18" s="10">
+        <f t="shared" si="86"/>
+        <v>0.45999999999999996</v>
+      </c>
     </row>
-    <row r="19" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>41</v>
       </c>
@@ -4587,92 +4686,96 @@
       </c>
       <c r="AH19" s="10">
         <f t="shared" si="95"/>
-        <v>0.10924859130060957</v>
-      </c>
-      <c r="AJ19" s="10">
-        <f t="shared" ref="AJ19" si="96">AJ8/AJ3</f>
+        <v>8.6205280706497245E-2</v>
+      </c>
+      <c r="AI19" s="10"/>
+      <c r="AJ19" s="10"/>
+      <c r="AK19" s="10"/>
+      <c r="AL19" s="10"/>
+      <c r="AN19" s="10">
+        <f t="shared" ref="AN19" si="96">AN8/AN3</f>
         <v>0.13825327510917029</v>
       </c>
-      <c r="AK19" s="10">
-        <f t="shared" ref="AK19" si="97">AK8/AK3</f>
+      <c r="AO19" s="10">
+        <f t="shared" ref="AO19" si="97">AO8/AO3</f>
         <v>0.12212544989971701</v>
       </c>
-      <c r="AL19" s="10">
-        <f t="shared" ref="AL19:AX19" si="98">AL8/AL3</f>
+      <c r="AP19" s="10">
+        <f t="shared" ref="AP19:BB19" si="98">AP8/AP3</f>
         <v>0.12199299537285579</v>
       </c>
-      <c r="AM19" s="10">
+      <c r="AQ19" s="10">
         <f t="shared" si="98"/>
         <v>8.3282089671951443E-2</v>
       </c>
-      <c r="AN19" s="10">
+      <c r="AR19" s="10">
         <f t="shared" si="98"/>
         <v>0.15575463649018814</v>
       </c>
-      <c r="AO19" s="10">
+      <c r="AS19" s="10">
         <f t="shared" si="98"/>
         <v>0.14290301862556198</v>
       </c>
-      <c r="AP19" s="10">
+      <c r="AT19" s="10">
         <f t="shared" si="98"/>
         <v>0.11548899779370131</v>
       </c>
-      <c r="AQ19" s="10">
+      <c r="AU19" s="10">
         <f t="shared" si="98"/>
         <v>0.12287294108484872</v>
       </c>
-      <c r="AR19" s="10">
-        <f t="shared" si="98"/>
-        <v>9.9323042348683083E-2</v>
-      </c>
-      <c r="AS19" s="10">
-        <f t="shared" si="98"/>
-        <v>0.13092950480336715</v>
-      </c>
-      <c r="AT19" s="10">
-        <f t="shared" si="98"/>
-        <v>0.13092950480336718</v>
-      </c>
-      <c r="AU19" s="10">
-        <f t="shared" si="98"/>
-        <v>0.13092950480336724</v>
-      </c>
       <c r="AV19" s="10">
         <f t="shared" si="98"/>
-        <v>0.13092950480336721</v>
+        <v>7.9941264117126265E-2</v>
       </c>
       <c r="AW19" s="10">
         <f t="shared" si="98"/>
-        <v>0.13092950480336718</v>
+        <v>0.11370995198603231</v>
       </c>
       <c r="AX19" s="10">
         <f t="shared" si="98"/>
-        <v>0.13092950480336715</v>
+        <v>0.13293968178036603</v>
       </c>
       <c r="AY19" s="10">
-        <f t="shared" ref="AY19:BB19" si="99">AY8/AY3</f>
-        <v>0.13092950480336724</v>
+        <f t="shared" si="98"/>
+        <v>0.13754279475550457</v>
       </c>
       <c r="AZ19" s="10">
+        <f t="shared" si="98"/>
+        <v>0.13754279475550465</v>
+      </c>
+      <c r="BA19" s="10">
+        <f t="shared" si="98"/>
+        <v>0.1375427947555046</v>
+      </c>
+      <c r="BB19" s="10">
+        <f t="shared" si="98"/>
+        <v>0.13754279475550465</v>
+      </c>
+      <c r="BC19" s="10">
+        <f t="shared" ref="BC19:BF19" si="99">BC8/BC3</f>
+        <v>0.13754279475550465</v>
+      </c>
+      <c r="BD19" s="10">
         <f t="shared" si="99"/>
-        <v>0.13092950480336729</v>
-      </c>
-      <c r="BA19" s="10">
+        <v>0.13754279475550463</v>
+      </c>
+      <c r="BE19" s="10">
         <f t="shared" si="99"/>
-        <v>0.13092950480336724</v>
-      </c>
-      <c r="BB19" s="10">
+        <v>0.13754279475550465</v>
+      </c>
+      <c r="BF19" s="10">
         <f t="shared" si="99"/>
-        <v>0.13092950480336724</v>
-      </c>
-      <c r="BD19" t="s">
+        <v>0.1375427947555046</v>
+      </c>
+      <c r="BH19" t="s">
         <v>45</v>
       </c>
-      <c r="BE19" s="10">
+      <c r="BI19" s="10">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="20" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>42</v>
       </c>
@@ -4802,92 +4905,96 @@
       </c>
       <c r="AH20" s="10">
         <f t="shared" si="108"/>
-        <v>0.09</v>
-      </c>
-      <c r="AJ20" s="10">
-        <f t="shared" ref="AJ20" si="109">AJ6/AJ3</f>
+        <v>0.11291340001802289</v>
+      </c>
+      <c r="AI20" s="10"/>
+      <c r="AJ20" s="10"/>
+      <c r="AK20" s="10"/>
+      <c r="AL20" s="10"/>
+      <c r="AN20" s="10">
+        <f t="shared" ref="AN20" si="109">AN6/AN3</f>
         <v>9.726346433770014E-2</v>
       </c>
-      <c r="AK20" s="10">
-        <f t="shared" ref="AK20" si="110">AK6/AK3</f>
+      <c r="AO20" s="10">
+        <f t="shared" ref="AO20" si="110">AO6/AO3</f>
         <v>9.8277330549221095E-2</v>
       </c>
-      <c r="AL20" s="10">
-        <f t="shared" ref="AL20:AX20" si="111">AL6/AL3</f>
+      <c r="AP20" s="10">
+        <f t="shared" ref="AP20:BB20" si="111">AP6/AP3</f>
         <v>9.5942940409540614E-2</v>
       </c>
-      <c r="AM20" s="10">
+      <c r="AQ20" s="10">
         <f t="shared" si="111"/>
         <v>9.6035077400208543E-2</v>
       </c>
-      <c r="AN20" s="10">
+      <c r="AR20" s="10">
         <f t="shared" si="111"/>
         <v>6.9917822982621586E-2</v>
       </c>
-      <c r="AO20" s="10">
+      <c r="AS20" s="10">
         <f t="shared" si="111"/>
         <v>8.2423463926354093E-2</v>
       </c>
-      <c r="AP20" s="10">
+      <c r="AT20" s="10">
         <f t="shared" si="111"/>
         <v>7.9270554698635212E-2</v>
       </c>
-      <c r="AQ20" s="10">
+      <c r="AU20" s="10">
         <f t="shared" si="111"/>
         <v>8.3427436626299603E-2</v>
       </c>
-      <c r="AR20" s="10">
-        <f t="shared" si="111"/>
-        <v>9.5686943678974457E-2</v>
-      </c>
-      <c r="AS20" s="10">
-        <f t="shared" si="111"/>
-        <v>0.09</v>
-      </c>
-      <c r="AT20" s="10">
-        <f t="shared" si="111"/>
-        <v>0.09</v>
-      </c>
-      <c r="AU20" s="10">
-        <f t="shared" si="111"/>
-        <v>8.9999999999999983E-2</v>
-      </c>
       <c r="AV20" s="10">
         <f t="shared" si="111"/>
-        <v>9.0000000000000011E-2</v>
+        <v>0.10125461573344274</v>
       </c>
       <c r="AW20" s="10">
         <f t="shared" si="111"/>
-        <v>0.09</v>
+        <v>9.0000000000000011E-2</v>
       </c>
       <c r="AX20" s="10">
         <f t="shared" si="111"/>
         <v>0.09</v>
       </c>
       <c r="AY20" s="10">
-        <f t="shared" ref="AY20:BB20" si="112">AY6/AY3</f>
+        <f t="shared" si="111"/>
+        <v>8.9999999999999983E-2</v>
+      </c>
+      <c r="AZ20" s="10">
+        <f t="shared" si="111"/>
         <v>0.09</v>
       </c>
-      <c r="AZ20" s="10">
+      <c r="BA20" s="10">
+        <f t="shared" si="111"/>
+        <v>9.0000000000000011E-2</v>
+      </c>
+      <c r="BB20" s="10">
+        <f t="shared" si="111"/>
+        <v>9.0000000000000011E-2</v>
+      </c>
+      <c r="BC20" s="10">
+        <f t="shared" ref="BC20:BF20" si="112">BC6/BC3</f>
+        <v>0.09</v>
+      </c>
+      <c r="BD20" s="10">
+        <f t="shared" si="112"/>
+        <v>9.0000000000000011E-2</v>
+      </c>
+      <c r="BE20" s="10">
         <f t="shared" si="112"/>
         <v>0.09</v>
       </c>
-      <c r="BA20" s="10">
-        <f t="shared" si="112"/>
-        <v>9.0000000000000011E-2</v>
-      </c>
-      <c r="BB20" s="10">
+      <c r="BF20" s="10">
         <f t="shared" si="112"/>
         <v>0.09</v>
       </c>
-      <c r="BD20" t="s">
+      <c r="BH20" t="s">
         <v>46</v>
       </c>
-      <c r="BE20" s="10">
+      <c r="BI20" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="21" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>43</v>
       </c>
@@ -5005,90 +5112,94 @@
       </c>
       <c r="AH21" s="10">
         <f t="shared" ref="AH21" si="129">AH7/AD7-1</f>
-        <v>2.0000000000000018E-2</v>
-      </c>
+        <v>-3.4034034034034044E-2</v>
+      </c>
+      <c r="AI21" s="10"/>
       <c r="AJ21" s="10"/>
-      <c r="AK21" s="10">
-        <f t="shared" ref="AK21" si="130">AK7/AJ7-1</f>
+      <c r="AK21" s="10"/>
+      <c r="AL21" s="10"/>
+      <c r="AN21" s="10"/>
+      <c r="AO21" s="10">
+        <f t="shared" ref="AO21" si="130">AO7/AN7-1</f>
         <v>9.8587648850733789E-2</v>
       </c>
-      <c r="AL21" s="10">
-        <f t="shared" ref="AL21:AX21" si="131">AL7/AK7-1</f>
+      <c r="AP21" s="10">
+        <f t="shared" ref="AP21:BB21" si="131">AP7/AO7-1</f>
         <v>0.12793042601462057</v>
       </c>
-      <c r="AM21" s="10">
+      <c r="AQ21" s="10">
         <f t="shared" si="131"/>
         <v>6.5370432450553073E-2</v>
       </c>
-      <c r="AN21" s="10">
+      <c r="AR21" s="10">
         <f t="shared" si="131"/>
         <v>3.9542689322425106E-2</v>
       </c>
-      <c r="AO21" s="10">
+      <c r="AS21" s="10">
         <f t="shared" si="131"/>
         <v>0.10523660579154481</v>
       </c>
-      <c r="AP21" s="10">
+      <c r="AT21" s="10">
         <f t="shared" si="131"/>
         <v>0.12442943217089653</v>
       </c>
-      <c r="AQ21" s="10">
+      <c r="AU21" s="10">
         <f t="shared" si="131"/>
         <v>-2.1109036291304673E-3</v>
       </c>
-      <c r="AR21" s="10">
-        <f t="shared" si="131"/>
-        <v>-5.9397933447237761E-2</v>
-      </c>
-      <c r="AS21" s="10">
-        <f t="shared" si="131"/>
-        <v>-9.9999999999998979E-3</v>
-      </c>
-      <c r="AT21" s="10">
-        <f t="shared" si="131"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AU21" s="10">
-        <f t="shared" si="131"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="AV21" s="10">
         <f t="shared" si="131"/>
-        <v>1.0000000000000009E-2</v>
+        <v>-7.257342771133346E-2</v>
       </c>
       <c r="AW21" s="10">
         <f t="shared" si="131"/>
-        <v>1.0000000000000009E-2</v>
+        <v>-1.0000000000000009E-2</v>
       </c>
       <c r="AX21" s="10">
         <f t="shared" si="131"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY21" s="10">
-        <f t="shared" ref="AY21" si="132">AY7/AX7-1</f>
+        <f t="shared" si="131"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ21" s="10">
-        <f t="shared" ref="AZ21" si="133">AZ7/AY7-1</f>
+        <f t="shared" si="131"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BA21" s="10">
-        <f t="shared" ref="BA21" si="134">BA7/AZ7-1</f>
+        <f t="shared" si="131"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BB21" s="10">
-        <f t="shared" ref="BB21" si="135">BB7/BA7-1</f>
+        <f t="shared" si="131"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BD21" t="s">
+      <c r="BC21" s="10">
+        <f t="shared" ref="BC21" si="132">BC7/BB7-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="BD21" s="10">
+        <f t="shared" ref="BD21" si="133">BD7/BC7-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="BE21" s="10">
+        <f t="shared" ref="BE21" si="134">BE7/BD7-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="BF21" s="10">
+        <f t="shared" ref="BF21" si="135">BF7/BE7-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="BH21" t="s">
         <v>47</v>
       </c>
-      <c r="BE21" s="5">
-        <f>NPV(BE20,AR13:FI13)</f>
-        <v>76107.134822998923</v>
+      <c r="BI21" s="5">
+        <f>NPV(BI20,AV13:FM13)</f>
+        <v>77220.823409649951</v>
       </c>
     </row>
-    <row r="22" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>32</v>
       </c>
@@ -5218,59 +5329,47 @@
       </c>
       <c r="AH22" s="10">
         <f t="shared" si="144"/>
-        <v>0.17</v>
-      </c>
-      <c r="AJ22" s="10">
-        <f t="shared" ref="AJ22" si="145">AJ12/AJ11</f>
+        <v>0.11220402256664082</v>
+      </c>
+      <c r="AI22" s="10"/>
+      <c r="AJ22" s="10"/>
+      <c r="AK22" s="10"/>
+      <c r="AL22" s="10"/>
+      <c r="AN22" s="10">
+        <f t="shared" ref="AN22" si="145">AN12/AN11</f>
         <v>0.13221449038067951</v>
       </c>
-      <c r="AK22" s="10">
-        <f t="shared" ref="AK22" si="146">AK12/AK11</f>
+      <c r="AO22" s="10">
+        <f t="shared" ref="AO22" si="146">AO12/AO11</f>
         <v>0.55293573740175683</v>
       </c>
-      <c r="AL22" s="10">
-        <f t="shared" ref="AL22:AX22" si="147">AL12/AL11</f>
+      <c r="AP22" s="10">
+        <f t="shared" ref="AP22:BB22" si="147">AP12/AP11</f>
         <v>0.16079983336804832</v>
       </c>
-      <c r="AM22" s="10">
+      <c r="AQ22" s="10">
         <f t="shared" si="147"/>
         <v>0.12054035330793211</v>
       </c>
-      <c r="AN22" s="10">
+      <c r="AR22" s="10">
         <f t="shared" si="147"/>
         <v>0.14021918630836211</v>
       </c>
-      <c r="AO22" s="10">
+      <c r="AS22" s="10">
         <f t="shared" si="147"/>
         <v>9.0963764847391368E-2</v>
       </c>
-      <c r="AP22" s="10">
+      <c r="AT22" s="10">
         <f t="shared" si="147"/>
         <v>0.18238993710691823</v>
       </c>
-      <c r="AQ22" s="10">
+      <c r="AU22" s="10">
         <f t="shared" si="147"/>
         <v>0.14925373134328357</v>
       </c>
-      <c r="AR22" s="10">
-        <f t="shared" si="147"/>
-        <v>0.16043290084015641</v>
-      </c>
-      <c r="AS22" s="10">
-        <f t="shared" si="147"/>
-        <v>0.17</v>
-      </c>
-      <c r="AT22" s="10">
-        <f t="shared" si="147"/>
-        <v>0.17</v>
-      </c>
-      <c r="AU22" s="10">
-        <f t="shared" si="147"/>
-        <v>0.17</v>
-      </c>
       <c r="AV22" s="10">
         <f t="shared" si="147"/>
-        <v>0.17</v>
+        <v>0.17142857142857143</v>
       </c>
       <c r="AW22" s="10">
         <f t="shared" si="147"/>
@@ -5281,30 +5380,46 @@
         <v>0.17</v>
       </c>
       <c r="AY22" s="10">
-        <f t="shared" ref="AY22:BB22" si="148">AY12/AY11</f>
+        <f t="shared" si="147"/>
         <v>0.17</v>
       </c>
       <c r="AZ22" s="10">
+        <f t="shared" si="147"/>
+        <v>0.17</v>
+      </c>
+      <c r="BA22" s="10">
+        <f t="shared" si="147"/>
+        <v>0.17</v>
+      </c>
+      <c r="BB22" s="10">
+        <f t="shared" si="147"/>
+        <v>0.17</v>
+      </c>
+      <c r="BC22" s="10">
+        <f t="shared" ref="BC22:BF22" si="148">BC12/BC11</f>
+        <v>0.17</v>
+      </c>
+      <c r="BD22" s="10">
         <f t="shared" si="148"/>
         <v>0.17</v>
       </c>
-      <c r="BA22" s="10">
-        <f t="shared" si="148"/>
-        <v>0.17000000000000004</v>
-      </c>
-      <c r="BB22" s="10">
+      <c r="BE22" s="10">
         <f t="shared" si="148"/>
         <v>0.17</v>
       </c>
-      <c r="BD22" t="s">
+      <c r="BF22" s="10">
+        <f t="shared" si="148"/>
+        <v>0.17</v>
+      </c>
+      <c r="BH22" t="s">
         <v>48</v>
       </c>
-      <c r="BE22" s="5">
+      <c r="BI22" s="5">
         <f>Main!D8</f>
         <v>1433</v>
       </c>
     </row>
-    <row r="23" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>44</v>
       </c>
@@ -5434,125 +5549,129 @@
       </c>
       <c r="AH23" s="10">
         <f t="shared" si="157"/>
-        <v>9.8156085257233752E-2</v>
-      </c>
-      <c r="AJ23" s="10">
-        <f t="shared" ref="AJ23" si="158">AJ13/AJ3</f>
+        <v>7.6292691718482464E-2</v>
+      </c>
+      <c r="AI23" s="10"/>
+      <c r="AJ23" s="10"/>
+      <c r="AK23" s="10"/>
+      <c r="AL23" s="10"/>
+      <c r="AN23" s="10">
+        <f t="shared" ref="AN23" si="158">AN13/AN3</f>
         <v>0.12343522561863174</v>
       </c>
-      <c r="AK23" s="10">
-        <f t="shared" ref="AK23" si="159">AK13/AK3</f>
+      <c r="AO23" s="10">
+        <f t="shared" ref="AO23" si="159">AO13/AO3</f>
         <v>5.313624749292524E-2</v>
       </c>
-      <c r="AL23" s="10">
-        <f t="shared" ref="AL23:AX23" si="160">AL13/AL3</f>
+      <c r="AP23" s="10">
+        <f t="shared" ref="AP23:BB23" si="160">AP13/AP3</f>
         <v>0.10299869621903521</v>
       </c>
-      <c r="AM23" s="10">
+      <c r="AQ23" s="10">
         <f t="shared" si="160"/>
         <v>6.7882255434056085E-2</v>
       </c>
-      <c r="AN23" s="10">
+      <c r="AR23" s="10">
         <f t="shared" si="160"/>
         <v>0.12858682473393507</v>
       </c>
-      <c r="AO23" s="10">
+      <c r="AS23" s="10">
         <f t="shared" si="160"/>
         <v>0.12943695140226932</v>
       </c>
-      <c r="AP23" s="10">
+      <c r="AT23" s="10">
         <f t="shared" si="160"/>
         <v>9.8990569537458259E-2</v>
       </c>
-      <c r="AQ23" s="10">
+      <c r="AU23" s="10">
         <f t="shared" si="160"/>
         <v>0.11097698687745804</v>
       </c>
-      <c r="AR23" s="10">
-        <f t="shared" si="160"/>
-        <v>8.8605290868888839E-2</v>
-      </c>
-      <c r="AS23" s="10">
-        <f t="shared" si="160"/>
-        <v>0.11377840935739296</v>
-      </c>
-      <c r="AT23" s="10">
-        <f t="shared" si="160"/>
-        <v>0.113778409357393</v>
-      </c>
-      <c r="AU23" s="10">
-        <f t="shared" si="160"/>
-        <v>0.11377840935739304</v>
-      </c>
       <c r="AV23" s="10">
         <f t="shared" si="160"/>
-        <v>0.11377840935739301</v>
+        <v>6.9511326092120324E-2</v>
       </c>
       <c r="AW23" s="10">
         <f t="shared" si="160"/>
-        <v>0.11377840935739299</v>
+        <v>9.7727337407245748E-2</v>
       </c>
       <c r="AX23" s="10">
         <f t="shared" si="160"/>
-        <v>0.11377840935739297</v>
+        <v>0.11356254380199665</v>
       </c>
       <c r="AY23" s="10">
-        <f t="shared" ref="AY23:BB23" si="161">AY13/AY3</f>
-        <v>0.11377840935739303</v>
+        <f t="shared" si="160"/>
+        <v>0.11732055266021033</v>
       </c>
       <c r="AZ23" s="10">
+        <f t="shared" si="160"/>
+        <v>0.11732055266021038</v>
+      </c>
+      <c r="BA23" s="10">
+        <f t="shared" si="160"/>
+        <v>0.11732055266021034</v>
+      </c>
+      <c r="BB23" s="10">
+        <f t="shared" si="160"/>
+        <v>0.11732055266021037</v>
+      </c>
+      <c r="BC23" s="10">
+        <f t="shared" ref="BC23:BF23" si="161">BC13/BC3</f>
+        <v>0.11732055266021038</v>
+      </c>
+      <c r="BD23" s="10">
         <f t="shared" si="161"/>
-        <v>0.11377840935739306</v>
-      </c>
-      <c r="BA23" s="10">
+        <v>0.11732055266021037</v>
+      </c>
+      <c r="BE23" s="10">
         <f t="shared" si="161"/>
-        <v>0.11377840935739304</v>
-      </c>
-      <c r="BB23" s="10">
+        <v>0.11732055266021038</v>
+      </c>
+      <c r="BF23" s="10">
         <f t="shared" si="161"/>
-        <v>0.11377840935739303</v>
-      </c>
-      <c r="BD23" t="s">
+        <v>0.11732055266021035</v>
+      </c>
+      <c r="BH23" t="s">
         <v>49</v>
       </c>
-      <c r="BE23" s="5">
-        <f>BE21+BE22</f>
-        <v>77540.134822998923</v>
+      <c r="BI23" s="5">
+        <f>BI21+BI22</f>
+        <v>78653.823409649951</v>
       </c>
     </row>
-    <row r="24" spans="2:57" x14ac:dyDescent="0.3">
-      <c r="BD24" t="s">
+    <row r="24" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="BH24" t="s">
         <v>51</v>
       </c>
-      <c r="BE24" s="6">
-        <f>BE23/AX14</f>
-        <v>51.419187548407777</v>
+      <c r="BI24" s="6">
+        <f>BI23/BB14</f>
+        <v>53.256025059008699</v>
       </c>
     </row>
-    <row r="25" spans="2:57" x14ac:dyDescent="0.3">
-      <c r="BD25" t="s">
+    <row r="25" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="BH25" t="s">
         <v>50</v>
       </c>
-      <c r="BE25" s="6">
+      <c r="BI25" s="6">
         <f>Main!D3</f>
-        <v>58.29</v>
+        <v>74.23</v>
       </c>
     </row>
-    <row r="26" spans="2:57" x14ac:dyDescent="0.3">
-      <c r="BD26" s="1" t="s">
+    <row r="26" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="BH26" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BE26" s="11">
-        <f>BE24/BE25-1</f>
-        <v>-0.11787291905287733</v>
+      <c r="BI26" s="11">
+        <f>BI24/BI25-1</f>
+        <v>-0.28255388577382867</v>
       </c>
     </row>
-    <row r="27" spans="2:57" x14ac:dyDescent="0.3">
-      <c r="BD27" t="s">
+    <row r="27" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="BH27" t="s">
         <v>53</v>
       </c>
-      <c r="BE27" s="7" t="s">
-        <v>70</v>
+      <c r="BI27" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/NKE.xlsx
+++ b/Financial Analysis/NKE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA916C6-11FF-4EC0-93A3-6F5C463100E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12977B67-1E0E-4644-837F-B8DD35C138CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{979F10BC-B7A7-4127-A37D-ADC4ED82FE8E}"/>
   </bookViews>
@@ -311,7 +311,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -330,6 +330,7 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -351,14 +352,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>99060</xdr:rowOff>
     </xdr:to>
@@ -375,7 +376,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25024080" y="7620"/>
+          <a:off x="25740360" y="7620"/>
           <a:ext cx="0" cy="6126480"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -401,14 +402,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
@@ -425,7 +426,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="30533340" y="0"/>
+          <a:off x="35044380" y="0"/>
           <a:ext cx="0" cy="6126480"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -774,17 +775,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="6">
-        <v>74.23</v>
+        <v>74.84</v>
       </c>
       <c r="E3" s="4">
-        <v>45909</v>
+        <v>45932</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45909</v>
+        <v>45932</v>
       </c>
       <c r="G3" s="4">
-        <v>45930</v>
+        <v>46009</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -792,11 +793,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <f>1476.9</f>
-        <v>1476.9</v>
+        <f>1478.2</f>
+        <v>1478.2</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -805,7 +806,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>109630.28700000001</v>
+        <v>110628.48800000001</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -813,11 +814,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <f>8601+1792</f>
-        <v>10393</v>
+        <f>7024+1551</f>
+        <v>8575</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -825,11 +826,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="5">
-        <f>1000+4+7956</f>
-        <v>8960</v>
+        <f>4+7996</f>
+        <v>8000</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -838,7 +839,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>1433</v>
+        <v>575</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -847,7 +848,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>108197.28700000001</v>
+        <v>110053.48800000001</v>
       </c>
     </row>
   </sheetData>
@@ -1304,10 +1305,21 @@
         <f>AV3-AG3-AF3-AE3</f>
         <v>11097</v>
       </c>
-      <c r="AI3" s="9"/>
-      <c r="AJ3" s="9"/>
-      <c r="AK3" s="9"/>
-      <c r="AL3" s="9"/>
+      <c r="AI3" s="9">
+        <v>11720</v>
+      </c>
+      <c r="AJ3" s="9">
+        <f>AF3*1.01</f>
+        <v>12477.54</v>
+      </c>
+      <c r="AK3" s="9">
+        <f t="shared" ref="AK3:AL3" si="0">AG3*1.02</f>
+        <v>11494.380000000001</v>
+      </c>
+      <c r="AL3" s="9">
+        <f t="shared" si="0"/>
+        <v>11318.94</v>
+      </c>
       <c r="AN3" s="9">
         <v>34350</v>
       </c>
@@ -1343,42 +1355,43 @@
         <v>46309</v>
       </c>
       <c r="AW3" s="9">
-        <v>45820</v>
+        <f>SUM(AI3:AL3)</f>
+        <v>47010.86</v>
       </c>
       <c r="AX3" s="9">
-        <v>48080</v>
+        <v>49110</v>
       </c>
       <c r="AY3" s="9">
         <f>AX3*1.03</f>
-        <v>49522.400000000001</v>
+        <v>50583.3</v>
       </c>
       <c r="AZ3" s="9">
-        <f t="shared" ref="AZ3:BF3" si="0">AY3*1.01</f>
-        <v>50017.624000000003</v>
+        <f t="shared" ref="AZ3:BF3" si="1">AY3*1.01</f>
+        <v>51089.133000000002</v>
       </c>
       <c r="BA3" s="9">
-        <f t="shared" si="0"/>
-        <v>50517.800240000004</v>
+        <f t="shared" si="1"/>
+        <v>51600.02433</v>
       </c>
       <c r="BB3" s="9">
-        <f t="shared" si="0"/>
-        <v>51022.978242400008</v>
+        <f t="shared" si="1"/>
+        <v>52116.024573299997</v>
       </c>
       <c r="BC3" s="9">
-        <f t="shared" si="0"/>
-        <v>51533.208024824009</v>
+        <f t="shared" si="1"/>
+        <v>52637.184819032998</v>
       </c>
       <c r="BD3" s="9">
-        <f t="shared" si="0"/>
-        <v>52048.54010507225</v>
+        <f t="shared" si="1"/>
+        <v>53163.556667223325</v>
       </c>
       <c r="BE3" s="9">
-        <f t="shared" si="0"/>
-        <v>52569.025506122976</v>
+        <f t="shared" si="1"/>
+        <v>53695.192233895556</v>
       </c>
       <c r="BF3" s="9">
-        <f t="shared" si="0"/>
-        <v>53094.715761184205</v>
+        <f t="shared" si="1"/>
+        <v>54232.144156234514</v>
       </c>
     </row>
     <row r="4" spans="2:169" x14ac:dyDescent="0.3">
@@ -1482,10 +1495,21 @@
         <f>AV4-AG4-AF4-AE4</f>
         <v>6628</v>
       </c>
-      <c r="AI4" s="5"/>
-      <c r="AJ4" s="5"/>
-      <c r="AK4" s="5"/>
-      <c r="AL4" s="5"/>
+      <c r="AI4" s="5">
+        <v>6777</v>
+      </c>
+      <c r="AJ4" s="5">
+        <f>AJ3-AJ5</f>
+        <v>7112.1978000000008</v>
+      </c>
+      <c r="AK4" s="5">
+        <f t="shared" ref="AK4:AL4" si="2">AK3-AK5</f>
+        <v>6436.8528000000006</v>
+      </c>
+      <c r="AL4" s="5">
+        <f t="shared" si="2"/>
+        <v>6225.4170000000004</v>
+      </c>
       <c r="AN4" s="5">
         <v>19038</v>
       </c>
@@ -1520,45 +1544,45 @@
       <c r="AV4" s="5">
         <v>26519</v>
       </c>
-      <c r="AW4" s="5">
-        <f t="shared" ref="AW4:BB4" si="1">AW3-AW5</f>
-        <v>25201</v>
+      <c r="AW4" s="12">
+        <f>SUM(AI4:AL4)</f>
+        <v>26551.467600000004</v>
       </c>
       <c r="AX4" s="5">
-        <f t="shared" si="1"/>
-        <v>25963.200000000001</v>
+        <f t="shared" ref="AW4:BB4" si="3">AX3-AX5</f>
+        <v>27010.5</v>
       </c>
       <c r="AY4" s="5">
-        <f t="shared" si="1"/>
-        <v>26742.096000000001</v>
+        <f t="shared" si="3"/>
+        <v>27314.982</v>
       </c>
       <c r="AZ4" s="5">
-        <f t="shared" si="1"/>
-        <v>27009.516960000001</v>
+        <f t="shared" si="3"/>
+        <v>27588.131819999999</v>
       </c>
       <c r="BA4" s="5">
-        <f t="shared" si="1"/>
-        <v>27279.612129600002</v>
+        <f t="shared" si="3"/>
+        <v>27864.0131382</v>
       </c>
       <c r="BB4" s="5">
-        <f t="shared" si="1"/>
-        <v>27552.408250896002</v>
+        <f t="shared" si="3"/>
+        <v>28142.653269581999</v>
       </c>
       <c r="BC4" s="5">
-        <f t="shared" ref="BC4:BF4" si="2">BC3-BC5</f>
-        <v>27827.932333404962</v>
+        <f t="shared" ref="BC4:BF4" si="4">BC3-BC5</f>
+        <v>28424.079802277818</v>
       </c>
       <c r="BD4" s="5">
-        <f t="shared" si="2"/>
-        <v>28106.211656739015</v>
+        <f t="shared" si="4"/>
+        <v>28708.320600300594</v>
       </c>
       <c r="BE4" s="5">
-        <f t="shared" si="2"/>
-        <v>28387.273773306406</v>
+        <f t="shared" si="4"/>
+        <v>28995.403806303599</v>
       </c>
       <c r="BF4" s="5">
-        <f t="shared" si="2"/>
-        <v>28671.146511039471</v>
+        <f t="shared" si="4"/>
+        <v>29285.357844366637</v>
       </c>
     </row>
     <row r="5" spans="2:169" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1566,137 +1590,149 @@
         <v>25</v>
       </c>
       <c r="C5" s="9">
-        <f t="shared" ref="C5:S5" si="3">C3-C4</f>
+        <f t="shared" ref="C5:S5" si="5">C3-C4</f>
         <v>3962</v>
       </c>
       <c r="D5" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3678</v>
       </c>
       <c r="E5" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3938</v>
       </c>
       <c r="F5" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4378</v>
       </c>
       <c r="G5" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4397</v>
       </c>
       <c r="H5" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4105</v>
       </c>
       <c r="I5" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4339</v>
       </c>
       <c r="J5" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4633</v>
       </c>
       <c r="K5" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4871</v>
       </c>
       <c r="L5" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4544</v>
       </c>
       <c r="M5" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4473</v>
       </c>
       <c r="N5" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2353</v>
       </c>
       <c r="O5" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4741</v>
       </c>
       <c r="P5" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4847</v>
       </c>
       <c r="Q5" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4719</v>
       </c>
       <c r="R5" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5655</v>
       </c>
       <c r="S5" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5696</v>
       </c>
       <c r="T5" s="9">
-        <f t="shared" ref="T5:U5" si="4">T3-T4</f>
+        <f t="shared" ref="T5:U5" si="6">T3-T4</f>
         <v>5213</v>
       </c>
       <c r="U5" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>5067</v>
       </c>
       <c r="V5" s="9">
-        <f t="shared" ref="V5:W5" si="5">V3-V4</f>
+        <f t="shared" ref="V5:W5" si="7">V3-V4</f>
         <v>5503</v>
       </c>
       <c r="W5" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5615</v>
       </c>
       <c r="X5" s="9">
-        <f t="shared" ref="X5" si="6">X3-X4</f>
+        <f t="shared" ref="X5" si="8">X3-X4</f>
         <v>5711</v>
       </c>
       <c r="Y5" s="9">
-        <f t="shared" ref="Y5:AA5" si="7">Y3-Y4</f>
+        <f t="shared" ref="Y5:AA5" si="9">Y3-Y4</f>
         <v>5371</v>
       </c>
       <c r="Z5" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>5595</v>
       </c>
       <c r="AA5" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>5720</v>
       </c>
       <c r="AB5" s="9">
-        <f t="shared" ref="AB5" si="8">AB3-AB4</f>
+        <f t="shared" ref="AB5" si="10">AB3-AB4</f>
         <v>5971</v>
       </c>
       <c r="AC5" s="9">
-        <f t="shared" ref="AC5:AG5" si="9">AC3-AC4</f>
+        <f t="shared" ref="AC5:AH5" si="11">AC3-AC4</f>
         <v>5562</v>
       </c>
       <c r="AD5" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>5634</v>
       </c>
       <c r="AE5" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>5257</v>
       </c>
       <c r="AF5" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>5389</v>
       </c>
       <c r="AG5" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>4675</v>
       </c>
       <c r="AH5" s="9">
-        <f>AH3*0.46</f>
-        <v>5104.62</v>
-      </c>
-      <c r="AI5" s="9"/>
-      <c r="AJ5" s="9"/>
-      <c r="AK5" s="9"/>
-      <c r="AL5" s="9"/>
+        <f t="shared" si="11"/>
+        <v>4469</v>
+      </c>
+      <c r="AI5" s="9">
+        <f t="shared" ref="AI5" si="12">AI3-AI4</f>
+        <v>4943</v>
+      </c>
+      <c r="AJ5" s="9">
+        <f>AJ3*0.43</f>
+        <v>5365.3422</v>
+      </c>
+      <c r="AK5" s="9">
+        <f>AK3*0.44</f>
+        <v>5057.5272000000004</v>
+      </c>
+      <c r="AL5" s="9">
+        <f>AL3*0.45</f>
+        <v>5093.5230000000001</v>
+      </c>
       <c r="AN5" s="9">
         <f>AN3-AN4</f>
         <v>15312</v>
@@ -1718,60 +1754,60 @@
         <v>19962</v>
       </c>
       <c r="AS5" s="9">
-        <f t="shared" ref="AS5:AV5" si="10">AS3-AS4</f>
+        <f t="shared" ref="AS5:AW5" si="13">AS3-AS4</f>
         <v>21479</v>
       </c>
       <c r="AT5" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>22292</v>
       </c>
       <c r="AU5" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>22887</v>
       </c>
       <c r="AV5" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>19790</v>
       </c>
       <c r="AW5" s="9">
-        <f>AW3*0.45</f>
-        <v>20619</v>
+        <f t="shared" si="13"/>
+        <v>20459.392399999997</v>
       </c>
       <c r="AX5" s="9">
-        <f t="shared" ref="AX5:BF5" si="11">AX3*0.46</f>
-        <v>22116.799999999999</v>
+        <f>AX3*0.45</f>
+        <v>22099.5</v>
       </c>
       <c r="AY5" s="9">
-        <f t="shared" si="11"/>
-        <v>22780.304</v>
+        <f t="shared" ref="AX5:BF5" si="14">AY3*0.46</f>
+        <v>23268.318000000003</v>
       </c>
       <c r="AZ5" s="9">
-        <f t="shared" si="11"/>
-        <v>23008.107040000003</v>
+        <f t="shared" si="14"/>
+        <v>23501.001180000003</v>
       </c>
       <c r="BA5" s="9">
-        <f t="shared" si="11"/>
-        <v>23238.188110400002</v>
+        <f t="shared" si="14"/>
+        <v>23736.0111918</v>
       </c>
       <c r="BB5" s="9">
-        <f t="shared" si="11"/>
-        <v>23470.569991504006</v>
+        <f t="shared" si="14"/>
+        <v>23973.371303717999</v>
       </c>
       <c r="BC5" s="9">
-        <f t="shared" si="11"/>
-        <v>23705.275691419047</v>
+        <f t="shared" si="14"/>
+        <v>24213.10501675518</v>
       </c>
       <c r="BD5" s="9">
-        <f t="shared" si="11"/>
-        <v>23942.328448333235</v>
+        <f t="shared" si="14"/>
+        <v>24455.236066922731</v>
       </c>
       <c r="BE5" s="9">
-        <f t="shared" si="11"/>
-        <v>24181.75173281657</v>
+        <f t="shared" si="14"/>
+        <v>24699.788427591957</v>
       </c>
       <c r="BF5" s="9">
-        <f t="shared" si="11"/>
-        <v>24423.569250144734</v>
+        <f t="shared" si="14"/>
+        <v>24946.786311867876</v>
       </c>
     </row>
     <row r="6" spans="2:169" x14ac:dyDescent="0.3">
@@ -1872,13 +1908,24 @@
         <v>1088</v>
       </c>
       <c r="AH6" s="5">
-        <f t="shared" ref="AH6:AH7" si="12">AV6-AG6-AF6-AE6</f>
+        <f t="shared" ref="AH6:AI7" si="15">AV6-AG6-AF6-AE6</f>
         <v>1253</v>
       </c>
-      <c r="AI6" s="5"/>
-      <c r="AJ6" s="5"/>
-      <c r="AK6" s="5"/>
-      <c r="AL6" s="5"/>
+      <c r="AI6" s="5">
+        <v>1188</v>
+      </c>
+      <c r="AJ6" s="5">
+        <f>AJ3*0.1</f>
+        <v>1247.7540000000001</v>
+      </c>
+      <c r="AK6" s="5">
+        <f t="shared" ref="AK6:AL6" si="16">AK3*0.1</f>
+        <v>1149.4380000000001</v>
+      </c>
+      <c r="AL6" s="5">
+        <f t="shared" si="16"/>
+        <v>1131.894</v>
+      </c>
       <c r="AN6" s="5">
         <v>3341</v>
       </c>
@@ -1913,45 +1960,45 @@
       <c r="AV6" s="5">
         <v>4689</v>
       </c>
-      <c r="AW6" s="5">
-        <f>AW3*0.09</f>
-        <v>4123.8</v>
+      <c r="AW6" s="12">
+        <f t="shared" ref="AW6:AW7" si="17">SUM(AI6:AL6)</f>
+        <v>4717.0860000000002</v>
       </c>
       <c r="AX6" s="5">
-        <f t="shared" ref="AX6:BF6" si="13">AX3*0.09</f>
-        <v>4327.2</v>
+        <f t="shared" ref="AX6:BF6" si="18">AX3*0.09</f>
+        <v>4419.8999999999996</v>
       </c>
       <c r="AY6" s="5">
-        <f t="shared" si="13"/>
-        <v>4457.0159999999996</v>
+        <f t="shared" si="18"/>
+        <v>4552.4970000000003</v>
       </c>
       <c r="AZ6" s="5">
-        <f t="shared" si="13"/>
-        <v>4501.5861599999998</v>
+        <f t="shared" si="18"/>
+        <v>4598.0219699999998</v>
       </c>
       <c r="BA6" s="5">
-        <f t="shared" si="13"/>
-        <v>4546.6020216000006</v>
+        <f t="shared" si="18"/>
+        <v>4644.0021896999997</v>
       </c>
       <c r="BB6" s="5">
-        <f t="shared" si="13"/>
-        <v>4592.0680418160009</v>
+        <f t="shared" si="18"/>
+        <v>4690.4422115969992</v>
       </c>
       <c r="BC6" s="5">
-        <f t="shared" si="13"/>
-        <v>4637.9887222341604</v>
+        <f t="shared" si="18"/>
+        <v>4737.3466337129694</v>
       </c>
       <c r="BD6" s="5">
-        <f t="shared" si="13"/>
-        <v>4684.3686094565028</v>
+        <f t="shared" si="18"/>
+        <v>4784.7201000500991</v>
       </c>
       <c r="BE6" s="5">
-        <f t="shared" si="13"/>
-        <v>4731.2122955510677</v>
+        <f t="shared" si="18"/>
+        <v>4832.5673010505998</v>
       </c>
       <c r="BF6" s="5">
-        <f t="shared" si="13"/>
-        <v>4778.5244185065785</v>
+        <f t="shared" si="18"/>
+        <v>4880.8929740611056</v>
       </c>
     </row>
     <row r="7" spans="2:169" x14ac:dyDescent="0.3">
@@ -2052,13 +2099,24 @@
         <v>2799</v>
       </c>
       <c r="AH7" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2895</v>
       </c>
-      <c r="AI7" s="5"/>
-      <c r="AJ7" s="5"/>
-      <c r="AK7" s="5"/>
-      <c r="AL7" s="5"/>
+      <c r="AI7" s="5">
+        <v>2828</v>
+      </c>
+      <c r="AJ7" s="5">
+        <f>AF7*1.01</f>
+        <v>2911.83</v>
+      </c>
+      <c r="AK7" s="5">
+        <f t="shared" ref="AK7:AL7" si="19">AG7*1.01</f>
+        <v>2826.9900000000002</v>
+      </c>
+      <c r="AL7" s="5">
+        <f t="shared" si="19"/>
+        <v>2923.95</v>
+      </c>
       <c r="AN7" s="5">
         <v>7222</v>
       </c>
@@ -2093,45 +2151,45 @@
       <c r="AV7" s="5">
         <v>11399</v>
       </c>
-      <c r="AW7" s="5">
-        <f>AV7*0.99</f>
-        <v>11285.01</v>
+      <c r="AW7" s="12">
+        <f t="shared" si="17"/>
+        <v>11490.77</v>
       </c>
       <c r="AX7" s="5">
         <f>AW7*1.01</f>
-        <v>11397.8601</v>
+        <v>11605.6777</v>
       </c>
       <c r="AY7" s="5">
         <f>AX7*1.01</f>
-        <v>11511.838701000001</v>
+        <v>11721.734477</v>
       </c>
       <c r="AZ7" s="5">
-        <f t="shared" ref="AZ7:BF7" si="14">AY7*1.01</f>
-        <v>11626.95708801</v>
+        <f t="shared" ref="AZ7:BF7" si="20">AY7*1.01</f>
+        <v>11838.951821770001</v>
       </c>
       <c r="BA7" s="5">
-        <f t="shared" si="14"/>
-        <v>11743.2266588901</v>
+        <f t="shared" si="20"/>
+        <v>11957.341339987701</v>
       </c>
       <c r="BB7" s="5">
-        <f t="shared" si="14"/>
-        <v>11860.658925479001</v>
+        <f t="shared" si="20"/>
+        <v>12076.914753387578</v>
       </c>
       <c r="BC7" s="5">
-        <f t="shared" si="14"/>
-        <v>11979.265514733792</v>
+        <f t="shared" si="20"/>
+        <v>12197.683900921455</v>
       </c>
       <c r="BD7" s="5">
-        <f t="shared" si="14"/>
-        <v>12099.058169881129</v>
+        <f t="shared" si="20"/>
+        <v>12319.660739930669</v>
       </c>
       <c r="BE7" s="5">
-        <f t="shared" si="14"/>
-        <v>12220.048751579941</v>
+        <f t="shared" si="20"/>
+        <v>12442.857347329975</v>
       </c>
       <c r="BF7" s="5">
-        <f t="shared" si="14"/>
-        <v>12342.249239095741</v>
+        <f t="shared" si="20"/>
+        <v>12567.285920803275</v>
       </c>
     </row>
     <row r="8" spans="2:169" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2139,137 +2197,149 @@
         <v>28</v>
       </c>
       <c r="C8" s="9">
-        <f t="shared" ref="C8:S8" si="15">C5-C6-C7</f>
+        <f t="shared" ref="C8:S8" si="21">C5-C6-C7</f>
         <v>1106</v>
       </c>
       <c r="D8" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>910</v>
       </c>
       <c r="E8" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>1171</v>
       </c>
       <c r="F8" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>1258</v>
       </c>
       <c r="G8" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>1334</v>
       </c>
       <c r="H8" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>963</v>
       </c>
       <c r="I8" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>1248</v>
       </c>
       <c r="J8" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>1227</v>
       </c>
       <c r="K8" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>1543</v>
       </c>
       <c r="L8" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>1220</v>
       </c>
       <c r="M8" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>1190</v>
       </c>
       <c r="N8" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>-838</v>
       </c>
       <c r="O8" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>1766</v>
       </c>
       <c r="P8" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>1580</v>
       </c>
       <c r="Q8" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>1678</v>
       </c>
       <c r="R8" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>1913</v>
       </c>
       <c r="S8" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>2124</v>
       </c>
       <c r="T8" s="9">
-        <f t="shared" ref="T8:U8" si="16">T5-T6-T7</f>
+        <f t="shared" ref="T8:U8" si="22">T5-T6-T7</f>
         <v>1454</v>
       </c>
       <c r="U8" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>1629</v>
       </c>
       <c r="V8" s="9">
-        <f t="shared" ref="V8:W8" si="17">V5-V6-V7</f>
+        <f t="shared" ref="V8:W8" si="23">V5-V6-V7</f>
         <v>1468</v>
       </c>
       <c r="W8" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>1695</v>
       </c>
       <c r="X8" s="9">
-        <f t="shared" ref="X8" si="18">X5-X6-X7</f>
+        <f t="shared" ref="X8" si="24">X5-X6-X7</f>
         <v>1587</v>
       </c>
       <c r="Y8" s="9">
-        <f t="shared" ref="Y8:AA8" si="19">Y5-Y6-Y7</f>
+        <f t="shared" ref="Y8:AA8" si="25">Y5-Y6-Y7</f>
         <v>1412</v>
       </c>
       <c r="Z8" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1221</v>
       </c>
       <c r="AA8" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1604</v>
       </c>
       <c r="AB8" s="9">
-        <f t="shared" ref="AB8" si="20">AB5-AB6-AB7</f>
+        <f t="shared" ref="AB8" si="26">AB5-AB6-AB7</f>
         <v>1825</v>
       </c>
       <c r="AC8" s="9">
-        <f t="shared" ref="AC8:AD8" si="21">AC5-AC6-AC7</f>
+        <f t="shared" ref="AC8:AD8" si="27">AC5-AC6-AC7</f>
         <v>1336</v>
       </c>
       <c r="AD8" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>1546</v>
       </c>
       <c r="AE8" s="9">
-        <f t="shared" ref="AE8:AH8" si="22">AE5-AE6-AE7</f>
+        <f t="shared" ref="AE8:AH8" si="28">AE5-AE6-AE7</f>
         <v>1209</v>
       </c>
       <c r="AF8" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>1384</v>
       </c>
       <c r="AG8" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>788</v>
       </c>
       <c r="AH8" s="9">
-        <f t="shared" si="22"/>
-        <v>956.61999999999989</v>
-      </c>
-      <c r="AI8" s="9"/>
-      <c r="AJ8" s="9"/>
-      <c r="AK8" s="9"/>
-      <c r="AL8" s="9"/>
+        <f t="shared" si="28"/>
+        <v>321</v>
+      </c>
+      <c r="AI8" s="9">
+        <f t="shared" ref="AI8:AL8" si="29">AI5-AI6-AI7</f>
+        <v>927</v>
+      </c>
+      <c r="AJ8" s="9">
+        <f t="shared" si="29"/>
+        <v>1205.7582000000002</v>
+      </c>
+      <c r="AK8" s="9">
+        <f t="shared" si="29"/>
+        <v>1081.0992000000001</v>
+      </c>
+      <c r="AL8" s="9">
+        <f t="shared" si="29"/>
+        <v>1037.6790000000001</v>
+      </c>
       <c r="AN8" s="9">
         <f>AN5-AN6-AN7</f>
         <v>4749</v>
@@ -2291,60 +2361,60 @@
         <v>6937</v>
       </c>
       <c r="AS8" s="9">
-        <f t="shared" ref="AS8:BB8" si="23">AS5-AS6-AS7</f>
+        <f t="shared" ref="AS8:BB8" si="30">AS5-AS6-AS7</f>
         <v>6675</v>
       </c>
       <c r="AT8" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>5915</v>
       </c>
       <c r="AU8" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>6311</v>
       </c>
       <c r="AV8" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>3702</v>
       </c>
       <c r="AW8" s="9">
-        <f t="shared" si="23"/>
-        <v>5210.1900000000005</v>
+        <f t="shared" si="30"/>
+        <v>4251.5363999999972</v>
       </c>
       <c r="AX8" s="9">
-        <f t="shared" si="23"/>
-        <v>6391.7398999999987</v>
+        <f t="shared" si="30"/>
+        <v>6073.9222999999984</v>
       </c>
       <c r="AY8" s="9">
-        <f t="shared" si="23"/>
-        <v>6811.4492989999999</v>
+        <f t="shared" si="30"/>
+        <v>6994.0865230000036</v>
       </c>
       <c r="AZ8" s="9">
-        <f t="shared" si="23"/>
-        <v>6879.5637919900037</v>
+        <f t="shared" si="30"/>
+        <v>7064.0273882300044</v>
       </c>
       <c r="BA8" s="9">
-        <f t="shared" si="23"/>
-        <v>6948.3594299099022</v>
+        <f t="shared" si="30"/>
+        <v>7134.6676621122988</v>
       </c>
       <c r="BB8" s="9">
-        <f t="shared" si="23"/>
-        <v>7017.8430242090035</v>
+        <f t="shared" si="30"/>
+        <v>7206.0143387334192</v>
       </c>
       <c r="BC8" s="9">
-        <f t="shared" ref="BC8:BF8" si="24">BC5-BC6-BC7</f>
-        <v>7088.0214544510945</v>
+        <f t="shared" ref="BC8:BF8" si="31">BC5-BC6-BC7</f>
+        <v>7278.0744821207572</v>
       </c>
       <c r="BD8" s="9">
-        <f t="shared" si="24"/>
-        <v>7158.9016689956043</v>
+        <f t="shared" si="31"/>
+        <v>7350.8552269419652</v>
       </c>
       <c r="BE8" s="9">
-        <f t="shared" si="24"/>
-        <v>7230.4906856855614</v>
+        <f t="shared" si="31"/>
+        <v>7424.3637792113823</v>
       </c>
       <c r="BF8" s="9">
-        <f t="shared" si="24"/>
-        <v>7302.7955925424139</v>
+        <f t="shared" si="31"/>
+        <v>7498.6074170034954</v>
       </c>
     </row>
     <row r="9" spans="2:169" x14ac:dyDescent="0.3">
@@ -2445,13 +2515,21 @@
         <v>-18</v>
       </c>
       <c r="AH9" s="5">
-        <f t="shared" ref="AH9:AH10" si="25">AV9-AG9-AF9-AE9</f>
+        <f t="shared" ref="AH9:AI10" si="32">AV9-AG9-AF9-AE9</f>
         <v>-22</v>
       </c>
-      <c r="AI9" s="5"/>
-      <c r="AJ9" s="5"/>
-      <c r="AK9" s="5"/>
-      <c r="AL9" s="5"/>
+      <c r="AI9" s="5">
+        <v>-18</v>
+      </c>
+      <c r="AJ9" s="5">
+        <v>-20</v>
+      </c>
+      <c r="AK9" s="5">
+        <v>-20</v>
+      </c>
+      <c r="AL9" s="5">
+        <v>-20</v>
+      </c>
       <c r="AN9" s="5">
         <v>59</v>
       </c>
@@ -2486,45 +2564,45 @@
       <c r="AV9" s="5">
         <v>-107</v>
       </c>
-      <c r="AW9" s="5">
-        <f t="shared" ref="AW9:BF9" si="26">AV9*1.01</f>
-        <v>-108.07000000000001</v>
+      <c r="AW9" s="12">
+        <f t="shared" ref="AW9:AW10" si="33">SUM(AI9:AL9)</f>
+        <v>-78</v>
       </c>
       <c r="AX9" s="5">
-        <f t="shared" si="26"/>
-        <v>-109.15070000000001</v>
+        <f t="shared" ref="AW9:BF9" si="34">AW9*1.01</f>
+        <v>-78.78</v>
       </c>
       <c r="AY9" s="5">
-        <f t="shared" si="26"/>
-        <v>-110.24220700000002</v>
+        <f t="shared" si="34"/>
+        <v>-79.567800000000005</v>
       </c>
       <c r="AZ9" s="5">
-        <f t="shared" si="26"/>
-        <v>-111.34462907000002</v>
+        <f t="shared" si="34"/>
+        <v>-80.363478000000001</v>
       </c>
       <c r="BA9" s="5">
-        <f t="shared" si="26"/>
-        <v>-112.45807536070002</v>
+        <f t="shared" si="34"/>
+        <v>-81.167112779999997</v>
       </c>
       <c r="BB9" s="5">
-        <f t="shared" si="26"/>
-        <v>-113.58265611430703</v>
+        <f t="shared" si="34"/>
+        <v>-81.978783907799993</v>
       </c>
       <c r="BC9" s="5">
-        <f t="shared" si="26"/>
-        <v>-114.7184826754501</v>
+        <f t="shared" si="34"/>
+        <v>-82.798571746877997</v>
       </c>
       <c r="BD9" s="5">
-        <f t="shared" si="26"/>
-        <v>-115.8656675022046</v>
+        <f t="shared" si="34"/>
+        <v>-83.626557464346774</v>
       </c>
       <c r="BE9" s="5">
-        <f t="shared" si="26"/>
-        <v>-117.02432417722665</v>
+        <f t="shared" si="34"/>
+        <v>-84.462823038990237</v>
       </c>
       <c r="BF9" s="5">
-        <f t="shared" si="26"/>
-        <v>-118.19456741899891</v>
+        <f t="shared" si="34"/>
+        <v>-85.307451269380138</v>
       </c>
     </row>
     <row r="10" spans="2:169" x14ac:dyDescent="0.3">
@@ -2625,13 +2703,21 @@
         <v>-38</v>
       </c>
       <c r="AH10" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>25</v>
       </c>
-      <c r="AI10" s="5"/>
-      <c r="AJ10" s="5"/>
-      <c r="AK10" s="5"/>
-      <c r="AL10" s="5"/>
+      <c r="AI10" s="5">
+        <v>23</v>
+      </c>
+      <c r="AJ10" s="5">
+        <v>20</v>
+      </c>
+      <c r="AK10" s="5">
+        <v>20</v>
+      </c>
+      <c r="AL10" s="5">
+        <v>20</v>
+      </c>
       <c r="AN10" s="5">
         <v>-196</v>
       </c>
@@ -2666,45 +2752,45 @@
       <c r="AV10" s="5">
         <v>-76</v>
       </c>
-      <c r="AW10" s="5">
-        <f>AV10*1.01</f>
-        <v>-76.760000000000005</v>
+      <c r="AW10" s="12">
+        <f t="shared" si="33"/>
+        <v>83</v>
       </c>
       <c r="AX10" s="5">
-        <f t="shared" ref="AX10:BF10" si="27">AW10*1.01</f>
-        <v>-77.527600000000007</v>
+        <f t="shared" ref="AX10:BF10" si="35">AW10*1.01</f>
+        <v>83.83</v>
       </c>
       <c r="AY10" s="5">
-        <f t="shared" si="27"/>
-        <v>-78.302876000000012</v>
+        <f t="shared" si="35"/>
+        <v>84.668300000000002</v>
       </c>
       <c r="AZ10" s="5">
-        <f t="shared" si="27"/>
-        <v>-79.08590476000002</v>
+        <f t="shared" si="35"/>
+        <v>85.514983000000001</v>
       </c>
       <c r="BA10" s="5">
-        <f t="shared" si="27"/>
-        <v>-79.876763807600014</v>
+        <f t="shared" si="35"/>
+        <v>86.370132830000003</v>
       </c>
       <c r="BB10" s="5">
-        <f t="shared" si="27"/>
-        <v>-80.675531445676015</v>
+        <f t="shared" si="35"/>
+        <v>87.233834158299999</v>
       </c>
       <c r="BC10" s="5">
-        <f t="shared" si="27"/>
-        <v>-81.48228676013278</v>
+        <f t="shared" si="35"/>
+        <v>88.106172499883002</v>
       </c>
       <c r="BD10" s="5">
-        <f t="shared" si="27"/>
-        <v>-82.297109627734102</v>
+        <f t="shared" si="35"/>
+        <v>88.987234224881831</v>
       </c>
       <c r="BE10" s="5">
-        <f t="shared" si="27"/>
-        <v>-83.120080724011444</v>
+        <f t="shared" si="35"/>
+        <v>89.877106567130653</v>
       </c>
       <c r="BF10" s="5">
-        <f t="shared" si="27"/>
-        <v>-83.951281531251553</v>
+        <f t="shared" si="35"/>
+        <v>90.775877632801965</v>
       </c>
     </row>
     <row r="11" spans="2:169" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2712,137 +2798,149 @@
         <v>31</v>
       </c>
       <c r="C11" s="9">
-        <f t="shared" ref="C11:S11" si="28">C8-C9-C10</f>
+        <f t="shared" ref="C11:S11" si="36">C8-C9-C10</f>
         <v>1072</v>
       </c>
       <c r="D11" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>879</v>
       </c>
       <c r="E11" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>1160</v>
       </c>
       <c r="F11" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>1215</v>
       </c>
       <c r="G11" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>1270</v>
       </c>
       <c r="H11" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>997</v>
       </c>
       <c r="I11" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>1291</v>
       </c>
       <c r="J11" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>1243</v>
       </c>
       <c r="K11" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>1561</v>
       </c>
       <c r="L11" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>1249</v>
       </c>
       <c r="M11" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>881</v>
       </c>
       <c r="N11" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>-804</v>
       </c>
       <c r="O11" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>1715</v>
       </c>
       <c r="P11" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>1456</v>
       </c>
       <c r="Q11" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>1636</v>
       </c>
       <c r="R11" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>1854</v>
       </c>
       <c r="S11" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>2106</v>
       </c>
       <c r="T11" s="9">
-        <f t="shared" ref="T11:U11" si="29">T8-T9-T10</f>
+        <f t="shared" ref="T11:U11" si="37">T8-T9-T10</f>
         <v>1501</v>
       </c>
       <c r="U11" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v>1670</v>
       </c>
       <c r="V11" s="9">
-        <f t="shared" ref="V11:W11" si="30">V8-V9-V10</f>
+        <f t="shared" ref="V11:W11" si="38">V8-V9-V10</f>
         <v>1374</v>
       </c>
       <c r="W11" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>1828</v>
       </c>
       <c r="X11" s="9">
-        <f t="shared" ref="X11" si="31">X8-X9-X10</f>
+        <f t="shared" ref="X11" si="39">X8-X9-X10</f>
         <v>1650</v>
       </c>
       <c r="Y11" s="9">
-        <f t="shared" ref="Y11:AA11" si="32">Y8-Y9-Y10</f>
+        <f t="shared" ref="Y11:AA11" si="40">Y8-Y9-Y10</f>
         <v>1477</v>
       </c>
       <c r="Z11" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>1246</v>
       </c>
       <c r="AA11" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>1648</v>
       </c>
       <c r="AB11" s="9">
-        <f t="shared" ref="AB11" si="33">AB8-AB9-AB10</f>
+        <f t="shared" ref="AB11" si="41">AB8-AB9-AB10</f>
         <v>1922</v>
       </c>
       <c r="AC11" s="9">
-        <f t="shared" ref="AC11:AD11" si="34">AC8-AC9-AC10</f>
+        <f t="shared" ref="AC11:AD11" si="42">AC8-AC9-AC10</f>
         <v>1404</v>
       </c>
       <c r="AD11" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>1726</v>
       </c>
       <c r="AE11" s="9">
-        <f t="shared" ref="AE11:AH11" si="35">AE8-AE9-AE10</f>
+        <f t="shared" ref="AE11:AH11" si="43">AE8-AE9-AE10</f>
         <v>1307</v>
       </c>
       <c r="AF11" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>1416</v>
       </c>
       <c r="AG11" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>844</v>
       </c>
       <c r="AH11" s="9">
-        <f t="shared" si="35"/>
-        <v>953.61999999999989</v>
-      </c>
-      <c r="AI11" s="9"/>
-      <c r="AJ11" s="9"/>
-      <c r="AK11" s="9"/>
-      <c r="AL11" s="9"/>
+        <f t="shared" si="43"/>
+        <v>318</v>
+      </c>
+      <c r="AI11" s="9">
+        <f t="shared" ref="AI11:AL11" si="44">AI8-AI9-AI10</f>
+        <v>922</v>
+      </c>
+      <c r="AJ11" s="9">
+        <f t="shared" si="44"/>
+        <v>1205.7582000000002</v>
+      </c>
+      <c r="AK11" s="9">
+        <f t="shared" si="44"/>
+        <v>1081.0992000000001</v>
+      </c>
+      <c r="AL11" s="9">
+        <f t="shared" si="44"/>
+        <v>1037.6790000000001</v>
+      </c>
       <c r="AN11" s="9">
         <f>AN8-AN9-AN10</f>
         <v>4886</v>
@@ -2864,60 +2962,60 @@
         <v>6661</v>
       </c>
       <c r="AS11" s="9">
-        <f t="shared" ref="AS11:BB11" si="36">AS8-AS9-AS10</f>
+        <f t="shared" ref="AS11:BB11" si="45">AS8-AS9-AS10</f>
         <v>6651</v>
       </c>
       <c r="AT11" s="9">
-        <f t="shared" si="36"/>
+        <f t="shared" si="45"/>
         <v>6201</v>
       </c>
       <c r="AU11" s="9">
-        <f t="shared" si="36"/>
+        <f t="shared" si="45"/>
         <v>6700</v>
       </c>
       <c r="AV11" s="9">
-        <f t="shared" si="36"/>
+        <f t="shared" si="45"/>
         <v>3885</v>
       </c>
       <c r="AW11" s="9">
-        <f t="shared" si="36"/>
-        <v>5395.02</v>
+        <f t="shared" si="45"/>
+        <v>4246.5363999999972</v>
       </c>
       <c r="AX11" s="9">
-        <f t="shared" si="36"/>
-        <v>6578.4181999999992</v>
+        <f t="shared" si="45"/>
+        <v>6068.8722999999982</v>
       </c>
       <c r="AY11" s="9">
-        <f t="shared" si="36"/>
-        <v>6999.9943819999999</v>
+        <f t="shared" si="45"/>
+        <v>6988.9860230000031</v>
       </c>
       <c r="AZ11" s="9">
-        <f t="shared" si="36"/>
-        <v>7069.9943258200037</v>
+        <f t="shared" si="45"/>
+        <v>7058.8758832300045</v>
       </c>
       <c r="BA11" s="9">
-        <f t="shared" si="36"/>
-        <v>7140.6942690782016</v>
+        <f t="shared" si="45"/>
+        <v>7129.4646420622985</v>
       </c>
       <c r="BB11" s="9">
-        <f t="shared" si="36"/>
-        <v>7212.1012117689861</v>
+        <f t="shared" si="45"/>
+        <v>7200.7592884829191</v>
       </c>
       <c r="BC11" s="9">
-        <f t="shared" ref="BC11:BF11" si="37">BC8-BC9-BC10</f>
-        <v>7284.2222238866771</v>
+        <f t="shared" ref="BC11:BF11" si="46">BC8-BC9-BC10</f>
+        <v>7272.7668813677528</v>
       </c>
       <c r="BD11" s="9">
-        <f t="shared" si="37"/>
-        <v>7357.0644461255433</v>
+        <f t="shared" si="46"/>
+        <v>7345.49455018143</v>
       </c>
       <c r="BE11" s="9">
-        <f t="shared" si="37"/>
-        <v>7430.6350905867994</v>
+        <f t="shared" si="46"/>
+        <v>7418.9494956832414</v>
       </c>
       <c r="BF11" s="9">
-        <f t="shared" si="37"/>
-        <v>7504.941441492665</v>
+        <f t="shared" si="46"/>
+        <v>7493.1389906400736</v>
       </c>
     </row>
     <row r="12" spans="2:169" x14ac:dyDescent="0.3">
@@ -3021,10 +3119,21 @@
         <f>AV12-AG12-AF12-AE12</f>
         <v>107</v>
       </c>
-      <c r="AI12" s="5"/>
-      <c r="AJ12" s="5"/>
-      <c r="AK12" s="5"/>
-      <c r="AL12" s="5"/>
+      <c r="AI12" s="5">
+        <v>195</v>
+      </c>
+      <c r="AJ12" s="5">
+        <f>AJ11*0.17</f>
+        <v>204.97889400000005</v>
+      </c>
+      <c r="AK12" s="5">
+        <f t="shared" ref="AK12:AL12" si="47">AK11*0.17</f>
+        <v>183.78686400000004</v>
+      </c>
+      <c r="AL12" s="5">
+        <f t="shared" si="47"/>
+        <v>176.40543000000002</v>
+      </c>
       <c r="AN12" s="5">
         <v>646</v>
       </c>
@@ -3059,45 +3168,45 @@
       <c r="AV12" s="5">
         <v>666</v>
       </c>
-      <c r="AW12" s="5">
-        <f>AW11*0.17</f>
-        <v>917.15340000000015</v>
+      <c r="AW12" s="12">
+        <f>SUM(AI12:AL12)</f>
+        <v>760.17118800000014</v>
       </c>
       <c r="AX12" s="5">
-        <f t="shared" ref="AX12:BF12" si="38">AX11*0.17</f>
-        <v>1118.3310939999999</v>
+        <f t="shared" ref="AX12:BF12" si="48">AX11*0.17</f>
+        <v>1031.7082909999997</v>
       </c>
       <c r="AY12" s="5">
-        <f t="shared" si="38"/>
-        <v>1189.99904494</v>
+        <f t="shared" si="48"/>
+        <v>1188.1276239100007</v>
       </c>
       <c r="AZ12" s="5">
-        <f t="shared" si="38"/>
-        <v>1201.8990353894008</v>
+        <f t="shared" si="48"/>
+        <v>1200.0089001491008</v>
       </c>
       <c r="BA12" s="5">
-        <f t="shared" si="38"/>
-        <v>1213.9180257432943</v>
+        <f t="shared" si="48"/>
+        <v>1212.0089891505909</v>
       </c>
       <c r="BB12" s="5">
-        <f t="shared" si="38"/>
-        <v>1226.0572060007278</v>
+        <f t="shared" si="48"/>
+        <v>1224.1290790420962</v>
       </c>
       <c r="BC12" s="5">
-        <f t="shared" si="38"/>
-        <v>1238.3177780607352</v>
+        <f t="shared" si="48"/>
+        <v>1236.370369832518</v>
       </c>
       <c r="BD12" s="5">
-        <f t="shared" si="38"/>
-        <v>1250.7009558413424</v>
+        <f t="shared" si="48"/>
+        <v>1248.7340735308433</v>
       </c>
       <c r="BE12" s="5">
-        <f t="shared" si="38"/>
-        <v>1263.2079653997559</v>
+        <f t="shared" si="48"/>
+        <v>1261.2214142661512</v>
       </c>
       <c r="BF12" s="5">
-        <f t="shared" si="38"/>
-        <v>1275.8400450537531</v>
+        <f t="shared" si="48"/>
+        <v>1273.8336284088125</v>
       </c>
     </row>
     <row r="13" spans="2:169" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3105,137 +3214,149 @@
         <v>33</v>
       </c>
       <c r="C13" s="9">
-        <f t="shared" ref="C13:S13" si="39">C11-C12</f>
+        <f t="shared" ref="C13:S13" si="49">C11-C12</f>
         <v>950</v>
       </c>
       <c r="D13" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>767</v>
       </c>
       <c r="E13" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>-920</v>
       </c>
       <c r="F13" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>1137</v>
       </c>
       <c r="G13" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>1092</v>
       </c>
       <c r="H13" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>847</v>
       </c>
       <c r="I13" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>1101</v>
       </c>
       <c r="J13" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>989</v>
       </c>
       <c r="K13" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>1367</v>
       </c>
       <c r="L13" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>1115</v>
       </c>
       <c r="M13" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>847</v>
       </c>
       <c r="N13" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>-790</v>
       </c>
       <c r="O13" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>1518</v>
       </c>
       <c r="P13" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>1251</v>
       </c>
       <c r="Q13" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>1449</v>
       </c>
       <c r="R13" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>1509</v>
       </c>
       <c r="S13" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>1874</v>
       </c>
       <c r="T13" s="9">
-        <f t="shared" ref="T13:U13" si="40">T11-T12</f>
+        <f t="shared" ref="T13:U13" si="50">T11-T12</f>
         <v>1337</v>
       </c>
       <c r="U13" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="50"/>
         <v>1396</v>
       </c>
       <c r="V13" s="9">
-        <f t="shared" ref="V13:W13" si="41">V11-V12</f>
+        <f t="shared" ref="V13:W13" si="51">V11-V12</f>
         <v>1439</v>
       </c>
       <c r="W13" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="51"/>
         <v>1468</v>
       </c>
       <c r="X13" s="9">
-        <f t="shared" ref="X13" si="42">X11-X12</f>
+        <f t="shared" ref="X13" si="52">X11-X12</f>
         <v>1331</v>
       </c>
       <c r="Y13" s="9">
-        <f t="shared" ref="Y13:AA13" si="43">Y11-Y12</f>
+        <f t="shared" ref="Y13:AA13" si="53">Y11-Y12</f>
         <v>1240</v>
       </c>
       <c r="Z13" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>1031</v>
       </c>
       <c r="AA13" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>1450</v>
       </c>
       <c r="AB13" s="9">
-        <f t="shared" ref="AB13" si="44">AB11-AB12</f>
+        <f t="shared" ref="AB13" si="54">AB11-AB12</f>
         <v>1578</v>
       </c>
       <c r="AC13" s="9">
-        <f t="shared" ref="AC13:AD13" si="45">AC11-AC12</f>
+        <f t="shared" ref="AC13:AD13" si="55">AC11-AC12</f>
         <v>1172</v>
       </c>
       <c r="AD13" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="55"/>
         <v>1500</v>
       </c>
       <c r="AE13" s="9">
-        <f t="shared" ref="AE13:AH13" si="46">AE11-AE12</f>
+        <f t="shared" ref="AE13:AH13" si="56">AE11-AE12</f>
         <v>1051</v>
       </c>
       <c r="AF13" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="56"/>
         <v>1163</v>
       </c>
       <c r="AG13" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="56"/>
         <v>794</v>
       </c>
       <c r="AH13" s="9">
-        <f t="shared" si="46"/>
-        <v>846.61999999999989</v>
-      </c>
-      <c r="AI13" s="9"/>
-      <c r="AJ13" s="9"/>
-      <c r="AK13" s="9"/>
-      <c r="AL13" s="9"/>
+        <f t="shared" si="56"/>
+        <v>211</v>
+      </c>
+      <c r="AI13" s="9">
+        <f t="shared" ref="AI13:AK13" si="57">AI11-AI12</f>
+        <v>727</v>
+      </c>
+      <c r="AJ13" s="9">
+        <f t="shared" ref="AJ13:AL13" si="58">AJ11-AJ12</f>
+        <v>1000.7793060000001</v>
+      </c>
+      <c r="AK13" s="9">
+        <f t="shared" si="58"/>
+        <v>897.31233600000007</v>
+      </c>
+      <c r="AL13" s="9">
+        <f t="shared" si="58"/>
+        <v>861.27357000000006</v>
+      </c>
       <c r="AN13" s="9">
         <f>AN11-AN12</f>
         <v>4240</v>
@@ -3257,504 +3378,504 @@
         <v>5727</v>
       </c>
       <c r="AS13" s="9">
-        <f t="shared" ref="AS13:BB13" si="47">AS11-AS12</f>
+        <f t="shared" ref="AS13:BB13" si="59">AS11-AS12</f>
         <v>6046</v>
       </c>
       <c r="AT13" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>5070</v>
       </c>
       <c r="AU13" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>5700</v>
       </c>
       <c r="AV13" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>3219</v>
       </c>
       <c r="AW13" s="9">
-        <f t="shared" si="47"/>
-        <v>4477.8666000000003</v>
+        <f t="shared" si="59"/>
+        <v>3486.365211999997</v>
       </c>
       <c r="AX13" s="9">
-        <f t="shared" si="47"/>
-        <v>5460.087105999999</v>
+        <f t="shared" si="59"/>
+        <v>5037.1640089999983</v>
       </c>
       <c r="AY13" s="9">
-        <f t="shared" si="47"/>
-        <v>5809.9953370599997</v>
+        <f t="shared" si="59"/>
+        <v>5800.8583990900024</v>
       </c>
       <c r="AZ13" s="9">
-        <f t="shared" si="47"/>
-        <v>5868.0952904306032</v>
+        <f t="shared" si="59"/>
+        <v>5858.866983080904</v>
       </c>
       <c r="BA13" s="9">
-        <f t="shared" si="47"/>
-        <v>5926.7762433349071</v>
+        <f t="shared" si="59"/>
+        <v>5917.4556529117071</v>
       </c>
       <c r="BB13" s="9">
-        <f t="shared" si="47"/>
-        <v>5986.0440057682581</v>
+        <f t="shared" si="59"/>
+        <v>5976.6302094408229</v>
       </c>
       <c r="BC13" s="9">
-        <f t="shared" ref="BC13:BF13" si="48">BC11-BC12</f>
-        <v>6045.9044458259414</v>
+        <f t="shared" ref="BC13:BF13" si="60">BC11-BC12</f>
+        <v>6036.3965115352348</v>
       </c>
       <c r="BD13" s="9">
-        <f t="shared" si="48"/>
-        <v>6106.3634902842005</v>
+        <f t="shared" si="60"/>
+        <v>6096.7604766505865</v>
       </c>
       <c r="BE13" s="9">
-        <f t="shared" si="48"/>
-        <v>6167.4271251870432</v>
+        <f t="shared" si="60"/>
+        <v>6157.7280814170899</v>
       </c>
       <c r="BF13" s="9">
-        <f t="shared" si="48"/>
-        <v>6229.1013964389122</v>
+        <f t="shared" si="60"/>
+        <v>6219.3053622312609</v>
       </c>
       <c r="BG13" s="1">
         <f>BF13*(1+$BI$19)</f>
-        <v>6166.8103824745231</v>
+        <v>6157.1123086089483</v>
       </c>
       <c r="BH13" s="1">
-        <f t="shared" ref="BH13:DS13" si="49">BG13*(1+$BI$19)</f>
-        <v>6105.1422786497778</v>
+        <f t="shared" ref="BH13:DS13" si="61">BG13*(1+$BI$19)</f>
+        <v>6095.5411855228585</v>
       </c>
       <c r="BI13" s="1">
-        <f t="shared" si="49"/>
-        <v>6044.09085586328</v>
+        <f t="shared" si="61"/>
+        <v>6034.5857736676298</v>
       </c>
       <c r="BJ13" s="1">
-        <f t="shared" si="49"/>
-        <v>5983.649947304647</v>
+        <f t="shared" si="61"/>
+        <v>5974.2399159309534</v>
       </c>
       <c r="BK13" s="1">
-        <f t="shared" si="49"/>
-        <v>5923.8134478316006</v>
+        <f t="shared" si="61"/>
+        <v>5914.4975167716439</v>
       </c>
       <c r="BL13" s="1">
-        <f t="shared" si="49"/>
-        <v>5864.5753133532844</v>
+        <f t="shared" si="61"/>
+        <v>5855.3525416039274</v>
       </c>
       <c r="BM13" s="1">
-        <f t="shared" si="49"/>
-        <v>5805.9295602197517</v>
+        <f t="shared" si="61"/>
+        <v>5796.7990161878879</v>
       </c>
       <c r="BN13" s="1">
-        <f t="shared" si="49"/>
-        <v>5747.8702646175543</v>
+        <f t="shared" si="61"/>
+        <v>5738.8310260260087</v>
       </c>
       <c r="BO13" s="1">
-        <f t="shared" si="49"/>
-        <v>5690.3915619713789</v>
+        <f t="shared" si="61"/>
+        <v>5681.4427157657483</v>
       </c>
       <c r="BP13" s="1">
-        <f t="shared" si="49"/>
-        <v>5633.4876463516648</v>
+        <f t="shared" si="61"/>
+        <v>5624.6282886080908</v>
       </c>
       <c r="BQ13" s="1">
-        <f t="shared" si="49"/>
-        <v>5577.1527698881482</v>
+        <f t="shared" si="61"/>
+        <v>5568.38200572201</v>
       </c>
       <c r="BR13" s="1">
-        <f t="shared" si="49"/>
-        <v>5521.3812421892662</v>
+        <f t="shared" si="61"/>
+        <v>5512.6981856647899</v>
       </c>
       <c r="BS13" s="1">
-        <f t="shared" si="49"/>
-        <v>5466.1674297673735</v>
+        <f t="shared" si="61"/>
+        <v>5457.5712038081419</v>
       </c>
       <c r="BT13" s="1">
-        <f t="shared" si="49"/>
-        <v>5411.5057554696996</v>
+        <f t="shared" si="61"/>
+        <v>5402.9954917700607</v>
       </c>
       <c r="BU13" s="1">
-        <f t="shared" si="49"/>
-        <v>5357.3906979150024</v>
+        <f t="shared" si="61"/>
+        <v>5348.9655368523599</v>
       </c>
       <c r="BV13" s="1">
-        <f t="shared" si="49"/>
-        <v>5303.8167909358526</v>
+        <f t="shared" si="61"/>
+        <v>5295.475881483836</v>
       </c>
       <c r="BW13" s="1">
-        <f t="shared" si="49"/>
-        <v>5250.7786230264937</v>
+        <f t="shared" si="61"/>
+        <v>5242.521122668998</v>
       </c>
       <c r="BX13" s="1">
-        <f t="shared" si="49"/>
-        <v>5198.2708367962287</v>
+        <f t="shared" si="61"/>
+        <v>5190.0959114423076</v>
       </c>
       <c r="BY13" s="1">
-        <f t="shared" si="49"/>
-        <v>5146.2881284282666</v>
+        <f t="shared" si="61"/>
+        <v>5138.1949523278845</v>
       </c>
       <c r="BZ13" s="1">
-        <f t="shared" si="49"/>
-        <v>5094.8252471439837</v>
+        <f t="shared" si="61"/>
+        <v>5086.8130028046053</v>
       </c>
       <c r="CA13" s="1">
-        <f t="shared" si="49"/>
-        <v>5043.8769946725442</v>
+        <f t="shared" si="61"/>
+        <v>5035.9448727765594</v>
       </c>
       <c r="CB13" s="1">
-        <f t="shared" si="49"/>
-        <v>4993.4382247258191</v>
+        <f t="shared" si="61"/>
+        <v>4985.5854240487934</v>
       </c>
       <c r="CC13" s="1">
-        <f t="shared" si="49"/>
-        <v>4943.5038424785607</v>
+        <f t="shared" si="61"/>
+        <v>4935.7295698083053</v>
       </c>
       <c r="CD13" s="1">
-        <f t="shared" si="49"/>
-        <v>4894.0688040537752</v>
+        <f t="shared" si="61"/>
+        <v>4886.372274110222</v>
       </c>
       <c r="CE13" s="1">
-        <f t="shared" si="49"/>
-        <v>4845.1281160132376</v>
+        <f t="shared" si="61"/>
+        <v>4837.5085513691201</v>
       </c>
       <c r="CF13" s="1">
-        <f t="shared" si="49"/>
-        <v>4796.676834853105</v>
+        <f t="shared" si="61"/>
+        <v>4789.1334658554288</v>
       </c>
       <c r="CG13" s="1">
-        <f t="shared" si="49"/>
-        <v>4748.7100665045737</v>
+        <f t="shared" si="61"/>
+        <v>4741.2421311968747</v>
       </c>
       <c r="CH13" s="1">
-        <f t="shared" si="49"/>
-        <v>4701.2229658395281</v>
+        <f t="shared" si="61"/>
+        <v>4693.8297098849062</v>
       </c>
       <c r="CI13" s="1">
-        <f t="shared" si="49"/>
-        <v>4654.2107361811331</v>
+        <f t="shared" si="61"/>
+        <v>4646.8914127860571</v>
       </c>
       <c r="CJ13" s="1">
-        <f t="shared" si="49"/>
-        <v>4607.6686288193214</v>
+        <f t="shared" si="61"/>
+        <v>4600.4224986581967</v>
       </c>
       <c r="CK13" s="1">
-        <f t="shared" si="49"/>
-        <v>4561.5919425311286</v>
+        <f t="shared" si="61"/>
+        <v>4554.4182736716148</v>
       </c>
       <c r="CL13" s="1">
-        <f t="shared" si="49"/>
-        <v>4515.9760231058171</v>
+        <f t="shared" si="61"/>
+        <v>4508.874090934899</v>
       </c>
       <c r="CM13" s="1">
-        <f t="shared" si="49"/>
-        <v>4470.8162628747586</v>
+        <f t="shared" si="61"/>
+        <v>4463.7853500255496</v>
       </c>
       <c r="CN13" s="1">
-        <f t="shared" si="49"/>
-        <v>4426.1081002460114</v>
+        <f t="shared" si="61"/>
+        <v>4419.1474965252937</v>
       </c>
       <c r="CO13" s="1">
-        <f t="shared" si="49"/>
-        <v>4381.8470192435516</v>
+        <f t="shared" si="61"/>
+        <v>4374.9560215600404</v>
       </c>
       <c r="CP13" s="1">
-        <f t="shared" si="49"/>
-        <v>4338.028549051116</v>
+        <f t="shared" si="61"/>
+        <v>4331.20646134444</v>
       </c>
       <c r="CQ13" s="1">
-        <f t="shared" si="49"/>
-        <v>4294.6482635606044</v>
+        <f t="shared" si="61"/>
+        <v>4287.8943967309951</v>
       </c>
       <c r="CR13" s="1">
-        <f t="shared" si="49"/>
-        <v>4251.7017809249983</v>
+        <f t="shared" si="61"/>
+        <v>4245.0154527636851</v>
       </c>
       <c r="CS13" s="1">
-        <f t="shared" si="49"/>
-        <v>4209.184763115748</v>
+        <f t="shared" si="61"/>
+        <v>4202.565298236048</v>
       </c>
       <c r="CT13" s="1">
-        <f t="shared" si="49"/>
-        <v>4167.0929154845908</v>
+        <f t="shared" si="61"/>
+        <v>4160.539645253687</v>
       </c>
       <c r="CU13" s="1">
-        <f t="shared" si="49"/>
-        <v>4125.4219863297449</v>
+        <f t="shared" si="61"/>
+        <v>4118.9342488011498</v>
       </c>
       <c r="CV13" s="1">
-        <f t="shared" si="49"/>
-        <v>4084.1677664664476</v>
+        <f t="shared" si="61"/>
+        <v>4077.7449063131385</v>
       </c>
       <c r="CW13" s="1">
-        <f t="shared" si="49"/>
-        <v>4043.326088801783</v>
+        <f t="shared" si="61"/>
+        <v>4036.9674572500071</v>
       </c>
       <c r="CX13" s="1">
-        <f t="shared" si="49"/>
-        <v>4002.8928279137654</v>
+        <f t="shared" si="61"/>
+        <v>3996.597782677507</v>
       </c>
       <c r="CY13" s="1">
-        <f t="shared" si="49"/>
-        <v>3962.8638996346276</v>
+        <f t="shared" si="61"/>
+        <v>3956.6318048507319</v>
       </c>
       <c r="CZ13" s="1">
-        <f t="shared" si="49"/>
-        <v>3923.2352606382815</v>
+        <f t="shared" si="61"/>
+        <v>3917.0654868022248</v>
       </c>
       <c r="DA13" s="1">
-        <f t="shared" si="49"/>
-        <v>3884.0029080318986</v>
+        <f t="shared" si="61"/>
+        <v>3877.8948319342026</v>
       </c>
       <c r="DB13" s="1">
-        <f t="shared" si="49"/>
-        <v>3845.1628789515798</v>
+        <f t="shared" si="61"/>
+        <v>3839.1158836148606</v>
       </c>
       <c r="DC13" s="1">
-        <f t="shared" si="49"/>
-        <v>3806.7112501620641</v>
+        <f t="shared" si="61"/>
+        <v>3800.7247247787118</v>
       </c>
       <c r="DD13" s="1">
-        <f t="shared" si="49"/>
-        <v>3768.6441376604434</v>
+        <f t="shared" si="61"/>
+        <v>3762.7174775309245</v>
       </c>
       <c r="DE13" s="1">
-        <f t="shared" si="49"/>
-        <v>3730.9576962838391</v>
+        <f t="shared" si="61"/>
+        <v>3725.0903027556151</v>
       </c>
       <c r="DF13" s="1">
-        <f t="shared" si="49"/>
-        <v>3693.6481193210006</v>
+        <f t="shared" si="61"/>
+        <v>3687.8393997280591</v>
       </c>
       <c r="DG13" s="1">
-        <f t="shared" si="49"/>
-        <v>3656.7116381277906</v>
+        <f t="shared" si="61"/>
+        <v>3650.9610057307787</v>
       </c>
       <c r="DH13" s="1">
-        <f t="shared" si="49"/>
-        <v>3620.1445217465125</v>
+        <f t="shared" si="61"/>
+        <v>3614.4513956734709</v>
       </c>
       <c r="DI13" s="1">
-        <f t="shared" si="49"/>
-        <v>3583.9430765290472</v>
+        <f t="shared" si="61"/>
+        <v>3578.3068817167359</v>
       </c>
       <c r="DJ13" s="1">
-        <f t="shared" si="49"/>
-        <v>3548.1036457637565</v>
+        <f t="shared" si="61"/>
+        <v>3542.5238128995684</v>
       </c>
       <c r="DK13" s="1">
-        <f t="shared" si="49"/>
-        <v>3512.6226093061191</v>
+        <f t="shared" si="61"/>
+        <v>3507.0985747705727</v>
       </c>
       <c r="DL13" s="1">
-        <f t="shared" si="49"/>
-        <v>3477.4963832130579</v>
+        <f t="shared" si="61"/>
+        <v>3472.0275890228668</v>
       </c>
       <c r="DM13" s="1">
-        <f t="shared" si="49"/>
-        <v>3442.7214193809273</v>
+        <f t="shared" si="61"/>
+        <v>3437.3073131326382</v>
       </c>
       <c r="DN13" s="1">
-        <f t="shared" si="49"/>
-        <v>3408.2942051871178</v>
+        <f t="shared" si="61"/>
+        <v>3402.934240001312</v>
       </c>
       <c r="DO13" s="1">
-        <f t="shared" si="49"/>
-        <v>3374.2112631352466</v>
+        <f t="shared" si="61"/>
+        <v>3368.9048976012987</v>
       </c>
       <c r="DP13" s="1">
-        <f t="shared" si="49"/>
-        <v>3340.4691505038941</v>
+        <f t="shared" si="61"/>
+        <v>3335.2158486252856</v>
       </c>
       <c r="DQ13" s="1">
-        <f t="shared" si="49"/>
-        <v>3307.0644589988551</v>
+        <f t="shared" si="61"/>
+        <v>3301.8636901390328</v>
       </c>
       <c r="DR13" s="1">
-        <f t="shared" si="49"/>
-        <v>3273.9938144088665</v>
+        <f t="shared" si="61"/>
+        <v>3268.8450532376423</v>
       </c>
       <c r="DS13" s="1">
-        <f t="shared" si="49"/>
-        <v>3241.2538762647778</v>
+        <f t="shared" si="61"/>
+        <v>3236.1566027052659</v>
       </c>
       <c r="DT13" s="1">
-        <f t="shared" ref="DT13:FM13" si="50">DS13*(1+$BI$19)</f>
-        <v>3208.84133750213</v>
+        <f t="shared" ref="DT13:FM13" si="62">DS13*(1+$BI$19)</f>
+        <v>3203.7950366782134</v>
       </c>
       <c r="DU13" s="1">
-        <f t="shared" si="50"/>
-        <v>3176.7529241271086</v>
+        <f t="shared" si="62"/>
+        <v>3171.7570863114311</v>
       </c>
       <c r="DV13" s="1">
-        <f t="shared" si="50"/>
-        <v>3144.9853948858376</v>
+        <f t="shared" si="62"/>
+        <v>3140.0395154483167</v>
       </c>
       <c r="DW13" s="1">
-        <f t="shared" si="50"/>
-        <v>3113.535540936979</v>
+        <f t="shared" si="62"/>
+        <v>3108.6391202938335</v>
       </c>
       <c r="DX13" s="1">
-        <f t="shared" si="50"/>
-        <v>3082.4001855276092</v>
+        <f t="shared" si="62"/>
+        <v>3077.5527290908949</v>
       </c>
       <c r="DY13" s="1">
-        <f t="shared" si="50"/>
-        <v>3051.5761836723332</v>
+        <f t="shared" si="62"/>
+        <v>3046.777201799986</v>
       </c>
       <c r="DZ13" s="1">
-        <f t="shared" si="50"/>
-        <v>3021.0604218356098</v>
+        <f t="shared" si="62"/>
+        <v>3016.3094297819862</v>
       </c>
       <c r="EA13" s="1">
-        <f t="shared" si="50"/>
-        <v>2990.8498176172538</v>
+        <f t="shared" si="62"/>
+        <v>2986.1463354841662</v>
       </c>
       <c r="EB13" s="1">
-        <f t="shared" si="50"/>
-        <v>2960.9413194410813</v>
+        <f t="shared" si="62"/>
+        <v>2956.2848721293244</v>
       </c>
       <c r="EC13" s="1">
-        <f t="shared" si="50"/>
-        <v>2931.3319062466703</v>
+        <f t="shared" si="62"/>
+        <v>2926.722023408031</v>
       </c>
       <c r="ED13" s="1">
-        <f t="shared" si="50"/>
-        <v>2902.0185871842036</v>
+        <f t="shared" si="62"/>
+        <v>2897.4548031739505</v>
       </c>
       <c r="EE13" s="1">
-        <f t="shared" si="50"/>
-        <v>2872.9984013123617</v>
+        <f t="shared" si="62"/>
+        <v>2868.4802551422108</v>
       </c>
       <c r="EF13" s="1">
-        <f t="shared" si="50"/>
-        <v>2844.2684172992381</v>
+        <f t="shared" si="62"/>
+        <v>2839.7954525907885</v>
       </c>
       <c r="EG13" s="1">
-        <f t="shared" si="50"/>
-        <v>2815.8257331262457</v>
+        <f t="shared" si="62"/>
+        <v>2811.3974980648804</v>
       </c>
       <c r="EH13" s="1">
-        <f t="shared" si="50"/>
-        <v>2787.6674757949831</v>
+        <f t="shared" si="62"/>
+        <v>2783.2835230842315</v>
       </c>
       <c r="EI13" s="1">
-        <f t="shared" si="50"/>
-        <v>2759.7908010370334</v>
+        <f t="shared" si="62"/>
+        <v>2755.4506878533894</v>
       </c>
       <c r="EJ13" s="1">
-        <f t="shared" si="50"/>
-        <v>2732.1928930266631</v>
+        <f t="shared" si="62"/>
+        <v>2727.8961809748553</v>
       </c>
       <c r="EK13" s="1">
-        <f t="shared" si="50"/>
-        <v>2704.8709640963966</v>
+        <f t="shared" si="62"/>
+        <v>2700.6172191651067</v>
       </c>
       <c r="EL13" s="1">
-        <f t="shared" si="50"/>
-        <v>2677.8222544554328</v>
+        <f t="shared" si="62"/>
+        <v>2673.6110469734558</v>
       </c>
       <c r="EM13" s="1">
-        <f t="shared" si="50"/>
-        <v>2651.0440319108784</v>
+        <f t="shared" si="62"/>
+        <v>2646.8749365037211</v>
       </c>
       <c r="EN13" s="1">
-        <f t="shared" si="50"/>
-        <v>2624.5335915917694</v>
+        <f t="shared" si="62"/>
+        <v>2620.4061871386839</v>
       </c>
       <c r="EO13" s="1">
-        <f t="shared" si="50"/>
-        <v>2598.2882556758518</v>
+        <f t="shared" si="62"/>
+        <v>2594.2021252672971</v>
       </c>
       <c r="EP13" s="1">
-        <f t="shared" si="50"/>
-        <v>2572.3053731190935</v>
+        <f t="shared" si="62"/>
+        <v>2568.2601040146242</v>
       </c>
       <c r="EQ13" s="1">
-        <f t="shared" si="50"/>
-        <v>2546.5823193879023</v>
+        <f t="shared" si="62"/>
+        <v>2542.5775029744777</v>
       </c>
       <c r="ER13" s="1">
-        <f t="shared" si="50"/>
-        <v>2521.1164961940231</v>
+        <f t="shared" si="62"/>
+        <v>2517.151727944733</v>
       </c>
       <c r="ES13" s="1">
-        <f t="shared" si="50"/>
-        <v>2495.905331232083</v>
+        <f t="shared" si="62"/>
+        <v>2491.9802106652855</v>
       </c>
       <c r="ET13" s="1">
-        <f t="shared" si="50"/>
-        <v>2470.946277919762</v>
+        <f t="shared" si="62"/>
+        <v>2467.0604085586328</v>
       </c>
       <c r="EU13" s="1">
-        <f t="shared" si="50"/>
-        <v>2446.2368151405644</v>
+        <f t="shared" si="62"/>
+        <v>2442.3898044730463</v>
       </c>
       <c r="EV13" s="1">
-        <f t="shared" si="50"/>
-        <v>2421.7744469891586</v>
+        <f t="shared" si="62"/>
+        <v>2417.965906428316</v>
       </c>
       <c r="EW13" s="1">
-        <f t="shared" si="50"/>
-        <v>2397.5567025192672</v>
+        <f t="shared" si="62"/>
+        <v>2393.786247364033</v>
       </c>
       <c r="EX13" s="1">
-        <f t="shared" si="50"/>
-        <v>2373.5811354940747</v>
+        <f t="shared" si="62"/>
+        <v>2369.8483848903925</v>
       </c>
       <c r="EY13" s="1">
-        <f t="shared" si="50"/>
-        <v>2349.8453241391339</v>
+        <f t="shared" si="62"/>
+        <v>2346.1499010414886</v>
       </c>
       <c r="EZ13" s="1">
-        <f t="shared" si="50"/>
-        <v>2326.3468708977425</v>
+        <f t="shared" si="62"/>
+        <v>2322.6884020310736</v>
       </c>
       <c r="FA13" s="1">
-        <f t="shared" si="50"/>
-        <v>2303.0834021887649</v>
+        <f t="shared" si="62"/>
+        <v>2299.461518010763</v>
       </c>
       <c r="FB13" s="1">
-        <f t="shared" si="50"/>
-        <v>2280.0525681668773</v>
+        <f t="shared" si="62"/>
+        <v>2276.4669028306553</v>
       </c>
       <c r="FC13" s="1">
-        <f t="shared" si="50"/>
-        <v>2257.2520424852087</v>
+        <f t="shared" si="62"/>
+        <v>2253.7022338023485</v>
       </c>
       <c r="FD13" s="1">
-        <f t="shared" si="50"/>
-        <v>2234.6795220603567</v>
+        <f t="shared" si="62"/>
+        <v>2231.1652114643248</v>
       </c>
       <c r="FE13" s="1">
-        <f t="shared" si="50"/>
-        <v>2212.3327268397529</v>
+        <f t="shared" si="62"/>
+        <v>2208.8535593496813</v>
       </c>
       <c r="FF13" s="1">
-        <f t="shared" si="50"/>
-        <v>2190.2093995713553</v>
+        <f t="shared" si="62"/>
+        <v>2186.7650237561843</v>
       </c>
       <c r="FG13" s="1">
-        <f t="shared" si="50"/>
-        <v>2168.3073055756417</v>
+        <f t="shared" si="62"/>
+        <v>2164.8973735186223</v>
       </c>
       <c r="FH13" s="1">
-        <f t="shared" si="50"/>
-        <v>2146.6242325198855</v>
+        <f t="shared" si="62"/>
+        <v>2143.2483997834361</v>
       </c>
       <c r="FI13" s="1">
-        <f t="shared" si="50"/>
-        <v>2125.1579901946866</v>
+        <f t="shared" si="62"/>
+        <v>2121.8159157856016</v>
       </c>
       <c r="FJ13" s="1">
-        <f t="shared" si="50"/>
-        <v>2103.9064102927396</v>
+        <f t="shared" si="62"/>
+        <v>2100.5977566277456</v>
       </c>
       <c r="FK13" s="1">
-        <f t="shared" si="50"/>
-        <v>2082.867346189812</v>
+        <f t="shared" si="62"/>
+        <v>2079.5917790614681</v>
       </c>
       <c r="FL13" s="1">
-        <f t="shared" si="50"/>
-        <v>2062.0386727279138</v>
+        <f t="shared" si="62"/>
+        <v>2058.7958612708535</v>
       </c>
       <c r="FM13" s="1">
-        <f t="shared" si="50"/>
-        <v>2041.4182860006347</v>
+        <f t="shared" si="62"/>
+        <v>2038.207902658145</v>
       </c>
     </row>
     <row r="14" spans="2:169" x14ac:dyDescent="0.3">
@@ -3859,10 +3980,22 @@
         <f>1476.9</f>
         <v>1476.9</v>
       </c>
-      <c r="AI14" s="5"/>
-      <c r="AJ14" s="5"/>
-      <c r="AK14" s="5"/>
-      <c r="AL14" s="5"/>
+      <c r="AI14" s="5">
+        <f>1478.2</f>
+        <v>1478.2</v>
+      </c>
+      <c r="AJ14" s="5">
+        <f t="shared" ref="AJ14:AL14" si="63">1478.2</f>
+        <v>1478.2</v>
+      </c>
+      <c r="AK14" s="5">
+        <f t="shared" si="63"/>
+        <v>1478.2</v>
+      </c>
+      <c r="AL14" s="5">
+        <f t="shared" si="63"/>
+        <v>1478.2</v>
+      </c>
       <c r="AN14" s="5">
         <v>1580</v>
       </c>
@@ -3888,48 +4021,48 @@
         <v>1509.4</v>
       </c>
       <c r="AV14" s="5">
-        <f t="shared" ref="AV14:BF14" si="51">1476.9</f>
+        <f>1476.9</f>
         <v>1476.9</v>
       </c>
       <c r="AW14" s="5">
-        <f t="shared" si="51"/>
-        <v>1476.9</v>
+        <f>1478.2</f>
+        <v>1478.2</v>
       </c>
       <c r="AX14" s="5">
-        <f t="shared" si="51"/>
-        <v>1476.9</v>
+        <f>1478.2</f>
+        <v>1478.2</v>
       </c>
       <c r="AY14" s="5">
-        <f t="shared" si="51"/>
-        <v>1476.9</v>
+        <f>1478.2</f>
+        <v>1478.2</v>
       </c>
       <c r="AZ14" s="5">
-        <f t="shared" si="51"/>
-        <v>1476.9</v>
+        <f>1478.2</f>
+        <v>1478.2</v>
       </c>
       <c r="BA14" s="5">
-        <f t="shared" si="51"/>
-        <v>1476.9</v>
+        <f>1478.2</f>
+        <v>1478.2</v>
       </c>
       <c r="BB14" s="5">
-        <f t="shared" si="51"/>
-        <v>1476.9</v>
+        <f>1478.2</f>
+        <v>1478.2</v>
       </c>
       <c r="BC14" s="5">
-        <f t="shared" si="51"/>
-        <v>1476.9</v>
+        <f>1478.2</f>
+        <v>1478.2</v>
       </c>
       <c r="BD14" s="5">
-        <f t="shared" si="51"/>
-        <v>1476.9</v>
+        <f>1478.2</f>
+        <v>1478.2</v>
       </c>
       <c r="BE14" s="5">
-        <f t="shared" si="51"/>
-        <v>1476.9</v>
+        <f>1478.2</f>
+        <v>1478.2</v>
       </c>
       <c r="BF14" s="5">
-        <f t="shared" si="51"/>
-        <v>1476.9</v>
+        <f>1478.2</f>
+        <v>1478.2</v>
       </c>
     </row>
     <row r="15" spans="2:169" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3937,137 +4070,149 @@
         <v>34</v>
       </c>
       <c r="C15" s="8">
-        <f t="shared" ref="C15:S15" si="52">C13/C14</f>
+        <f t="shared" ref="C15:S15" si="64">C13/C14</f>
         <v>0.60126582278481011</v>
       </c>
       <c r="D15" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="64"/>
         <v>0.48544303797468352</v>
       </c>
       <c r="E15" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="64"/>
         <v>-0.58227848101265822</v>
       </c>
       <c r="F15" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="64"/>
         <v>0.71962025316455691</v>
       </c>
       <c r="G15" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="64"/>
         <v>0.69113924050632913</v>
       </c>
       <c r="H15" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="64"/>
         <v>0.53607594936708858</v>
       </c>
       <c r="I15" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="64"/>
         <v>0.69683544303797473</v>
       </c>
       <c r="J15" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="64"/>
         <v>0.6259493670886076</v>
       </c>
       <c r="K15" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="64"/>
         <v>0.86518987341772147</v>
       </c>
       <c r="L15" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="64"/>
         <v>0.70569620253164556</v>
       </c>
       <c r="M15" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="64"/>
         <v>0.53607594936708858</v>
       </c>
       <c r="N15" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="64"/>
         <v>-0.5</v>
       </c>
       <c r="O15" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="64"/>
         <v>0.96075949367088609</v>
       </c>
       <c r="P15" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="64"/>
         <v>0.79177215189873418</v>
       </c>
       <c r="Q15" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="64"/>
         <v>0.91708860759493671</v>
       </c>
       <c r="R15" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="64"/>
         <v>0.95566814439518688</v>
       </c>
       <c r="S15" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="64"/>
         <v>1.1846513686073707</v>
       </c>
       <c r="T15" s="8">
-        <f t="shared" ref="T15:U15" si="53">T13/T14</f>
+        <f t="shared" ref="T15:U15" si="65">T13/T14</f>
         <v>0.84491911021233568</v>
       </c>
       <c r="U15" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="65"/>
         <v>0.8841038632045598</v>
       </c>
       <c r="V15" s="8">
-        <f t="shared" ref="V15:W15" si="54">V13/V14</f>
+        <f t="shared" ref="V15:W15" si="66">V13/V14</f>
         <v>0.91539440203562339</v>
       </c>
       <c r="W15" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="66"/>
         <v>0.9367621721651459</v>
       </c>
       <c r="X15" s="8">
-        <f t="shared" ref="X15" si="55">X13/X14</f>
+        <f t="shared" ref="X15" si="67">X13/X14</f>
         <v>0.85375240538806929</v>
       </c>
       <c r="Y15" s="8">
-        <f t="shared" ref="Y15:AA15" si="56">Y13/Y14</f>
+        <f t="shared" ref="Y15:AA15" si="68">Y13/Y14</f>
         <v>0.80321285140562249</v>
       </c>
       <c r="Z15" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="68"/>
         <v>0.67100553205336799</v>
       </c>
       <c r="AA15" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="68"/>
         <v>0.94870452761057311</v>
       </c>
       <c r="AB15" s="8">
-        <f t="shared" ref="AB15" si="57">AB13/AB14</f>
+        <f t="shared" ref="AB15" si="69">AB13/AB14</f>
         <v>1.0376117832719622</v>
       </c>
       <c r="AC15" s="8">
-        <f t="shared" ref="AC15:AD15" si="58">AC13/AC14</f>
+        <f t="shared" ref="AC15:AD15" si="70">AC13/AC14</f>
         <v>0.77451757864129001</v>
       </c>
       <c r="AD15" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="70"/>
         <v>0.99469496021220161</v>
       </c>
       <c r="AE15" s="8">
-        <f t="shared" ref="AE15:AH15" si="59">AE13/AE14</f>
+        <f t="shared" ref="AE15:AH15" si="71">AE13/AE14</f>
         <v>0.70607994625461878</v>
       </c>
       <c r="AF15" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="71"/>
         <v>0.78628895950240019</v>
       </c>
       <c r="AG15" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="71"/>
         <v>0.53794037940379402</v>
       </c>
       <c r="AH15" s="8">
-        <f t="shared" si="59"/>
-        <v>0.57324124856117531</v>
-      </c>
-      <c r="AI15" s="8"/>
-      <c r="AJ15" s="8"/>
-      <c r="AK15" s="8"/>
-      <c r="AL15" s="8"/>
+        <f t="shared" si="71"/>
+        <v>0.1428668156273275</v>
+      </c>
+      <c r="AI15" s="8">
+        <f t="shared" ref="AI15:AK15" si="72">AI13/AI14</f>
+        <v>0.49181436882695168</v>
+      </c>
+      <c r="AJ15" s="8">
+        <f t="shared" ref="AJ15:AL15" si="73">AJ13/AJ14</f>
+        <v>0.67702564335002036</v>
+      </c>
+      <c r="AK15" s="8">
+        <f t="shared" si="73"/>
+        <v>0.60703039913408208</v>
+      </c>
+      <c r="AL15" s="8">
+        <f t="shared" si="73"/>
+        <v>0.58265023000947103</v>
+      </c>
       <c r="AN15" s="8">
         <f>AN13/AN14</f>
         <v>2.6835443037974684</v>
@@ -4089,60 +4234,60 @@
         <v>3.6246835443037977</v>
       </c>
       <c r="AS15" s="8">
-        <f t="shared" ref="AS15:BB15" si="60">AS13/AS14</f>
+        <f t="shared" ref="AS15:BB15" si="74">AS13/AS14</f>
         <v>3.8265822784810126</v>
       </c>
       <c r="AT15" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="74"/>
         <v>3.2088607594936707</v>
       </c>
       <c r="AU15" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="74"/>
         <v>3.7763349675367692</v>
       </c>
       <c r="AV15" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="74"/>
         <v>2.1795653057079014</v>
       </c>
       <c r="AW15" s="8">
-        <f t="shared" si="60"/>
-        <v>3.0319362177534024</v>
+        <f t="shared" si="74"/>
+        <v>2.3585206413205229</v>
       </c>
       <c r="AX15" s="8">
-        <f t="shared" si="60"/>
-        <v>3.6969917435168247</v>
+        <f t="shared" si="74"/>
+        <v>3.4076336145311852</v>
       </c>
       <c r="AY15" s="8">
-        <f t="shared" si="60"/>
-        <v>3.9339124768501588</v>
+        <f t="shared" si="74"/>
+        <v>3.92427168115952</v>
       </c>
       <c r="AZ15" s="8">
-        <f t="shared" si="60"/>
-        <v>3.9732516016186628</v>
+        <f t="shared" si="74"/>
+        <v>3.963514397971116</v>
       </c>
       <c r="BA15" s="8">
-        <f t="shared" si="60"/>
-        <v>4.012984117634848</v>
+        <f t="shared" si="74"/>
+        <v>4.0031495419508234</v>
       </c>
       <c r="BB15" s="8">
-        <f t="shared" si="60"/>
-        <v>4.0531139588111973</v>
+        <f t="shared" si="74"/>
+        <v>4.0431810373703305</v>
       </c>
       <c r="BC15" s="8">
-        <f t="shared" ref="BC15:BF15" si="61">BC13/BC14</f>
-        <v>4.0936450983993105</v>
+        <f t="shared" ref="BC15:BF15" si="75">BC13/BC14</f>
+        <v>4.0836128477440363</v>
       </c>
       <c r="BD15" s="8">
-        <f t="shared" si="61"/>
-        <v>4.1345815493833031</v>
+        <f t="shared" si="75"/>
+        <v>4.1244489762214762</v>
       </c>
       <c r="BE15" s="8">
-        <f t="shared" si="61"/>
-        <v>4.1759273648771362</v>
+        <f t="shared" si="75"/>
+        <v>4.1656934659836891</v>
       </c>
       <c r="BF15" s="8">
-        <f t="shared" si="61"/>
-        <v>4.2176866385259064</v>
+        <f t="shared" si="75"/>
+        <v>4.2073504006435263</v>
       </c>
     </row>
     <row r="17" spans="2:61" x14ac:dyDescent="0.3">
@@ -4158,117 +4303,129 @@
         <v>9.6802646085997868E-2</v>
       </c>
       <c r="H17" s="10">
-        <f t="shared" ref="H17:R17" si="62">H3/D3-1</f>
+        <f t="shared" ref="H17:R17" si="76">H3/D3-1</f>
         <v>9.586158522328736E-2</v>
       </c>
       <c r="I17" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="76"/>
         <v>6.9790739091718512E-2</v>
       </c>
       <c r="J17" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="76"/>
         <v>4.0351414853406986E-2</v>
       </c>
       <c r="K17" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="76"/>
         <v>7.1572175311620523E-2</v>
       </c>
       <c r="L17" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="76"/>
         <v>0.10155749946660975</v>
       </c>
       <c r="M17" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="76"/>
         <v>5.1295390698158361E-2</v>
       </c>
       <c r="N17" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="76"/>
         <v>-0.38010604870384912</v>
       </c>
       <c r="O17" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="76"/>
         <v>-6.1913696060037493E-3</v>
       </c>
       <c r="P17" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="76"/>
         <v>8.8804958357544095E-2</v>
       </c>
       <c r="Q17" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="76"/>
         <v>2.5039588281868586E-2</v>
       </c>
       <c r="R17" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="76"/>
         <v>0.95533027086963407</v>
       </c>
       <c r="S17" s="10">
-        <f t="shared" ref="S17:AA17" si="63">S3/O3-1</f>
+        <f t="shared" ref="S17:AA17" si="77">S3/O3-1</f>
         <v>0.15612610911836899</v>
       </c>
       <c r="T17" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="77"/>
         <v>1.0139642444187524E-2</v>
       </c>
       <c r="U17" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="77"/>
         <v>4.9628270734768831E-2</v>
       </c>
       <c r="V17" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="77"/>
         <v>-8.9112119248218047E-3</v>
       </c>
       <c r="W17" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="77"/>
         <v>3.5842586544742039E-2</v>
       </c>
       <c r="X17" s="10">
-        <f t="shared" ref="X17" si="64">X3/T3-1</f>
+        <f t="shared" ref="X17" si="78">X3/T3-1</f>
         <v>0.17240468433565193</v>
       </c>
       <c r="Y17" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="77"/>
         <v>0.13972955569864776</v>
       </c>
       <c r="Z17" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="77"/>
         <v>4.8307994114762165E-2</v>
       </c>
       <c r="AA17" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="77"/>
         <v>1.986285173799951E-2</v>
       </c>
       <c r="AB17" s="10">
-        <f t="shared" ref="AB17:AE17" si="65">AB3/X3-1</f>
+        <f t="shared" ref="AB17:AE17" si="79">AB3/X3-1</f>
         <v>5.482538490424238E-3</v>
       </c>
       <c r="AC17" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="79"/>
         <v>3.1476997578692156E-3</v>
       </c>
       <c r="AD17" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="79"/>
         <v>-1.7076023391812911E-2</v>
       </c>
       <c r="AE17" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="79"/>
         <v>-0.10433572919081846</v>
       </c>
       <c r="AF17" s="10">
-        <f t="shared" ref="AF17" si="66">AF3/AB3-1</f>
+        <f t="shared" ref="AF17" si="80">AF3/AB3-1</f>
         <v>-7.7233343292500756E-2</v>
       </c>
       <c r="AG17" s="10">
-        <f t="shared" ref="AG17" si="67">AG3/AC3-1</f>
+        <f t="shared" ref="AG17:AI17" si="81">AG3/AC3-1</f>
         <v>-9.3330115053503859E-2</v>
       </c>
       <c r="AH17" s="10">
-        <f t="shared" ref="AH17" si="68">AH3/AD3-1</f>
+        <f t="shared" ref="AH17:AI17" si="82">AH3/AD3-1</f>
         <v>-0.11970490242741549</v>
       </c>
-      <c r="AI17" s="10"/>
-      <c r="AJ17" s="10"/>
-      <c r="AK17" s="10"/>
-      <c r="AL17" s="10"/>
+      <c r="AI17" s="10">
+        <f t="shared" si="81"/>
+        <v>1.1303822590387425E-2</v>
+      </c>
+      <c r="AJ17" s="10">
+        <f t="shared" ref="AJ17" si="83">AJ3/AF3-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AK17" s="10">
+        <f t="shared" ref="AK17" si="84">AK3/AG3-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AL17" s="10">
+        <f t="shared" ref="AL17" si="85">AL3/AH3-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
       <c r="AN17" s="10"/>
       <c r="AO17" s="10">
         <f>AO3/AN3-1</f>
@@ -4279,67 +4436,67 @@
         <v>7.4731433909388079E-2</v>
       </c>
       <c r="AQ17" s="10">
-        <f t="shared" ref="AQ17:BB17" si="69">AQ3/AP3-1</f>
+        <f t="shared" ref="AQ17:BB17" si="86">AQ3/AP3-1</f>
         <v>-4.3817266150267153E-2</v>
       </c>
       <c r="AR17" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="86"/>
         <v>0.19076009945726269</v>
       </c>
       <c r="AS17" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="86"/>
         <v>4.8767344739323759E-2</v>
       </c>
       <c r="AT17" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="86"/>
         <v>9.6488974523656568E-2</v>
       </c>
       <c r="AU17" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="86"/>
         <v>2.8310912392370824E-3</v>
       </c>
       <c r="AV17" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="86"/>
         <v>-9.8380125384525563E-2</v>
       </c>
       <c r="AW17" s="10">
-        <f t="shared" si="69"/>
-        <v>-1.0559502472521576E-2</v>
+        <f t="shared" si="86"/>
+        <v>1.5156017188883375E-2</v>
       </c>
       <c r="AX17" s="10">
-        <f t="shared" si="69"/>
-        <v>4.9323439546049785E-2</v>
+        <f t="shared" si="86"/>
+        <v>4.4652235674905727E-2</v>
       </c>
       <c r="AY17" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="86"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AZ17" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="86"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BA17" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="86"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BB17" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="86"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BC17" s="10">
-        <f t="shared" ref="BC17" si="70">BC3/BB3-1</f>
+        <f t="shared" ref="BC17" si="87">BC3/BB3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BD17" s="10">
-        <f t="shared" ref="BD17" si="71">BD3/BC3-1</f>
+        <f t="shared" ref="BD17" si="88">BD3/BC3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BE17" s="10">
-        <f t="shared" ref="BE17" si="72">BE3/BD3-1</f>
+        <f t="shared" ref="BE17" si="89">BE3/BD3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BF17" s="10">
-        <f t="shared" ref="BF17" si="73">BF3/BE3-1</f>
+        <f t="shared" ref="BF17" si="90">BF3/BE3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -4348,19 +4505,19 @@
         <v>40</v>
       </c>
       <c r="C18" s="10">
-        <f t="shared" ref="C18:F18" si="74">C5/C3</f>
+        <f t="shared" ref="C18:F18" si="91">C5/C3</f>
         <v>0.43682469680264607</v>
       </c>
       <c r="D18" s="10">
-        <f t="shared" si="74"/>
+        <f t="shared" si="91"/>
         <v>0.42997428103811081</v>
       </c>
       <c r="E18" s="10">
-        <f t="shared" si="74"/>
+        <f t="shared" si="91"/>
         <v>0.4383348174532502</v>
       </c>
       <c r="F18" s="10">
-        <f t="shared" si="74"/>
+        <f t="shared" si="91"/>
         <v>0.44723669424864643</v>
       </c>
       <c r="G18" s="10">
@@ -4368,192 +4525,204 @@
         <v>0.44199839163650984</v>
       </c>
       <c r="H18" s="10">
-        <f t="shared" ref="H18:S18" si="75">H5/H3</f>
+        <f t="shared" ref="H18:S18" si="92">H5/H3</f>
         <v>0.43791337742692554</v>
       </c>
       <c r="I18" s="10">
-        <f t="shared" si="75"/>
+        <f t="shared" si="92"/>
         <v>0.45146186661117471</v>
       </c>
       <c r="J18" s="10">
-        <f t="shared" si="75"/>
+        <f t="shared" si="92"/>
         <v>0.45492930086410055</v>
       </c>
       <c r="K18" s="10">
-        <f t="shared" si="75"/>
+        <f t="shared" si="92"/>
         <v>0.45694183864915572</v>
       </c>
       <c r="L18" s="10">
-        <f t="shared" si="75"/>
+        <f t="shared" si="92"/>
         <v>0.4400542320356382</v>
       </c>
       <c r="M18" s="10">
-        <f t="shared" si="75"/>
+        <f t="shared" si="92"/>
         <v>0.44269596199524941</v>
       </c>
       <c r="N18" s="10">
-        <f t="shared" si="75"/>
+        <f t="shared" si="92"/>
         <v>0.37272295263741484</v>
       </c>
       <c r="O18" s="10">
-        <f t="shared" si="75"/>
+        <f t="shared" si="92"/>
         <v>0.44751746271474419</v>
       </c>
       <c r="P18" s="10">
-        <f t="shared" si="75"/>
+        <f t="shared" si="92"/>
         <v>0.43111269234190164</v>
       </c>
       <c r="Q18" s="10">
-        <f t="shared" si="75"/>
+        <f t="shared" si="92"/>
         <v>0.45563387081201118</v>
       </c>
       <c r="R18" s="10">
-        <f t="shared" si="75"/>
+        <f t="shared" si="92"/>
         <v>0.45811730395333766</v>
       </c>
       <c r="S18" s="10">
-        <f t="shared" si="75"/>
+        <f t="shared" si="92"/>
         <v>0.46505551926845201</v>
       </c>
       <c r="T18" s="10">
-        <f t="shared" ref="T18:U18" si="76">T5/T3</f>
+        <f t="shared" ref="T18:U18" si="93">T5/T3</f>
         <v>0.45901206304481817</v>
       </c>
       <c r="U18" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="93"/>
         <v>0.4661024744733695</v>
       </c>
       <c r="V18" s="10">
-        <f t="shared" ref="V18:W18" si="77">V5/V3</f>
+        <f t="shared" ref="V18:W18" si="94">V5/V3</f>
         <v>0.44981199934608468</v>
       </c>
       <c r="W18" s="10">
-        <f t="shared" si="77"/>
+        <f t="shared" si="94"/>
         <v>0.44257901789233073</v>
       </c>
       <c r="X18" s="10">
-        <f t="shared" ref="X18" si="78">X5/X3</f>
+        <f t="shared" ref="X18" si="95">X5/X3</f>
         <v>0.42891475779196397</v>
       </c>
       <c r="Y18" s="10">
-        <f t="shared" ref="Y18:AA18" si="79">Y5/Y3</f>
+        <f t="shared" ref="Y18:AA18" si="96">Y5/Y3</f>
         <v>0.43349475383373687</v>
       </c>
       <c r="Z18" s="10">
-        <f t="shared" si="79"/>
+        <f t="shared" si="96"/>
         <v>0.43625730994152045</v>
       </c>
       <c r="AA18" s="10">
-        <f t="shared" si="79"/>
+        <f t="shared" si="96"/>
         <v>0.44207434886776414</v>
       </c>
       <c r="AB18" s="10">
-        <f t="shared" ref="AB18" si="80">AB5/AB3</f>
+        <f t="shared" ref="AB18" si="97">AB5/AB3</f>
         <v>0.44599641469973111</v>
       </c>
       <c r="AC18" s="10">
-        <f t="shared" ref="AC18:AD18" si="81">AC5/AC3</f>
+        <f t="shared" ref="AC18:AD18" si="98">AC5/AC3</f>
         <v>0.44750181028240404</v>
       </c>
       <c r="AD18" s="10">
-        <f t="shared" si="81"/>
+        <f t="shared" si="98"/>
         <v>0.44693003331746789</v>
       </c>
       <c r="AE18" s="10">
-        <f t="shared" ref="AE18:AH18" si="82">AE5/AE3</f>
+        <f t="shared" ref="AE18:AH18" si="99">AE5/AE3</f>
         <v>0.45361981189058592</v>
       </c>
       <c r="AF18" s="10">
-        <f t="shared" si="82"/>
+        <f t="shared" si="99"/>
         <v>0.43621499109600131</v>
       </c>
       <c r="AG18" s="10">
-        <f t="shared" si="82"/>
+        <f t="shared" si="99"/>
         <v>0.41485491170467653</v>
       </c>
       <c r="AH18" s="10">
-        <f t="shared" si="82"/>
-        <v>0.45999999999999996</v>
-      </c>
-      <c r="AI18" s="10"/>
-      <c r="AJ18" s="10"/>
-      <c r="AK18" s="10"/>
-      <c r="AL18" s="10"/>
+        <f t="shared" si="99"/>
+        <v>0.40272145624943678</v>
+      </c>
+      <c r="AI18" s="10">
+        <f t="shared" ref="AI18:AL18" si="100">AI5/AI3</f>
+        <v>0.42175767918088736</v>
+      </c>
+      <c r="AJ18" s="10">
+        <f t="shared" si="100"/>
+        <v>0.43</v>
+      </c>
+      <c r="AK18" s="10">
+        <f t="shared" si="100"/>
+        <v>0.44</v>
+      </c>
+      <c r="AL18" s="10">
+        <f t="shared" si="100"/>
+        <v>0.45</v>
+      </c>
       <c r="AN18" s="10">
-        <f t="shared" ref="AN18" si="83">AN5/AN3</f>
+        <f t="shared" ref="AN18" si="101">AN5/AN3</f>
         <v>0.445764192139738</v>
       </c>
       <c r="AO18" s="10">
-        <f t="shared" ref="AO18" si="84">AO5/AO3</f>
+        <f t="shared" ref="AO18" si="102">AO5/AO3</f>
         <v>0.43838777921257244</v>
       </c>
       <c r="AP18" s="10">
-        <f t="shared" ref="AP18:BB18" si="85">AP5/AP3</f>
+        <f t="shared" ref="AP18:BB18" si="103">AP5/AP3</f>
         <v>0.44671114860546568</v>
       </c>
       <c r="AQ18" s="10">
-        <f t="shared" si="85"/>
+        <f t="shared" si="103"/>
         <v>0.43421650669732376</v>
       </c>
       <c r="AR18" s="10">
-        <f t="shared" si="85"/>
+        <f t="shared" si="103"/>
         <v>0.44820153576721</v>
       </c>
       <c r="AS18" s="10">
-        <f t="shared" si="85"/>
+        <f t="shared" si="103"/>
         <v>0.45983729394134021</v>
       </c>
       <c r="AT18" s="10">
-        <f t="shared" si="85"/>
+        <f t="shared" si="103"/>
         <v>0.43524610969014194</v>
       </c>
       <c r="AU18" s="10">
-        <f t="shared" si="85"/>
+        <f t="shared" si="103"/>
         <v>0.44560180678322497</v>
       </c>
       <c r="AV18" s="10">
-        <f t="shared" si="85"/>
+        <f t="shared" si="103"/>
         <v>0.42734673605562634</v>
       </c>
       <c r="AW18" s="10">
-        <f t="shared" si="85"/>
+        <f t="shared" si="103"/>
+        <v>0.43520566098982227</v>
+      </c>
+      <c r="AX18" s="10">
+        <f t="shared" si="103"/>
         <v>0.45</v>
       </c>
-      <c r="AX18" s="10">
-        <f t="shared" si="85"/>
-        <v>0.45999999999999996</v>
-      </c>
       <c r="AY18" s="10">
-        <f t="shared" si="85"/>
-        <v>0.45999999999999996</v>
+        <f t="shared" si="103"/>
+        <v>0.46</v>
       </c>
       <c r="AZ18" s="10">
-        <f t="shared" si="85"/>
+        <f t="shared" si="103"/>
         <v>0.46</v>
       </c>
       <c r="BA18" s="10">
-        <f t="shared" si="85"/>
+        <f t="shared" si="103"/>
         <v>0.46</v>
       </c>
       <c r="BB18" s="10">
-        <f t="shared" si="85"/>
+        <f t="shared" si="103"/>
         <v>0.46</v>
       </c>
       <c r="BC18" s="10">
-        <f t="shared" ref="BC18:BF18" si="86">BC5/BC3</f>
-        <v>0.46000000000000008</v>
+        <f t="shared" ref="BC18:BF18" si="104">BC5/BC3</f>
+        <v>0.46</v>
       </c>
       <c r="BD18" s="10">
-        <f t="shared" si="86"/>
+        <f t="shared" si="104"/>
         <v>0.46</v>
       </c>
       <c r="BE18" s="10">
-        <f t="shared" si="86"/>
+        <f t="shared" si="104"/>
         <v>0.46</v>
       </c>
       <c r="BF18" s="10">
-        <f t="shared" si="86"/>
-        <v>0.45999999999999996</v>
+        <f t="shared" si="104"/>
+        <v>0.46</v>
       </c>
     </row>
     <row r="19" spans="2:61" x14ac:dyDescent="0.3">
@@ -4561,19 +4730,19 @@
         <v>41</v>
       </c>
       <c r="C19" s="10">
-        <f t="shared" ref="C19:F19" si="87">C8/C3</f>
+        <f t="shared" ref="C19:F19" si="105">C8/C3</f>
         <v>0.12194046306504962</v>
       </c>
       <c r="D19" s="10">
-        <f t="shared" si="87"/>
+        <f t="shared" si="105"/>
         <v>0.10638297872340426</v>
       </c>
       <c r="E19" s="10">
-        <f t="shared" si="87"/>
+        <f t="shared" si="105"/>
         <v>0.13034283170080144</v>
       </c>
       <c r="F19" s="10">
-        <f t="shared" si="87"/>
+        <f t="shared" si="105"/>
         <v>0.12851159464705281</v>
       </c>
       <c r="G19" s="10">
@@ -4581,192 +4750,204 @@
         <v>0.13409730599115399</v>
       </c>
       <c r="H19" s="10">
-        <f t="shared" ref="H19:S19" si="88">H8/H3</f>
+        <f t="shared" ref="H19:S19" si="106">H8/H3</f>
         <v>0.10273095796885001</v>
       </c>
       <c r="I19" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="106"/>
         <v>0.12985121215274165</v>
       </c>
       <c r="J19" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="106"/>
         <v>0.12048311076197958</v>
       </c>
       <c r="K19" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="106"/>
         <v>0.14474671669793621</v>
       </c>
       <c r="L19" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="106"/>
         <v>0.11814836335463877</v>
       </c>
       <c r="M19" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="106"/>
         <v>0.11777513855898654</v>
       </c>
       <c r="N19" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="106"/>
         <v>-0.13274196103278948</v>
       </c>
       <c r="O19" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="106"/>
         <v>0.16669813101755709</v>
       </c>
       <c r="P19" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="106"/>
         <v>0.14053188650716</v>
       </c>
       <c r="Q19" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="106"/>
         <v>0.16201602780728011</v>
       </c>
       <c r="R19" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="106"/>
         <v>0.15497407647440051</v>
       </c>
       <c r="S19" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="106"/>
         <v>0.17341606792945788</v>
       </c>
       <c r="T19" s="10">
-        <f t="shared" ref="T19:U19" si="89">T8/T3</f>
+        <f t="shared" ref="T19:U19" si="107">T8/T3</f>
         <v>0.12802676763229726</v>
       </c>
       <c r="U19" s="10">
-        <f t="shared" si="89"/>
+        <f t="shared" si="107"/>
         <v>0.14984822003495538</v>
       </c>
       <c r="V19" s="10">
-        <f t="shared" ref="V19:W19" si="90">V8/V3</f>
+        <f t="shared" ref="V19:W19" si="108">V8/V3</f>
         <v>0.11999346084682033</v>
       </c>
       <c r="W19" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="108"/>
         <v>0.13360132419011586</v>
       </c>
       <c r="X19" s="10">
-        <f t="shared" ref="X19" si="91">X8/X3</f>
+        <f t="shared" ref="X19" si="109">X8/X3</f>
         <v>0.11918888471648517</v>
       </c>
       <c r="Y19" s="10">
-        <f t="shared" ref="Y19:AA19" si="92">Y8/Y3</f>
+        <f t="shared" ref="Y19:AA19" si="110">Y8/Y3</f>
         <v>0.11396287328490719</v>
       </c>
       <c r="Z19" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="110"/>
         <v>9.5204678362573097E-2</v>
       </c>
       <c r="AA19" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="110"/>
         <v>0.12396630342375763</v>
       </c>
       <c r="AB19" s="10">
-        <f t="shared" ref="AB19" si="93">AB8/AB3</f>
+        <f t="shared" ref="AB19" si="111">AB8/AB3</f>
         <v>0.1363161039737078</v>
       </c>
       <c r="AC19" s="10">
-        <f t="shared" ref="AC19:AD19" si="94">AC8/AC3</f>
+        <f t="shared" ref="AC19:AD19" si="112">AC8/AC3</f>
         <v>0.10749054630300105</v>
       </c>
       <c r="AD19" s="10">
-        <f t="shared" si="94"/>
+        <f t="shared" si="112"/>
         <v>0.12264001269236871</v>
       </c>
       <c r="AE19" s="10">
-        <f t="shared" ref="AE19:AH19" si="95">AE8/AE3</f>
+        <f t="shared" ref="AE19:AH19" si="113">AE8/AE3</f>
         <v>0.10432306497540772</v>
       </c>
       <c r="AF19" s="10">
-        <f t="shared" si="95"/>
+        <f t="shared" si="113"/>
         <v>0.1120284927958556</v>
       </c>
       <c r="AG19" s="10">
-        <f t="shared" si="95"/>
+        <f t="shared" si="113"/>
         <v>6.9926346614606436E-2</v>
       </c>
       <c r="AH19" s="10">
-        <f t="shared" si="95"/>
-        <v>8.6205280706497245E-2</v>
-      </c>
-      <c r="AI19" s="10"/>
-      <c r="AJ19" s="10"/>
-      <c r="AK19" s="10"/>
-      <c r="AL19" s="10"/>
+        <f t="shared" si="113"/>
+        <v>2.8926736955934035E-2</v>
+      </c>
+      <c r="AI19" s="10">
+        <f t="shared" ref="AI19:AL19" si="114">AI8/AI3</f>
+        <v>7.909556313993174E-2</v>
+      </c>
+      <c r="AJ19" s="10">
+        <f t="shared" si="114"/>
+        <v>9.6634288489558046E-2</v>
+      </c>
+      <c r="AK19" s="10">
+        <f t="shared" si="114"/>
+        <v>9.4054590156232867E-2</v>
+      </c>
+      <c r="AL19" s="10">
+        <f t="shared" si="114"/>
+        <v>9.167634071741701E-2</v>
+      </c>
       <c r="AN19" s="10">
-        <f t="shared" ref="AN19" si="96">AN8/AN3</f>
+        <f t="shared" ref="AN19" si="115">AN8/AN3</f>
         <v>0.13825327510917029</v>
       </c>
       <c r="AO19" s="10">
-        <f t="shared" ref="AO19" si="97">AO8/AO3</f>
+        <f t="shared" ref="AO19" si="116">AO8/AO3</f>
         <v>0.12212544989971701</v>
       </c>
       <c r="AP19" s="10">
-        <f t="shared" ref="AP19:BB19" si="98">AP8/AP3</f>
+        <f t="shared" ref="AP19:BB19" si="117">AP8/AP3</f>
         <v>0.12199299537285579</v>
       </c>
       <c r="AQ19" s="10">
-        <f t="shared" si="98"/>
+        <f t="shared" si="117"/>
         <v>8.3282089671951443E-2</v>
       </c>
       <c r="AR19" s="10">
-        <f t="shared" si="98"/>
+        <f t="shared" si="117"/>
         <v>0.15575463649018814</v>
       </c>
       <c r="AS19" s="10">
-        <f t="shared" si="98"/>
+        <f t="shared" si="117"/>
         <v>0.14290301862556198</v>
       </c>
       <c r="AT19" s="10">
-        <f t="shared" si="98"/>
+        <f t="shared" si="117"/>
         <v>0.11548899779370131</v>
       </c>
       <c r="AU19" s="10">
-        <f t="shared" si="98"/>
+        <f t="shared" si="117"/>
         <v>0.12287294108484872</v>
       </c>
       <c r="AV19" s="10">
-        <f t="shared" si="98"/>
+        <f t="shared" si="117"/>
         <v>7.9941264117126265E-2</v>
       </c>
       <c r="AW19" s="10">
-        <f t="shared" si="98"/>
-        <v>0.11370995198603231</v>
+        <f t="shared" si="117"/>
+        <v>9.0437324482045153E-2</v>
       </c>
       <c r="AX19" s="10">
-        <f t="shared" si="98"/>
-        <v>0.13293968178036603</v>
+        <f t="shared" si="117"/>
+        <v>0.12367994909387087</v>
       </c>
       <c r="AY19" s="10">
-        <f t="shared" si="98"/>
-        <v>0.13754279475550457</v>
+        <f t="shared" si="117"/>
+        <v>0.13826868794641717</v>
       </c>
       <c r="AZ19" s="10">
-        <f t="shared" si="98"/>
-        <v>0.13754279475550465</v>
+        <f t="shared" si="117"/>
+        <v>0.13826868794641717</v>
       </c>
       <c r="BA19" s="10">
-        <f t="shared" si="98"/>
-        <v>0.1375427947555046</v>
+        <f t="shared" si="117"/>
+        <v>0.13826868794641708</v>
       </c>
       <c r="BB19" s="10">
-        <f t="shared" si="98"/>
-        <v>0.13754279475550465</v>
+        <f t="shared" si="117"/>
+        <v>0.13826868794641703</v>
       </c>
       <c r="BC19" s="10">
-        <f t="shared" ref="BC19:BF19" si="99">BC8/BC3</f>
-        <v>0.13754279475550465</v>
+        <f t="shared" ref="BC19:BF19" si="118">BC8/BC3</f>
+        <v>0.13826868794641711</v>
       </c>
       <c r="BD19" s="10">
-        <f t="shared" si="99"/>
-        <v>0.13754279475550463</v>
+        <f t="shared" si="118"/>
+        <v>0.13826868794641711</v>
       </c>
       <c r="BE19" s="10">
-        <f t="shared" si="99"/>
-        <v>0.13754279475550465</v>
+        <f t="shared" si="118"/>
+        <v>0.13826868794641708</v>
       </c>
       <c r="BF19" s="10">
-        <f t="shared" si="99"/>
-        <v>0.1375427947555046</v>
+        <f t="shared" si="118"/>
+        <v>0.13826868794641706</v>
       </c>
       <c r="BH19" t="s">
         <v>45</v>
@@ -4780,19 +4961,19 @@
         <v>42</v>
       </c>
       <c r="C20" s="10">
-        <f t="shared" ref="C20:F20" si="100">C6/C3</f>
+        <f t="shared" ref="C20:F20" si="119">C6/C3</f>
         <v>9.4266813671444322E-2</v>
       </c>
       <c r="D20" s="10">
-        <f t="shared" si="100"/>
+        <f t="shared" si="119"/>
         <v>0.10252513444002806</v>
       </c>
       <c r="E20" s="10">
-        <f t="shared" si="100"/>
+        <f t="shared" si="119"/>
         <v>9.5948352626892247E-2</v>
       </c>
       <c r="F20" s="10">
-        <f t="shared" si="100"/>
+        <f t="shared" si="119"/>
         <v>0.1004188374706303</v>
       </c>
       <c r="G20" s="10">
@@ -4800,192 +4981,204 @@
         <v>9.6903900281463617E-2</v>
       </c>
       <c r="H20" s="10">
-        <f t="shared" ref="H20:S20" si="101">H6/H3</f>
+        <f t="shared" ref="H20:S20" si="120">H6/H3</f>
         <v>9.707702154896522E-2</v>
       </c>
       <c r="I20" s="10">
-        <f t="shared" si="101"/>
+        <f t="shared" si="120"/>
         <v>9.0001040474456354E-2</v>
       </c>
       <c r="J20" s="10">
-        <f t="shared" si="101"/>
+        <f t="shared" si="120"/>
         <v>9.9567949725058918E-2</v>
       </c>
       <c r="K20" s="10">
-        <f t="shared" si="101"/>
+        <f t="shared" si="120"/>
         <v>9.5497185741088175E-2</v>
       </c>
       <c r="L20" s="10">
-        <f t="shared" si="101"/>
+        <f t="shared" si="120"/>
         <v>8.5318613209374394E-2</v>
       </c>
       <c r="M20" s="10">
-        <f t="shared" si="101"/>
+        <f t="shared" si="120"/>
         <v>8.6104513064133012E-2</v>
       </c>
       <c r="N20" s="10">
-        <f t="shared" si="101"/>
+        <f t="shared" si="120"/>
         <v>0.1303659116109615</v>
       </c>
       <c r="O20" s="10">
-        <f t="shared" si="101"/>
+        <f t="shared" si="120"/>
         <v>6.390409665848594E-2</v>
       </c>
       <c r="P20" s="10">
-        <f t="shared" si="101"/>
+        <f t="shared" si="120"/>
         <v>6.4840345103620037E-2</v>
       </c>
       <c r="Q20" s="10">
-        <f t="shared" si="101"/>
+        <f t="shared" si="120"/>
         <v>6.8649222747899974E-2</v>
       </c>
       <c r="R20" s="10">
-        <f t="shared" si="101"/>
+        <f t="shared" si="120"/>
         <v>8.0767984445884636E-2</v>
       </c>
       <c r="S20" s="10">
-        <f t="shared" si="101"/>
+        <f t="shared" si="120"/>
         <v>7.4951012410189422E-2</v>
       </c>
       <c r="T20" s="10">
-        <f t="shared" ref="T20:U20" si="102">T6/T3</f>
+        <f t="shared" ref="T20:U20" si="121">T6/T3</f>
         <v>8.954829620498371E-2</v>
       </c>
       <c r="U20" s="10">
-        <f t="shared" si="102"/>
+        <f t="shared" si="121"/>
         <v>7.8557630392788153E-2</v>
       </c>
       <c r="V20" s="10">
-        <f t="shared" ref="V20:W20" si="103">V6/V3</f>
+        <f t="shared" ref="V20:W20" si="122">V6/V3</f>
         <v>8.6725519045283639E-2</v>
       </c>
       <c r="W20" s="10">
-        <f t="shared" si="103"/>
+        <f t="shared" si="122"/>
         <v>7.4328052337037917E-2</v>
       </c>
       <c r="X20" s="10">
-        <f t="shared" ref="X20" si="104">X6/X3</f>
+        <f t="shared" ref="X20" si="123">X6/X3</f>
         <v>8.2763800225309797E-2</v>
       </c>
       <c r="Y20" s="10">
-        <f t="shared" ref="Y20:AA20" si="105">Y6/Y3</f>
+        <f t="shared" ref="Y20:AA20" si="124">Y6/Y3</f>
         <v>7.4495560936238908E-2</v>
       </c>
       <c r="Z20" s="10">
-        <f t="shared" si="105"/>
+        <f t="shared" si="124"/>
         <v>8.5146198830409359E-2</v>
       </c>
       <c r="AA20" s="10">
-        <f t="shared" si="105"/>
+        <f t="shared" si="124"/>
         <v>8.2618440374062907E-2</v>
       </c>
       <c r="AB20" s="10">
-        <f t="shared" ref="AB20" si="106">AB6/AB3</f>
+        <f t="shared" ref="AB20" si="125">AB6/AB3</f>
         <v>8.3208843740663285E-2</v>
       </c>
       <c r="AC20" s="10">
-        <f t="shared" ref="AC20:AD20" si="107">AC6/AC3</f>
+        <f t="shared" ref="AC20:AD20" si="126">AC6/AC3</f>
         <v>8.1342022688872792E-2</v>
       </c>
       <c r="AD20" s="10">
-        <f t="shared" si="107"/>
+        <f t="shared" si="126"/>
         <v>8.6546089163890214E-2</v>
       </c>
       <c r="AE20" s="10">
-        <f t="shared" ref="AE20:AH20" si="108">AE6/AE3</f>
+        <f t="shared" ref="AE20:AH20" si="127">AE6/AE3</f>
         <v>0.10578997325049616</v>
       </c>
       <c r="AF20" s="10">
-        <f t="shared" si="108"/>
+        <f t="shared" si="127"/>
         <v>9.0820786789703734E-2</v>
       </c>
       <c r="AG20" s="10">
-        <f t="shared" si="108"/>
+        <f t="shared" si="127"/>
         <v>9.6548052178542912E-2</v>
       </c>
       <c r="AH20" s="10">
-        <f t="shared" si="108"/>
+        <f t="shared" si="127"/>
         <v>0.11291340001802289</v>
       </c>
-      <c r="AI20" s="10"/>
-      <c r="AJ20" s="10"/>
-      <c r="AK20" s="10"/>
-      <c r="AL20" s="10"/>
+      <c r="AI20" s="10">
+        <f t="shared" ref="AI20:AL20" si="128">AI6/AI3</f>
+        <v>0.10136518771331059</v>
+      </c>
+      <c r="AJ20" s="10">
+        <f t="shared" si="128"/>
+        <v>0.1</v>
+      </c>
+      <c r="AK20" s="10">
+        <f t="shared" si="128"/>
+        <v>0.1</v>
+      </c>
+      <c r="AL20" s="10">
+        <f t="shared" si="128"/>
+        <v>9.9999999999999992E-2</v>
+      </c>
       <c r="AN20" s="10">
-        <f t="shared" ref="AN20" si="109">AN6/AN3</f>
+        <f t="shared" ref="AN20" si="129">AN6/AN3</f>
         <v>9.726346433770014E-2</v>
       </c>
       <c r="AO20" s="10">
-        <f t="shared" ref="AO20" si="110">AO6/AO3</f>
+        <f t="shared" ref="AO20" si="130">AO6/AO3</f>
         <v>9.8277330549221095E-2</v>
       </c>
       <c r="AP20" s="10">
-        <f t="shared" ref="AP20:BB20" si="111">AP6/AP3</f>
+        <f t="shared" ref="AP20:BB20" si="131">AP6/AP3</f>
         <v>9.5942940409540614E-2</v>
       </c>
       <c r="AQ20" s="10">
-        <f t="shared" si="111"/>
+        <f t="shared" si="131"/>
         <v>9.6035077400208543E-2</v>
       </c>
       <c r="AR20" s="10">
-        <f t="shared" si="111"/>
+        <f t="shared" si="131"/>
         <v>6.9917822982621586E-2</v>
       </c>
       <c r="AS20" s="10">
-        <f t="shared" si="111"/>
+        <f t="shared" si="131"/>
         <v>8.2423463926354093E-2</v>
       </c>
       <c r="AT20" s="10">
-        <f t="shared" si="111"/>
+        <f t="shared" si="131"/>
         <v>7.9270554698635212E-2</v>
       </c>
       <c r="AU20" s="10">
-        <f t="shared" si="111"/>
+        <f t="shared" si="131"/>
         <v>8.3427436626299603E-2</v>
       </c>
       <c r="AV20" s="10">
-        <f t="shared" si="111"/>
+        <f t="shared" si="131"/>
         <v>0.10125461573344274</v>
       </c>
       <c r="AW20" s="10">
-        <f t="shared" si="111"/>
-        <v>9.0000000000000011E-2</v>
+        <f t="shared" si="131"/>
+        <v>0.10034034689005902</v>
       </c>
       <c r="AX20" s="10">
-        <f t="shared" si="111"/>
+        <f t="shared" si="131"/>
         <v>0.09</v>
       </c>
       <c r="AY20" s="10">
-        <f t="shared" si="111"/>
+        <f t="shared" si="131"/>
+        <v>0.09</v>
+      </c>
+      <c r="AZ20" s="10">
+        <f t="shared" si="131"/>
+        <v>0.09</v>
+      </c>
+      <c r="BA20" s="10">
+        <f t="shared" si="131"/>
+        <v>0.09</v>
+      </c>
+      <c r="BB20" s="10">
+        <f t="shared" si="131"/>
         <v>8.9999999999999983E-2</v>
       </c>
-      <c r="AZ20" s="10">
-        <f t="shared" si="111"/>
+      <c r="BC20" s="10">
+        <f t="shared" ref="BC20:BF20" si="132">BC6/BC3</f>
         <v>0.09</v>
       </c>
-      <c r="BA20" s="10">
-        <f t="shared" si="111"/>
-        <v>9.0000000000000011E-2</v>
-      </c>
-      <c r="BB20" s="10">
-        <f t="shared" si="111"/>
-        <v>9.0000000000000011E-2</v>
-      </c>
-      <c r="BC20" s="10">
-        <f t="shared" ref="BC20:BF20" si="112">BC6/BC3</f>
+      <c r="BD20" s="10">
+        <f t="shared" si="132"/>
         <v>0.09</v>
       </c>
-      <c r="BD20" s="10">
-        <f t="shared" si="112"/>
-        <v>9.0000000000000011E-2</v>
-      </c>
       <c r="BE20" s="10">
-        <f t="shared" si="112"/>
+        <f t="shared" si="132"/>
         <v>0.09</v>
       </c>
       <c r="BF20" s="10">
-        <f t="shared" si="112"/>
-        <v>0.09</v>
+        <f t="shared" si="132"/>
+        <v>8.9999999999999983E-2</v>
       </c>
       <c r="BH20" t="s">
         <v>46</v>
@@ -5003,192 +5196,204 @@
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
       <c r="G21" s="10">
-        <f t="shared" ref="G21" si="113">G7/C7-1</f>
+        <f t="shared" ref="G21" si="133">G7/C7-1</f>
         <v>4.8975512243877972E-2</v>
       </c>
       <c r="H21" s="10">
-        <f t="shared" ref="H21" si="114">H7/D7-1</f>
+        <f t="shared" ref="H21" si="134">H7/D7-1</f>
         <v>0.18032786885245899</v>
       </c>
       <c r="I21" s="10">
-        <f t="shared" ref="I21" si="115">I7/E7-1</f>
+        <f t="shared" ref="I21" si="135">I7/E7-1</f>
         <v>0.16850393700787403</v>
       </c>
       <c r="J21" s="10">
-        <f t="shared" ref="J21" si="116">J7/F7-1</f>
+        <f t="shared" ref="J21" si="136">J7/F7-1</f>
         <v>0.11932615816565284</v>
       </c>
       <c r="K21" s="10">
-        <f t="shared" ref="K21" si="117">K7/G7-1</f>
+        <f t="shared" ref="K21" si="137">K7/G7-1</f>
         <v>0.10052405907575035</v>
       </c>
       <c r="L21" s="10">
-        <f t="shared" ref="L21" si="118">L7/H7-1</f>
+        <f t="shared" ref="L21" si="138">L7/H7-1</f>
         <v>9.4534050179211571E-2</v>
       </c>
       <c r="M21" s="10">
-        <f t="shared" ref="M21" si="119">M7/I7-1</f>
+        <f t="shared" ref="M21" si="139">M7/I7-1</f>
         <v>8.4007187780772652E-2</v>
       </c>
       <c r="N21" s="10">
-        <f t="shared" ref="N21" si="120">N7/J7-1</f>
+        <f t="shared" ref="N21" si="140">N7/J7-1</f>
         <v>-1.0033444816053505E-2</v>
       </c>
       <c r="O21" s="10">
-        <f t="shared" ref="O21" si="121">O7/K7-1</f>
+        <f t="shared" ref="O21" si="141">O7/K7-1</f>
         <v>-5.1948051948051965E-3</v>
       </c>
       <c r="P21" s="10">
-        <f t="shared" ref="P21" si="122">P7/L7-1</f>
+        <f t="shared" ref="P21" si="142">P7/L7-1</f>
         <v>3.8886614817846832E-2</v>
       </c>
       <c r="Q21" s="10">
-        <f t="shared" ref="Q21:R21" si="123">Q7/M7-1</f>
+        <f t="shared" ref="Q21:R21" si="143">Q7/M7-1</f>
         <v>-3.4397016162453387E-2</v>
       </c>
       <c r="R21" s="10">
-        <f t="shared" si="123"/>
+        <f t="shared" si="143"/>
         <v>0.15920608108108114</v>
       </c>
       <c r="S21" s="10">
-        <f t="shared" ref="S21:AA21" si="124">S7/O7-1</f>
+        <f t="shared" ref="S21:AA21" si="144">S7/O7-1</f>
         <v>0.15491731940818099</v>
       </c>
       <c r="T21" s="10">
-        <f t="shared" si="124"/>
+        <f t="shared" si="144"/>
         <v>8.0378250591016442E-2</v>
       </c>
       <c r="U21" s="10">
-        <f t="shared" si="124"/>
+        <f t="shared" si="144"/>
         <v>0.10901287553648076</v>
       </c>
       <c r="V21" s="10">
-        <f t="shared" si="124"/>
+        <f t="shared" si="144"/>
         <v>8.3424408014571849E-2</v>
       </c>
       <c r="W21" s="10">
-        <f t="shared" si="124"/>
+        <f t="shared" si="144"/>
         <v>0.12170308967596077</v>
       </c>
       <c r="X21" s="10">
-        <f t="shared" ref="X21" si="125">X7/T7-1</f>
+        <f t="shared" ref="X21" si="145">X7/T7-1</f>
         <v>0.10211524434719177</v>
       </c>
       <c r="Y21" s="10">
-        <f t="shared" si="124"/>
+        <f t="shared" si="144"/>
         <v>0.17492260061919507</v>
       </c>
       <c r="Z21" s="10">
-        <f t="shared" si="124"/>
+        <f t="shared" si="144"/>
         <v>0.10356422326832559</v>
       </c>
       <c r="AA21" s="10">
-        <f t="shared" si="124"/>
+        <f t="shared" si="144"/>
         <v>2.3513604299630453E-2</v>
       </c>
       <c r="AB21" s="10">
-        <f t="shared" ref="AB21:AE21" si="126">AB7/X7-1</f>
+        <f t="shared" ref="AB21:AE21" si="146">AB7/X7-1</f>
         <v>3.3090668431501324E-3</v>
       </c>
       <c r="AC21" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="146"/>
         <v>5.895915678524366E-2</v>
       </c>
       <c r="AD21" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="146"/>
         <v>-8.6837294332723913E-2</v>
       </c>
       <c r="AE21" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="146"/>
         <v>-7.3843124384640579E-2</v>
       </c>
       <c r="AF21" s="10">
-        <f t="shared" ref="AF21" si="127">AF7/AB7-1</f>
+        <f t="shared" ref="AF21" si="147">AF7/AB7-1</f>
         <v>-4.9142480211081807E-2</v>
       </c>
       <c r="AG21" s="10">
-        <f t="shared" ref="AG21" si="128">AG7/AC7-1</f>
+        <f t="shared" ref="AG21:AI21" si="148">AG7/AC7-1</f>
         <v>-0.12939346811819596</v>
       </c>
       <c r="AH21" s="10">
-        <f t="shared" ref="AH21" si="129">AH7/AD7-1</f>
+        <f t="shared" ref="AH21:AI21" si="149">AH7/AD7-1</f>
         <v>-3.4034034034034044E-2</v>
       </c>
-      <c r="AI21" s="10"/>
-      <c r="AJ21" s="10"/>
-      <c r="AK21" s="10"/>
-      <c r="AL21" s="10"/>
+      <c r="AI21" s="10">
+        <f t="shared" si="148"/>
+        <v>2.1261516654855761E-3</v>
+      </c>
+      <c r="AJ21" s="10">
+        <f t="shared" ref="AJ21" si="150">AJ7/AF7-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AK21" s="10">
+        <f t="shared" ref="AK21" si="151">AK7/AG7-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AL21" s="10">
+        <f t="shared" ref="AL21" si="152">AL7/AH7-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
       <c r="AN21" s="10"/>
       <c r="AO21" s="10">
-        <f t="shared" ref="AO21" si="130">AO7/AN7-1</f>
+        <f t="shared" ref="AO21" si="153">AO7/AN7-1</f>
         <v>9.8587648850733789E-2</v>
       </c>
       <c r="AP21" s="10">
-        <f t="shared" ref="AP21:BB21" si="131">AP7/AO7-1</f>
+        <f t="shared" ref="AP21:BB21" si="154">AP7/AO7-1</f>
         <v>0.12793042601462057</v>
       </c>
       <c r="AQ21" s="10">
-        <f t="shared" si="131"/>
+        <f t="shared" si="154"/>
         <v>6.5370432450553073E-2</v>
       </c>
       <c r="AR21" s="10">
-        <f t="shared" si="131"/>
+        <f t="shared" si="154"/>
         <v>3.9542689322425106E-2</v>
       </c>
       <c r="AS21" s="10">
-        <f t="shared" si="131"/>
+        <f t="shared" si="154"/>
         <v>0.10523660579154481</v>
       </c>
       <c r="AT21" s="10">
-        <f t="shared" si="131"/>
+        <f t="shared" si="154"/>
         <v>0.12442943217089653</v>
       </c>
       <c r="AU21" s="10">
-        <f t="shared" si="131"/>
+        <f t="shared" si="154"/>
         <v>-2.1109036291304673E-3</v>
       </c>
       <c r="AV21" s="10">
-        <f t="shared" si="131"/>
+        <f t="shared" si="154"/>
         <v>-7.257342771133346E-2</v>
       </c>
       <c r="AW21" s="10">
-        <f t="shared" si="131"/>
-        <v>-1.0000000000000009E-2</v>
+        <f t="shared" si="154"/>
+        <v>8.0507062022985298E-3</v>
       </c>
       <c r="AX21" s="10">
-        <f t="shared" si="131"/>
+        <f t="shared" si="154"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY21" s="10">
-        <f t="shared" si="131"/>
+        <f t="shared" si="154"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ21" s="10">
-        <f t="shared" si="131"/>
+        <f t="shared" si="154"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BA21" s="10">
-        <f t="shared" si="131"/>
+        <f t="shared" si="154"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BB21" s="10">
-        <f t="shared" si="131"/>
+        <f t="shared" si="154"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BC21" s="10">
-        <f t="shared" ref="BC21" si="132">BC7/BB7-1</f>
+        <f t="shared" ref="BC21" si="155">BC7/BB7-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BD21" s="10">
-        <f t="shared" ref="BD21" si="133">BD7/BC7-1</f>
+        <f t="shared" ref="BD21" si="156">BD7/BC7-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BE21" s="10">
-        <f t="shared" ref="BE21" si="134">BE7/BD7-1</f>
+        <f t="shared" ref="BE21" si="157">BE7/BD7-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BF21" s="10">
-        <f t="shared" ref="BF21" si="135">BF7/BE7-1</f>
+        <f t="shared" ref="BF21" si="158">BF7/BE7-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BH21" t="s">
@@ -5196,7 +5401,7 @@
       </c>
       <c r="BI21" s="5">
         <f>NPV(BI20,AV13:FM13)</f>
-        <v>77220.823409649951</v>
+        <v>75906.028284662112</v>
       </c>
     </row>
     <row r="22" spans="2:61" x14ac:dyDescent="0.3">
@@ -5204,19 +5409,19 @@
         <v>32</v>
       </c>
       <c r="C22" s="10">
-        <f t="shared" ref="C22:F22" si="136">C12/C11</f>
+        <f t="shared" ref="C22:F22" si="159">C12/C11</f>
         <v>0.11380597014925373</v>
       </c>
       <c r="D22" s="10">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>0.12741751990898748</v>
       </c>
       <c r="E22" s="10">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>1.7931034482758621</v>
       </c>
       <c r="F22" s="10">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>6.4197530864197536E-2</v>
       </c>
       <c r="G22" s="10">
@@ -5224,199 +5429,211 @@
         <v>0.14015748031496064</v>
       </c>
       <c r="H22" s="10">
-        <f t="shared" ref="H22:S22" si="137">H12/H11</f>
+        <f t="shared" ref="H22:S22" si="160">H12/H11</f>
         <v>0.15045135406218657</v>
       </c>
       <c r="I22" s="10">
-        <f t="shared" si="137"/>
+        <f t="shared" si="160"/>
         <v>0.14717273431448488</v>
       </c>
       <c r="J22" s="10">
-        <f t="shared" si="137"/>
+        <f t="shared" si="160"/>
         <v>0.20434432823813356</v>
       </c>
       <c r="K22" s="10">
-        <f t="shared" si="137"/>
+        <f t="shared" si="160"/>
         <v>0.12427930813581038</v>
       </c>
       <c r="L22" s="10">
-        <f t="shared" si="137"/>
+        <f t="shared" si="160"/>
         <v>0.10728582866293035</v>
       </c>
       <c r="M22" s="10">
-        <f t="shared" si="137"/>
+        <f t="shared" si="160"/>
         <v>3.8592508513053347E-2</v>
       </c>
       <c r="N22" s="10">
-        <f t="shared" si="137"/>
+        <f t="shared" si="160"/>
         <v>1.7412935323383085E-2</v>
       </c>
       <c r="O22" s="10">
-        <f t="shared" si="137"/>
+        <f t="shared" si="160"/>
         <v>0.11486880466472303</v>
       </c>
       <c r="P22" s="10">
-        <f t="shared" si="137"/>
+        <f t="shared" si="160"/>
         <v>0.1407967032967033</v>
       </c>
       <c r="Q22" s="10">
-        <f t="shared" si="137"/>
+        <f t="shared" si="160"/>
         <v>0.11430317848410758</v>
       </c>
       <c r="R22" s="10">
-        <f t="shared" si="137"/>
+        <f t="shared" si="160"/>
         <v>0.18608414239482202</v>
       </c>
       <c r="S22" s="10">
-        <f t="shared" si="137"/>
+        <f t="shared" si="160"/>
         <v>0.11016144349477683</v>
       </c>
       <c r="T22" s="10">
-        <f t="shared" ref="T22:U22" si="138">T12/T11</f>
+        <f t="shared" ref="T22:U22" si="161">T12/T11</f>
         <v>0.10926049300466356</v>
       </c>
       <c r="U22" s="10">
-        <f t="shared" si="138"/>
+        <f t="shared" si="161"/>
         <v>0.16407185628742516</v>
       </c>
       <c r="V22" s="10">
-        <f t="shared" ref="V22:W22" si="139">V12/V11</f>
+        <f t="shared" ref="V22:W22" si="162">V12/V11</f>
         <v>-4.730713245997089E-2</v>
       </c>
       <c r="W22" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="162"/>
         <v>0.19693654266958424</v>
       </c>
       <c r="X22" s="10">
-        <f t="shared" ref="X22" si="140">X12/X11</f>
+        <f t="shared" ref="X22" si="163">X12/X11</f>
         <v>0.19333333333333333</v>
       </c>
       <c r="Y22" s="10">
-        <f t="shared" ref="Y22:AA22" si="141">Y12/Y11</f>
+        <f t="shared" ref="Y22:AA22" si="164">Y12/Y11</f>
         <v>0.16046039268788084</v>
       </c>
       <c r="Z22" s="10">
-        <f t="shared" si="141"/>
+        <f t="shared" si="164"/>
         <v>0.1725521669341894</v>
       </c>
       <c r="AA22" s="10">
-        <f t="shared" si="141"/>
+        <f t="shared" si="164"/>
         <v>0.12014563106796117</v>
       </c>
       <c r="AB22" s="10">
-        <f t="shared" ref="AB22" si="142">AB12/AB11</f>
+        <f t="shared" ref="AB22" si="165">AB12/AB11</f>
         <v>0.17898022892819979</v>
       </c>
       <c r="AC22" s="10">
-        <f t="shared" ref="AC22:AD22" si="143">AC12/AC11</f>
+        <f t="shared" ref="AC22:AD22" si="166">AC12/AC11</f>
         <v>0.16524216524216523</v>
       </c>
       <c r="AD22" s="10">
-        <f t="shared" si="143"/>
+        <f t="shared" si="166"/>
         <v>0.13093858632676708</v>
       </c>
       <c r="AE22" s="10">
-        <f t="shared" ref="AE22:AH22" si="144">AE12/AE11</f>
+        <f t="shared" ref="AE22:AH22" si="167">AE12/AE11</f>
         <v>0.19586840091813312</v>
       </c>
       <c r="AF22" s="10">
-        <f t="shared" si="144"/>
+        <f t="shared" si="167"/>
         <v>0.1786723163841808</v>
       </c>
       <c r="AG22" s="10">
-        <f t="shared" si="144"/>
+        <f t="shared" si="167"/>
         <v>5.9241706161137442E-2</v>
       </c>
       <c r="AH22" s="10">
-        <f t="shared" si="144"/>
-        <v>0.11220402256664082</v>
-      </c>
-      <c r="AI22" s="10"/>
-      <c r="AJ22" s="10"/>
-      <c r="AK22" s="10"/>
-      <c r="AL22" s="10"/>
+        <f t="shared" si="167"/>
+        <v>0.33647798742138363</v>
+      </c>
+      <c r="AI22" s="10">
+        <f t="shared" ref="AI22:AL22" si="168">AI12/AI11</f>
+        <v>0.21149674620390455</v>
+      </c>
+      <c r="AJ22" s="10">
+        <f t="shared" si="168"/>
+        <v>0.17</v>
+      </c>
+      <c r="AK22" s="10">
+        <f t="shared" si="168"/>
+        <v>0.17</v>
+      </c>
+      <c r="AL22" s="10">
+        <f t="shared" si="168"/>
+        <v>0.17</v>
+      </c>
       <c r="AN22" s="10">
-        <f t="shared" ref="AN22" si="145">AN12/AN11</f>
+        <f t="shared" ref="AN22" si="169">AN12/AN11</f>
         <v>0.13221449038067951</v>
       </c>
       <c r="AO22" s="10">
-        <f t="shared" ref="AO22" si="146">AO12/AO11</f>
+        <f t="shared" ref="AO22" si="170">AO12/AO11</f>
         <v>0.55293573740175683</v>
       </c>
       <c r="AP22" s="10">
-        <f t="shared" ref="AP22:BB22" si="147">AP12/AP11</f>
+        <f t="shared" ref="AP22:BB22" si="171">AP12/AP11</f>
         <v>0.16079983336804832</v>
       </c>
       <c r="AQ22" s="10">
-        <f t="shared" si="147"/>
+        <f t="shared" si="171"/>
         <v>0.12054035330793211</v>
       </c>
       <c r="AR22" s="10">
-        <f t="shared" si="147"/>
+        <f t="shared" si="171"/>
         <v>0.14021918630836211</v>
       </c>
       <c r="AS22" s="10">
-        <f t="shared" si="147"/>
+        <f t="shared" si="171"/>
         <v>9.0963764847391368E-2</v>
       </c>
       <c r="AT22" s="10">
-        <f t="shared" si="147"/>
+        <f t="shared" si="171"/>
         <v>0.18238993710691823</v>
       </c>
       <c r="AU22" s="10">
-        <f t="shared" si="147"/>
+        <f t="shared" si="171"/>
         <v>0.14925373134328357</v>
       </c>
       <c r="AV22" s="10">
-        <f t="shared" si="147"/>
+        <f t="shared" si="171"/>
         <v>0.17142857142857143</v>
       </c>
       <c r="AW22" s="10">
-        <f t="shared" si="147"/>
+        <f t="shared" si="171"/>
+        <v>0.17900969552504029</v>
+      </c>
+      <c r="AX22" s="10">
+        <f t="shared" si="171"/>
         <v>0.17</v>
       </c>
-      <c r="AX22" s="10">
-        <f t="shared" si="147"/>
+      <c r="AY22" s="10">
+        <f t="shared" si="171"/>
         <v>0.17</v>
       </c>
-      <c r="AY22" s="10">
-        <f t="shared" si="147"/>
+      <c r="AZ22" s="10">
+        <f t="shared" si="171"/>
         <v>0.17</v>
       </c>
-      <c r="AZ22" s="10">
-        <f t="shared" si="147"/>
+      <c r="BA22" s="10">
+        <f t="shared" si="171"/>
         <v>0.17</v>
       </c>
-      <c r="BA22" s="10">
-        <f t="shared" si="147"/>
+      <c r="BB22" s="10">
+        <f t="shared" si="171"/>
+        <v>0.16999999999999998</v>
+      </c>
+      <c r="BC22" s="10">
+        <f t="shared" ref="BC22:BF22" si="172">BC12/BC11</f>
         <v>0.17</v>
       </c>
-      <c r="BB22" s="10">
-        <f t="shared" si="147"/>
+      <c r="BD22" s="10">
+        <f t="shared" si="172"/>
         <v>0.17</v>
       </c>
-      <c r="BC22" s="10">
-        <f t="shared" ref="BC22:BF22" si="148">BC12/BC11</f>
+      <c r="BE22" s="10">
+        <f t="shared" si="172"/>
         <v>0.17</v>
       </c>
-      <c r="BD22" s="10">
-        <f t="shared" si="148"/>
-        <v>0.17</v>
-      </c>
-      <c r="BE22" s="10">
-        <f t="shared" si="148"/>
-        <v>0.17</v>
-      </c>
       <c r="BF22" s="10">
-        <f t="shared" si="148"/>
-        <v>0.17</v>
+        <f t="shared" si="172"/>
+        <v>0.16999999999999998</v>
       </c>
       <c r="BH22" t="s">
         <v>48</v>
       </c>
       <c r="BI22" s="5">
         <f>Main!D8</f>
-        <v>1433</v>
+        <v>575</v>
       </c>
     </row>
     <row r="23" spans="2:61" x14ac:dyDescent="0.3">
@@ -5424,19 +5641,19 @@
         <v>44</v>
       </c>
       <c r="C23" s="10">
-        <f t="shared" ref="C23:F23" si="149">C13/C3</f>
+        <f t="shared" ref="C23:F23" si="173">C13/C3</f>
         <v>0.10474090407938258</v>
       </c>
       <c r="D23" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="173"/>
         <v>8.9665653495440728E-2</v>
       </c>
       <c r="E23" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="173"/>
         <v>-0.10240427426536064</v>
       </c>
       <c r="F23" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="173"/>
         <v>0.11615078148942691</v>
       </c>
       <c r="G23" s="10">
@@ -5444,199 +5661,211 @@
         <v>0.10977080820265379</v>
       </c>
       <c r="H23" s="10">
-        <f t="shared" ref="H23:S23" si="150">H13/H3</f>
+        <f t="shared" ref="H23:S23" si="174">H13/H3</f>
         <v>9.0356304672498403E-2</v>
       </c>
       <c r="I23" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="174"/>
         <v>0.11455623764436583</v>
       </c>
       <c r="J23" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="174"/>
         <v>9.7113118617439126E-2</v>
       </c>
       <c r="K23" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="174"/>
         <v>0.12823639774859288</v>
       </c>
       <c r="L23" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="174"/>
         <v>0.10797985667247724</v>
       </c>
       <c r="M23" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="174"/>
         <v>8.3828186856690426E-2</v>
       </c>
       <c r="N23" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="174"/>
         <v>-0.12513860288293996</v>
       </c>
       <c r="O23" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="174"/>
         <v>0.1432886539550689</v>
       </c>
       <c r="P23" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="174"/>
         <v>0.11126923419016277</v>
       </c>
       <c r="Q23" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="174"/>
         <v>0.13990537800521385</v>
       </c>
       <c r="R23" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="174"/>
         <v>0.12224562540505508</v>
       </c>
       <c r="S23" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="174"/>
         <v>0.15300457217504898</v>
       </c>
       <c r="T23" s="10">
-        <f t="shared" ref="T23:U23" si="151">T13/T3</f>
+        <f t="shared" ref="T23:U23" si="175">T13/T3</f>
         <v>0.11772475125473277</v>
       </c>
       <c r="U23" s="10">
-        <f t="shared" si="151"/>
+        <f t="shared" si="175"/>
         <v>0.12841504921350383</v>
       </c>
       <c r="V23" s="10">
-        <f t="shared" ref="V23:W23" si="152">V13/V3</f>
+        <f t="shared" ref="V23:W23" si="176">V13/V3</f>
         <v>0.11762301781919242</v>
       </c>
       <c r="W23" s="10">
-        <f t="shared" si="152"/>
+        <f t="shared" si="176"/>
         <v>0.11570899345787027</v>
       </c>
       <c r="X23" s="10">
-        <f t="shared" ref="X23" si="153">X13/X3</f>
+        <f t="shared" ref="X23" si="177">X13/X3</f>
         <v>9.9962448366503948E-2</v>
       </c>
       <c r="Y23" s="10">
-        <f t="shared" ref="Y23:AA23" si="154">Y13/Y3</f>
+        <f t="shared" ref="Y23:AA23" si="178">Y13/Y3</f>
         <v>0.10008071025020178</v>
       </c>
       <c r="Z23" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="178"/>
         <v>8.0389863547758289E-2</v>
       </c>
       <c r="AA23" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="178"/>
         <v>0.11206430172347168</v>
       </c>
       <c r="AB23" s="10">
-        <f t="shared" ref="AB23" si="155">AB13/AB3</f>
+        <f t="shared" ref="AB23" si="179">AB13/AB3</f>
         <v>0.11786674634000598</v>
       </c>
       <c r="AC23" s="10">
-        <f t="shared" ref="AC23:AD23" si="156">AC13/AC3</f>
+        <f t="shared" ref="AC23:AD23" si="180">AC13/AC3</f>
         <v>9.4295599002333252E-2</v>
       </c>
       <c r="AD23" s="10">
-        <f t="shared" si="156"/>
+        <f t="shared" si="180"/>
         <v>0.11899095668729176</v>
       </c>
       <c r="AE23" s="10">
-        <f t="shared" ref="AE23:AH23" si="157">AE13/AE3</f>
+        <f t="shared" ref="AE23:AH23" si="181">AE13/AE3</f>
         <v>9.0689446889291564E-2</v>
       </c>
       <c r="AF23" s="10">
-        <f t="shared" si="157"/>
+        <f t="shared" si="181"/>
         <v>9.4139549943338188E-2</v>
       </c>
       <c r="AG23" s="10">
-        <f t="shared" si="157"/>
+        <f t="shared" si="181"/>
         <v>7.045878072588517E-2</v>
       </c>
       <c r="AH23" s="10">
-        <f t="shared" si="157"/>
-        <v>7.6292691718482464E-2</v>
-      </c>
-      <c r="AI23" s="10"/>
-      <c r="AJ23" s="10"/>
-      <c r="AK23" s="10"/>
-      <c r="AL23" s="10"/>
+        <f t="shared" si="181"/>
+        <v>1.9014147967919257E-2</v>
+      </c>
+      <c r="AI23" s="10">
+        <f t="shared" ref="AI23:AL23" si="182">AI13/AI3</f>
+        <v>6.2030716723549491E-2</v>
+      </c>
+      <c r="AJ23" s="10">
+        <f t="shared" si="182"/>
+        <v>8.0206459446333173E-2</v>
+      </c>
+      <c r="AK23" s="10">
+        <f t="shared" si="182"/>
+        <v>7.8065309829673288E-2</v>
+      </c>
+      <c r="AL23" s="10">
+        <f t="shared" si="182"/>
+        <v>7.6091362795456113E-2</v>
+      </c>
       <c r="AN23" s="10">
-        <f t="shared" ref="AN23" si="158">AN13/AN3</f>
+        <f t="shared" ref="AN23" si="183">AN13/AN3</f>
         <v>0.12343522561863174</v>
       </c>
       <c r="AO23" s="10">
-        <f t="shared" ref="AO23" si="159">AO13/AO3</f>
+        <f t="shared" ref="AO23" si="184">AO13/AO3</f>
         <v>5.313624749292524E-2</v>
       </c>
       <c r="AP23" s="10">
-        <f t="shared" ref="AP23:BB23" si="160">AP13/AP3</f>
+        <f t="shared" ref="AP23:BB23" si="185">AP13/AP3</f>
         <v>0.10299869621903521</v>
       </c>
       <c r="AQ23" s="10">
-        <f t="shared" si="160"/>
+        <f t="shared" si="185"/>
         <v>6.7882255434056085E-2</v>
       </c>
       <c r="AR23" s="10">
-        <f t="shared" si="160"/>
+        <f t="shared" si="185"/>
         <v>0.12858682473393507</v>
       </c>
       <c r="AS23" s="10">
-        <f t="shared" si="160"/>
+        <f t="shared" si="185"/>
         <v>0.12943695140226932</v>
       </c>
       <c r="AT23" s="10">
-        <f t="shared" si="160"/>
+        <f t="shared" si="185"/>
         <v>9.8990569537458259E-2</v>
       </c>
       <c r="AU23" s="10">
-        <f t="shared" si="160"/>
+        <f t="shared" si="185"/>
         <v>0.11097698687745804</v>
       </c>
       <c r="AV23" s="10">
-        <f t="shared" si="160"/>
+        <f t="shared" si="185"/>
         <v>6.9511326092120324E-2</v>
       </c>
       <c r="AW23" s="10">
-        <f t="shared" si="160"/>
-        <v>9.7727337407245748E-2</v>
+        <f t="shared" si="185"/>
+        <v>7.4160847344634767E-2</v>
       </c>
       <c r="AX23" s="10">
-        <f t="shared" si="160"/>
-        <v>0.11356254380199665</v>
+        <f t="shared" si="185"/>
+        <v>0.10256900853186721</v>
       </c>
       <c r="AY23" s="10">
-        <f t="shared" si="160"/>
-        <v>0.11732055266021033</v>
+        <f t="shared" si="185"/>
+        <v>0.11467931904581161</v>
       </c>
       <c r="AZ23" s="10">
-        <f t="shared" si="160"/>
-        <v>0.11732055266021038</v>
+        <f t="shared" si="185"/>
+        <v>0.11467931904581163</v>
       </c>
       <c r="BA23" s="10">
-        <f t="shared" si="160"/>
-        <v>0.11732055266021034</v>
+        <f t="shared" si="185"/>
+        <v>0.11467931904581152</v>
       </c>
       <c r="BB23" s="10">
-        <f t="shared" si="160"/>
-        <v>0.11732055266021037</v>
+        <f t="shared" si="185"/>
+        <v>0.11467931904581151</v>
       </c>
       <c r="BC23" s="10">
-        <f t="shared" ref="BC23:BF23" si="161">BC13/BC3</f>
-        <v>0.11732055266021038</v>
+        <f t="shared" ref="BC23:BF23" si="186">BC13/BC3</f>
+        <v>0.11467931904581158</v>
       </c>
       <c r="BD23" s="10">
-        <f t="shared" si="161"/>
-        <v>0.11732055266021037</v>
+        <f t="shared" si="186"/>
+        <v>0.11467931904581156</v>
       </c>
       <c r="BE23" s="10">
-        <f t="shared" si="161"/>
-        <v>0.11732055266021038</v>
+        <f t="shared" si="186"/>
+        <v>0.11467931904581152</v>
       </c>
       <c r="BF23" s="10">
-        <f t="shared" si="161"/>
-        <v>0.11732055266021035</v>
+        <f t="shared" si="186"/>
+        <v>0.11467931904581152</v>
       </c>
       <c r="BH23" t="s">
         <v>49</v>
       </c>
       <c r="BI23" s="5">
         <f>BI21+BI22</f>
-        <v>78653.823409649951</v>
+        <v>76481.028284662112</v>
       </c>
     </row>
     <row r="24" spans="2:61" x14ac:dyDescent="0.3">
@@ -5645,7 +5874,7 @@
       </c>
       <c r="BI24" s="6">
         <f>BI23/BB14</f>
-        <v>53.256025059008699</v>
+        <v>51.73929663419166</v>
       </c>
     </row>
     <row r="25" spans="2:61" x14ac:dyDescent="0.3">
@@ -5654,7 +5883,7 @@
       </c>
       <c r="BI25" s="6">
         <f>Main!D3</f>
-        <v>74.23</v>
+        <v>74.84</v>
       </c>
     </row>
     <row r="26" spans="2:61" x14ac:dyDescent="0.3">
@@ -5663,7 +5892,7 @@
       </c>
       <c r="BI26" s="11">
         <f>BI24/BI25-1</f>
-        <v>-0.28255388577382867</v>
+        <v>-0.30866786966606552</v>
       </c>
     </row>
     <row r="27" spans="2:61" x14ac:dyDescent="0.3">

--- a/Financial Analysis/NKE.xlsx
+++ b/Financial Analysis/NKE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12977B67-1E0E-4644-837F-B8DD35C138CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC77C18-EE6B-450F-993C-3CBEDE2562CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{979F10BC-B7A7-4127-A37D-ADC4ED82FE8E}"/>
   </bookViews>
@@ -250,7 +250,7 @@
     <t>Q426</t>
   </si>
   <si>
-    <t>Overvalued</t>
+    <t>Slightly overvalued</t>
   </si>
 </sst>
 </file>
@@ -311,7 +311,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -330,7 +330,6 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -775,14 +774,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="6">
-        <v>74.84</v>
+        <v>62.31</v>
       </c>
       <c r="E3" s="4">
-        <v>45932</v>
+        <v>45965</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45932</v>
+        <v>45965</v>
       </c>
       <c r="G3" s="4">
         <v>46009</v>
@@ -806,7 +805,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>110628.48800000001</v>
+        <v>92106.642000000007</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -848,7 +847,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>110053.48800000001</v>
+        <v>91531.642000000007</v>
       </c>
     </row>
   </sheetData>
@@ -1544,12 +1543,12 @@
       <c r="AV4" s="5">
         <v>26519</v>
       </c>
-      <c r="AW4" s="12">
+      <c r="AW4" s="5">
         <f>SUM(AI4:AL4)</f>
         <v>26551.467600000004</v>
       </c>
       <c r="AX4" s="5">
-        <f t="shared" ref="AW4:BB4" si="3">AX3-AX5</f>
+        <f t="shared" ref="AX4:BB4" si="3">AX3-AX5</f>
         <v>27010.5</v>
       </c>
       <c r="AY4" s="5">
@@ -1778,7 +1777,7 @@
         <v>22099.5</v>
       </c>
       <c r="AY5" s="9">
-        <f t="shared" ref="AX5:BF5" si="14">AY3*0.46</f>
+        <f t="shared" ref="AY5:BF5" si="14">AY3*0.46</f>
         <v>23268.318000000003</v>
       </c>
       <c r="AZ5" s="9">
@@ -1908,7 +1907,7 @@
         <v>1088</v>
       </c>
       <c r="AH6" s="5">
-        <f t="shared" ref="AH6:AI7" si="15">AV6-AG6-AF6-AE6</f>
+        <f t="shared" ref="AH6:AH7" si="15">AV6-AG6-AF6-AE6</f>
         <v>1253</v>
       </c>
       <c r="AI6" s="5">
@@ -1960,7 +1959,7 @@
       <c r="AV6" s="5">
         <v>4689</v>
       </c>
-      <c r="AW6" s="12">
+      <c r="AW6" s="5">
         <f t="shared" ref="AW6:AW7" si="17">SUM(AI6:AL6)</f>
         <v>4717.0860000000002</v>
       </c>
@@ -2151,7 +2150,7 @@
       <c r="AV7" s="5">
         <v>11399</v>
       </c>
-      <c r="AW7" s="12">
+      <c r="AW7" s="5">
         <f t="shared" si="17"/>
         <v>11490.77</v>
       </c>
@@ -2515,7 +2514,7 @@
         <v>-18</v>
       </c>
       <c r="AH9" s="5">
-        <f t="shared" ref="AH9:AI10" si="32">AV9-AG9-AF9-AE9</f>
+        <f t="shared" ref="AH9:AH10" si="32">AV9-AG9-AF9-AE9</f>
         <v>-22</v>
       </c>
       <c r="AI9" s="5">
@@ -2564,12 +2563,12 @@
       <c r="AV9" s="5">
         <v>-107</v>
       </c>
-      <c r="AW9" s="12">
+      <c r="AW9" s="5">
         <f t="shared" ref="AW9:AW10" si="33">SUM(AI9:AL9)</f>
         <v>-78</v>
       </c>
       <c r="AX9" s="5">
-        <f t="shared" ref="AW9:BF9" si="34">AW9*1.01</f>
+        <f t="shared" ref="AX9:BF9" si="34">AW9*1.01</f>
         <v>-78.78</v>
       </c>
       <c r="AY9" s="5">
@@ -2752,7 +2751,7 @@
       <c r="AV10" s="5">
         <v>-76</v>
       </c>
-      <c r="AW10" s="12">
+      <c r="AW10" s="5">
         <f t="shared" si="33"/>
         <v>83</v>
       </c>
@@ -3168,7 +3167,7 @@
       <c r="AV12" s="5">
         <v>666</v>
       </c>
-      <c r="AW12" s="12">
+      <c r="AW12" s="5">
         <f>SUM(AI12:AL12)</f>
         <v>760.17118800000014</v>
       </c>
@@ -3342,7 +3341,7 @@
         <v>211</v>
       </c>
       <c r="AI13" s="9">
-        <f t="shared" ref="AI13:AK13" si="57">AI11-AI12</f>
+        <f t="shared" ref="AI13" si="57">AI11-AI12</f>
         <v>727</v>
       </c>
       <c r="AJ13" s="9">
@@ -4025,43 +4024,43 @@
         <v>1476.9</v>
       </c>
       <c r="AW14" s="5">
-        <f>1478.2</f>
+        <f t="shared" ref="AW14:BF14" si="64">1478.2</f>
         <v>1478.2</v>
       </c>
       <c r="AX14" s="5">
-        <f>1478.2</f>
+        <f t="shared" si="64"/>
         <v>1478.2</v>
       </c>
       <c r="AY14" s="5">
-        <f>1478.2</f>
+        <f t="shared" si="64"/>
         <v>1478.2</v>
       </c>
       <c r="AZ14" s="5">
-        <f>1478.2</f>
+        <f t="shared" si="64"/>
         <v>1478.2</v>
       </c>
       <c r="BA14" s="5">
-        <f>1478.2</f>
+        <f t="shared" si="64"/>
         <v>1478.2</v>
       </c>
       <c r="BB14" s="5">
-        <f>1478.2</f>
+        <f t="shared" si="64"/>
         <v>1478.2</v>
       </c>
       <c r="BC14" s="5">
-        <f>1478.2</f>
+        <f t="shared" si="64"/>
         <v>1478.2</v>
       </c>
       <c r="BD14" s="5">
-        <f>1478.2</f>
+        <f t="shared" si="64"/>
         <v>1478.2</v>
       </c>
       <c r="BE14" s="5">
-        <f>1478.2</f>
+        <f t="shared" si="64"/>
         <v>1478.2</v>
       </c>
       <c r="BF14" s="5">
-        <f>1478.2</f>
+        <f t="shared" si="64"/>
         <v>1478.2</v>
       </c>
     </row>
@@ -4070,147 +4069,147 @@
         <v>34</v>
       </c>
       <c r="C15" s="8">
-        <f t="shared" ref="C15:S15" si="64">C13/C14</f>
+        <f t="shared" ref="C15:S15" si="65">C13/C14</f>
         <v>0.60126582278481011</v>
       </c>
       <c r="D15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.48544303797468352</v>
       </c>
       <c r="E15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>-0.58227848101265822</v>
       </c>
       <c r="F15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.71962025316455691</v>
       </c>
       <c r="G15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.69113924050632913</v>
       </c>
       <c r="H15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.53607594936708858</v>
       </c>
       <c r="I15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.69683544303797473</v>
       </c>
       <c r="J15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.6259493670886076</v>
       </c>
       <c r="K15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.86518987341772147</v>
       </c>
       <c r="L15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.70569620253164556</v>
       </c>
       <c r="M15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.53607594936708858</v>
       </c>
       <c r="N15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>-0.5</v>
       </c>
       <c r="O15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.96075949367088609</v>
       </c>
       <c r="P15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.79177215189873418</v>
       </c>
       <c r="Q15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.91708860759493671</v>
       </c>
       <c r="R15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.95566814439518688</v>
       </c>
       <c r="S15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>1.1846513686073707</v>
       </c>
       <c r="T15" s="8">
-        <f t="shared" ref="T15:U15" si="65">T13/T14</f>
+        <f t="shared" ref="T15:U15" si="66">T13/T14</f>
         <v>0.84491911021233568</v>
       </c>
       <c r="U15" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0.8841038632045598</v>
       </c>
       <c r="V15" s="8">
-        <f t="shared" ref="V15:W15" si="66">V13/V14</f>
+        <f t="shared" ref="V15:W15" si="67">V13/V14</f>
         <v>0.91539440203562339</v>
       </c>
       <c r="W15" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.9367621721651459</v>
       </c>
       <c r="X15" s="8">
-        <f t="shared" ref="X15" si="67">X13/X14</f>
+        <f t="shared" ref="X15" si="68">X13/X14</f>
         <v>0.85375240538806929</v>
       </c>
       <c r="Y15" s="8">
-        <f t="shared" ref="Y15:AA15" si="68">Y13/Y14</f>
+        <f t="shared" ref="Y15:AA15" si="69">Y13/Y14</f>
         <v>0.80321285140562249</v>
       </c>
       <c r="Z15" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.67100553205336799</v>
       </c>
       <c r="AA15" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.94870452761057311</v>
       </c>
       <c r="AB15" s="8">
-        <f t="shared" ref="AB15" si="69">AB13/AB14</f>
+        <f t="shared" ref="AB15" si="70">AB13/AB14</f>
         <v>1.0376117832719622</v>
       </c>
       <c r="AC15" s="8">
-        <f t="shared" ref="AC15:AD15" si="70">AC13/AC14</f>
+        <f t="shared" ref="AC15:AD15" si="71">AC13/AC14</f>
         <v>0.77451757864129001</v>
       </c>
       <c r="AD15" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.99469496021220161</v>
       </c>
       <c r="AE15" s="8">
-        <f t="shared" ref="AE15:AH15" si="71">AE13/AE14</f>
+        <f t="shared" ref="AE15:AH15" si="72">AE13/AE14</f>
         <v>0.70607994625461878</v>
       </c>
       <c r="AF15" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0.78628895950240019</v>
       </c>
       <c r="AG15" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0.53794037940379402</v>
       </c>
       <c r="AH15" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0.1428668156273275</v>
       </c>
       <c r="AI15" s="8">
-        <f t="shared" ref="AI15:AK15" si="72">AI13/AI14</f>
+        <f t="shared" ref="AI15" si="73">AI13/AI14</f>
         <v>0.49181436882695168</v>
       </c>
       <c r="AJ15" s="8">
-        <f t="shared" ref="AJ15:AL15" si="73">AJ13/AJ14</f>
+        <f t="shared" ref="AJ15:AL15" si="74">AJ13/AJ14</f>
         <v>0.67702564335002036</v>
       </c>
       <c r="AK15" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.60703039913408208</v>
       </c>
       <c r="AL15" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.58265023000947103</v>
       </c>
       <c r="AN15" s="8">
@@ -4234,59 +4233,59 @@
         <v>3.6246835443037977</v>
       </c>
       <c r="AS15" s="8">
-        <f t="shared" ref="AS15:BB15" si="74">AS13/AS14</f>
+        <f t="shared" ref="AS15:BB15" si="75">AS13/AS14</f>
         <v>3.8265822784810126</v>
       </c>
       <c r="AT15" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>3.2088607594936707</v>
       </c>
       <c r="AU15" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>3.7763349675367692</v>
       </c>
       <c r="AV15" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>2.1795653057079014</v>
       </c>
       <c r="AW15" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>2.3585206413205229</v>
       </c>
       <c r="AX15" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>3.4076336145311852</v>
       </c>
       <c r="AY15" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>3.92427168115952</v>
       </c>
       <c r="AZ15" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>3.963514397971116</v>
       </c>
       <c r="BA15" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>4.0031495419508234</v>
       </c>
       <c r="BB15" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>4.0431810373703305</v>
       </c>
       <c r="BC15" s="8">
-        <f t="shared" ref="BC15:BF15" si="75">BC13/BC14</f>
+        <f t="shared" ref="BC15:BF15" si="76">BC13/BC14</f>
         <v>4.0836128477440363</v>
       </c>
       <c r="BD15" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>4.1244489762214762</v>
       </c>
       <c r="BE15" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>4.1656934659836891</v>
       </c>
       <c r="BF15" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>4.2073504006435263</v>
       </c>
     </row>
@@ -4303,127 +4302,127 @@
         <v>9.6802646085997868E-2</v>
       </c>
       <c r="H17" s="10">
-        <f t="shared" ref="H17:R17" si="76">H3/D3-1</f>
+        <f t="shared" ref="H17:R17" si="77">H3/D3-1</f>
         <v>9.586158522328736E-2</v>
       </c>
       <c r="I17" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>6.9790739091718512E-2</v>
       </c>
       <c r="J17" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>4.0351414853406986E-2</v>
       </c>
       <c r="K17" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>7.1572175311620523E-2</v>
       </c>
       <c r="L17" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0.10155749946660975</v>
       </c>
       <c r="M17" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>5.1295390698158361E-2</v>
       </c>
       <c r="N17" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>-0.38010604870384912</v>
       </c>
       <c r="O17" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>-6.1913696060037493E-3</v>
       </c>
       <c r="P17" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>8.8804958357544095E-2</v>
       </c>
       <c r="Q17" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>2.5039588281868586E-2</v>
       </c>
       <c r="R17" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0.95533027086963407</v>
       </c>
       <c r="S17" s="10">
-        <f t="shared" ref="S17:AA17" si="77">S3/O3-1</f>
+        <f t="shared" ref="S17:AA17" si="78">S3/O3-1</f>
         <v>0.15612610911836899</v>
       </c>
       <c r="T17" s="10">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1.0139642444187524E-2</v>
       </c>
       <c r="U17" s="10">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>4.9628270734768831E-2</v>
       </c>
       <c r="V17" s="10">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>-8.9112119248218047E-3</v>
       </c>
       <c r="W17" s="10">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>3.5842586544742039E-2</v>
       </c>
       <c r="X17" s="10">
-        <f t="shared" ref="X17" si="78">X3/T3-1</f>
+        <f t="shared" ref="X17" si="79">X3/T3-1</f>
         <v>0.17240468433565193</v>
       </c>
       <c r="Y17" s="10">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0.13972955569864776</v>
       </c>
       <c r="Z17" s="10">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>4.8307994114762165E-2</v>
       </c>
       <c r="AA17" s="10">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1.986285173799951E-2</v>
       </c>
       <c r="AB17" s="10">
-        <f t="shared" ref="AB17:AE17" si="79">AB3/X3-1</f>
+        <f t="shared" ref="AB17:AE17" si="80">AB3/X3-1</f>
         <v>5.482538490424238E-3</v>
       </c>
       <c r="AC17" s="10">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>3.1476997578692156E-3</v>
       </c>
       <c r="AD17" s="10">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>-1.7076023391812911E-2</v>
       </c>
       <c r="AE17" s="10">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>-0.10433572919081846</v>
       </c>
       <c r="AF17" s="10">
-        <f t="shared" ref="AF17" si="80">AF3/AB3-1</f>
+        <f t="shared" ref="AF17" si="81">AF3/AB3-1</f>
         <v>-7.7233343292500756E-2</v>
       </c>
       <c r="AG17" s="10">
-        <f t="shared" ref="AG17:AI17" si="81">AG3/AC3-1</f>
+        <f t="shared" ref="AG17:AI17" si="82">AG3/AC3-1</f>
         <v>-9.3330115053503859E-2</v>
       </c>
       <c r="AH17" s="10">
-        <f t="shared" ref="AH17:AI17" si="82">AH3/AD3-1</f>
+        <f t="shared" ref="AH17" si="83">AH3/AD3-1</f>
         <v>-0.11970490242741549</v>
       </c>
       <c r="AI17" s="10">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>1.1303822590387425E-2</v>
       </c>
       <c r="AJ17" s="10">
-        <f t="shared" ref="AJ17" si="83">AJ3/AF3-1</f>
+        <f t="shared" ref="AJ17" si="84">AJ3/AF3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AK17" s="10">
-        <f t="shared" ref="AK17" si="84">AK3/AG3-1</f>
+        <f t="shared" ref="AK17" si="85">AK3/AG3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL17" s="10">
-        <f t="shared" ref="AL17" si="85">AL3/AH3-1</f>
+        <f t="shared" ref="AL17" si="86">AL3/AH3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AN17" s="10"/>
@@ -4436,67 +4435,67 @@
         <v>7.4731433909388079E-2</v>
       </c>
       <c r="AQ17" s="10">
-        <f t="shared" ref="AQ17:BB17" si="86">AQ3/AP3-1</f>
+        <f t="shared" ref="AQ17:BB17" si="87">AQ3/AP3-1</f>
         <v>-4.3817266150267153E-2</v>
       </c>
       <c r="AR17" s="10">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0.19076009945726269</v>
       </c>
       <c r="AS17" s="10">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>4.8767344739323759E-2</v>
       </c>
       <c r="AT17" s="10">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>9.6488974523656568E-2</v>
       </c>
       <c r="AU17" s="10">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>2.8310912392370824E-3</v>
       </c>
       <c r="AV17" s="10">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>-9.8380125384525563E-2</v>
       </c>
       <c r="AW17" s="10">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>1.5156017188883375E-2</v>
       </c>
       <c r="AX17" s="10">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>4.4652235674905727E-2</v>
       </c>
       <c r="AY17" s="10">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AZ17" s="10">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BA17" s="10">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BB17" s="10">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BC17" s="10">
-        <f t="shared" ref="BC17" si="87">BC3/BB3-1</f>
+        <f t="shared" ref="BC17" si="88">BC3/BB3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BD17" s="10">
-        <f t="shared" ref="BD17" si="88">BD3/BC3-1</f>
+        <f t="shared" ref="BD17" si="89">BD3/BC3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BE17" s="10">
-        <f t="shared" ref="BE17" si="89">BE3/BD3-1</f>
+        <f t="shared" ref="BE17" si="90">BE3/BD3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BF17" s="10">
-        <f t="shared" ref="BF17" si="90">BF3/BE3-1</f>
+        <f t="shared" ref="BF17" si="91">BF3/BE3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -4505,19 +4504,19 @@
         <v>40</v>
       </c>
       <c r="C18" s="10">
-        <f t="shared" ref="C18:F18" si="91">C5/C3</f>
+        <f t="shared" ref="C18:F18" si="92">C5/C3</f>
         <v>0.43682469680264607</v>
       </c>
       <c r="D18" s="10">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0.42997428103811081</v>
       </c>
       <c r="E18" s="10">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0.4383348174532502</v>
       </c>
       <c r="F18" s="10">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0.44723669424864643</v>
       </c>
       <c r="G18" s="10">
@@ -4525,203 +4524,203 @@
         <v>0.44199839163650984</v>
       </c>
       <c r="H18" s="10">
-        <f t="shared" ref="H18:S18" si="92">H5/H3</f>
+        <f t="shared" ref="H18:S18" si="93">H5/H3</f>
         <v>0.43791337742692554</v>
       </c>
       <c r="I18" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0.45146186661117471</v>
       </c>
       <c r="J18" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0.45492930086410055</v>
       </c>
       <c r="K18" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0.45694183864915572</v>
       </c>
       <c r="L18" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0.4400542320356382</v>
       </c>
       <c r="M18" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0.44269596199524941</v>
       </c>
       <c r="N18" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0.37272295263741484</v>
       </c>
       <c r="O18" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0.44751746271474419</v>
       </c>
       <c r="P18" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0.43111269234190164</v>
       </c>
       <c r="Q18" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0.45563387081201118</v>
       </c>
       <c r="R18" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0.45811730395333766</v>
       </c>
       <c r="S18" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0.46505551926845201</v>
       </c>
       <c r="T18" s="10">
-        <f t="shared" ref="T18:U18" si="93">T5/T3</f>
+        <f t="shared" ref="T18:U18" si="94">T5/T3</f>
         <v>0.45901206304481817</v>
       </c>
       <c r="U18" s="10">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.4661024744733695</v>
       </c>
       <c r="V18" s="10">
-        <f t="shared" ref="V18:W18" si="94">V5/V3</f>
+        <f t="shared" ref="V18:W18" si="95">V5/V3</f>
         <v>0.44981199934608468</v>
       </c>
       <c r="W18" s="10">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0.44257901789233073</v>
       </c>
       <c r="X18" s="10">
-        <f t="shared" ref="X18" si="95">X5/X3</f>
+        <f t="shared" ref="X18" si="96">X5/X3</f>
         <v>0.42891475779196397</v>
       </c>
       <c r="Y18" s="10">
-        <f t="shared" ref="Y18:AA18" si="96">Y5/Y3</f>
+        <f t="shared" ref="Y18:AA18" si="97">Y5/Y3</f>
         <v>0.43349475383373687</v>
       </c>
       <c r="Z18" s="10">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>0.43625730994152045</v>
       </c>
       <c r="AA18" s="10">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>0.44207434886776414</v>
       </c>
       <c r="AB18" s="10">
-        <f t="shared" ref="AB18" si="97">AB5/AB3</f>
+        <f t="shared" ref="AB18" si="98">AB5/AB3</f>
         <v>0.44599641469973111</v>
       </c>
       <c r="AC18" s="10">
-        <f t="shared" ref="AC18:AD18" si="98">AC5/AC3</f>
+        <f t="shared" ref="AC18:AD18" si="99">AC5/AC3</f>
         <v>0.44750181028240404</v>
       </c>
       <c r="AD18" s="10">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.44693003331746789</v>
       </c>
       <c r="AE18" s="10">
-        <f t="shared" ref="AE18:AH18" si="99">AE5/AE3</f>
+        <f t="shared" ref="AE18:AH18" si="100">AE5/AE3</f>
         <v>0.45361981189058592</v>
       </c>
       <c r="AF18" s="10">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>0.43621499109600131</v>
       </c>
       <c r="AG18" s="10">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>0.41485491170467653</v>
       </c>
       <c r="AH18" s="10">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>0.40272145624943678</v>
       </c>
       <c r="AI18" s="10">
-        <f t="shared" ref="AI18:AL18" si="100">AI5/AI3</f>
+        <f t="shared" ref="AI18:AL18" si="101">AI5/AI3</f>
         <v>0.42175767918088736</v>
       </c>
       <c r="AJ18" s="10">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>0.43</v>
       </c>
       <c r="AK18" s="10">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>0.44</v>
       </c>
       <c r="AL18" s="10">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>0.45</v>
       </c>
       <c r="AN18" s="10">
-        <f t="shared" ref="AN18" si="101">AN5/AN3</f>
+        <f t="shared" ref="AN18" si="102">AN5/AN3</f>
         <v>0.445764192139738</v>
       </c>
       <c r="AO18" s="10">
-        <f t="shared" ref="AO18" si="102">AO5/AO3</f>
+        <f t="shared" ref="AO18" si="103">AO5/AO3</f>
         <v>0.43838777921257244</v>
       </c>
       <c r="AP18" s="10">
-        <f t="shared" ref="AP18:BB18" si="103">AP5/AP3</f>
+        <f t="shared" ref="AP18:BB18" si="104">AP5/AP3</f>
         <v>0.44671114860546568</v>
       </c>
       <c r="AQ18" s="10">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.43421650669732376</v>
       </c>
       <c r="AR18" s="10">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.44820153576721</v>
       </c>
       <c r="AS18" s="10">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.45983729394134021</v>
       </c>
       <c r="AT18" s="10">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.43524610969014194</v>
       </c>
       <c r="AU18" s="10">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.44560180678322497</v>
       </c>
       <c r="AV18" s="10">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.42734673605562634</v>
       </c>
       <c r="AW18" s="10">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.43520566098982227</v>
       </c>
       <c r="AX18" s="10">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.45</v>
       </c>
       <c r="AY18" s="10">
-        <f t="shared" si="103"/>
-        <v>0.46</v>
-      </c>
-      <c r="AZ18" s="10">
-        <f t="shared" si="103"/>
-        <v>0.46</v>
-      </c>
-      <c r="BA18" s="10">
-        <f t="shared" si="103"/>
-        <v>0.46</v>
-      </c>
-      <c r="BB18" s="10">
-        <f t="shared" si="103"/>
-        <v>0.46</v>
-      </c>
-      <c r="BC18" s="10">
-        <f t="shared" ref="BC18:BF18" si="104">BC5/BC3</f>
-        <v>0.46</v>
-      </c>
-      <c r="BD18" s="10">
         <f t="shared" si="104"/>
         <v>0.46</v>
       </c>
-      <c r="BE18" s="10">
+      <c r="AZ18" s="10">
         <f t="shared" si="104"/>
         <v>0.46</v>
       </c>
+      <c r="BA18" s="10">
+        <f t="shared" si="104"/>
+        <v>0.46</v>
+      </c>
+      <c r="BB18" s="10">
+        <f t="shared" si="104"/>
+        <v>0.46</v>
+      </c>
+      <c r="BC18" s="10">
+        <f t="shared" ref="BC18:BF18" si="105">BC5/BC3</f>
+        <v>0.46</v>
+      </c>
+      <c r="BD18" s="10">
+        <f t="shared" si="105"/>
+        <v>0.46</v>
+      </c>
+      <c r="BE18" s="10">
+        <f t="shared" si="105"/>
+        <v>0.46</v>
+      </c>
       <c r="BF18" s="10">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0.46</v>
       </c>
     </row>
@@ -4730,19 +4729,19 @@
         <v>41</v>
       </c>
       <c r="C19" s="10">
-        <f t="shared" ref="C19:F19" si="105">C8/C3</f>
+        <f t="shared" ref="C19:F19" si="106">C8/C3</f>
         <v>0.12194046306504962</v>
       </c>
       <c r="D19" s="10">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>0.10638297872340426</v>
       </c>
       <c r="E19" s="10">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>0.13034283170080144</v>
       </c>
       <c r="F19" s="10">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>0.12851159464705281</v>
       </c>
       <c r="G19" s="10">
@@ -4750,203 +4749,203 @@
         <v>0.13409730599115399</v>
       </c>
       <c r="H19" s="10">
-        <f t="shared" ref="H19:S19" si="106">H8/H3</f>
+        <f t="shared" ref="H19:S19" si="107">H8/H3</f>
         <v>0.10273095796885001</v>
       </c>
       <c r="I19" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.12985121215274165</v>
       </c>
       <c r="J19" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.12048311076197958</v>
       </c>
       <c r="K19" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.14474671669793621</v>
       </c>
       <c r="L19" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.11814836335463877</v>
       </c>
       <c r="M19" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.11777513855898654</v>
       </c>
       <c r="N19" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>-0.13274196103278948</v>
       </c>
       <c r="O19" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.16669813101755709</v>
       </c>
       <c r="P19" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.14053188650716</v>
       </c>
       <c r="Q19" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.16201602780728011</v>
       </c>
       <c r="R19" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.15497407647440051</v>
       </c>
       <c r="S19" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.17341606792945788</v>
       </c>
       <c r="T19" s="10">
-        <f t="shared" ref="T19:U19" si="107">T8/T3</f>
+        <f t="shared" ref="T19:U19" si="108">T8/T3</f>
         <v>0.12802676763229726</v>
       </c>
       <c r="U19" s="10">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.14984822003495538</v>
       </c>
       <c r="V19" s="10">
-        <f t="shared" ref="V19:W19" si="108">V8/V3</f>
+        <f t="shared" ref="V19:W19" si="109">V8/V3</f>
         <v>0.11999346084682033</v>
       </c>
       <c r="W19" s="10">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.13360132419011586</v>
       </c>
       <c r="X19" s="10">
-        <f t="shared" ref="X19" si="109">X8/X3</f>
+        <f t="shared" ref="X19" si="110">X8/X3</f>
         <v>0.11918888471648517</v>
       </c>
       <c r="Y19" s="10">
-        <f t="shared" ref="Y19:AA19" si="110">Y8/Y3</f>
+        <f t="shared" ref="Y19:AA19" si="111">Y8/Y3</f>
         <v>0.11396287328490719</v>
       </c>
       <c r="Z19" s="10">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>9.5204678362573097E-2</v>
       </c>
       <c r="AA19" s="10">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>0.12396630342375763</v>
       </c>
       <c r="AB19" s="10">
-        <f t="shared" ref="AB19" si="111">AB8/AB3</f>
+        <f t="shared" ref="AB19" si="112">AB8/AB3</f>
         <v>0.1363161039737078</v>
       </c>
       <c r="AC19" s="10">
-        <f t="shared" ref="AC19:AD19" si="112">AC8/AC3</f>
+        <f t="shared" ref="AC19:AD19" si="113">AC8/AC3</f>
         <v>0.10749054630300105</v>
       </c>
       <c r="AD19" s="10">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>0.12264001269236871</v>
       </c>
       <c r="AE19" s="10">
-        <f t="shared" ref="AE19:AH19" si="113">AE8/AE3</f>
+        <f t="shared" ref="AE19:AH19" si="114">AE8/AE3</f>
         <v>0.10432306497540772</v>
       </c>
       <c r="AF19" s="10">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>0.1120284927958556</v>
       </c>
       <c r="AG19" s="10">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>6.9926346614606436E-2</v>
       </c>
       <c r="AH19" s="10">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>2.8926736955934035E-2</v>
       </c>
       <c r="AI19" s="10">
-        <f t="shared" ref="AI19:AL19" si="114">AI8/AI3</f>
+        <f t="shared" ref="AI19:AL19" si="115">AI8/AI3</f>
         <v>7.909556313993174E-2</v>
       </c>
       <c r="AJ19" s="10">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>9.6634288489558046E-2</v>
       </c>
       <c r="AK19" s="10">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>9.4054590156232867E-2</v>
       </c>
       <c r="AL19" s="10">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>9.167634071741701E-2</v>
       </c>
       <c r="AN19" s="10">
-        <f t="shared" ref="AN19" si="115">AN8/AN3</f>
+        <f t="shared" ref="AN19" si="116">AN8/AN3</f>
         <v>0.13825327510917029</v>
       </c>
       <c r="AO19" s="10">
-        <f t="shared" ref="AO19" si="116">AO8/AO3</f>
+        <f t="shared" ref="AO19" si="117">AO8/AO3</f>
         <v>0.12212544989971701</v>
       </c>
       <c r="AP19" s="10">
-        <f t="shared" ref="AP19:BB19" si="117">AP8/AP3</f>
+        <f t="shared" ref="AP19:BB19" si="118">AP8/AP3</f>
         <v>0.12199299537285579</v>
       </c>
       <c r="AQ19" s="10">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>8.3282089671951443E-2</v>
       </c>
       <c r="AR19" s="10">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.15575463649018814</v>
       </c>
       <c r="AS19" s="10">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.14290301862556198</v>
       </c>
       <c r="AT19" s="10">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.11548899779370131</v>
       </c>
       <c r="AU19" s="10">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.12287294108484872</v>
       </c>
       <c r="AV19" s="10">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>7.9941264117126265E-2</v>
       </c>
       <c r="AW19" s="10">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>9.0437324482045153E-2</v>
       </c>
       <c r="AX19" s="10">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.12367994909387087</v>
       </c>
       <c r="AY19" s="10">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.13826868794641717</v>
       </c>
       <c r="AZ19" s="10">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.13826868794641717</v>
       </c>
       <c r="BA19" s="10">
-        <f t="shared" si="117"/>
-        <v>0.13826868794641708</v>
-      </c>
-      <c r="BB19" s="10">
-        <f t="shared" si="117"/>
-        <v>0.13826868794641703</v>
-      </c>
-      <c r="BC19" s="10">
-        <f t="shared" ref="BC19:BF19" si="118">BC8/BC3</f>
-        <v>0.13826868794641711</v>
-      </c>
-      <c r="BD19" s="10">
-        <f t="shared" si="118"/>
-        <v>0.13826868794641711</v>
-      </c>
-      <c r="BE19" s="10">
         <f t="shared" si="118"/>
         <v>0.13826868794641708</v>
       </c>
+      <c r="BB19" s="10">
+        <f t="shared" si="118"/>
+        <v>0.13826868794641703</v>
+      </c>
+      <c r="BC19" s="10">
+        <f t="shared" ref="BC19:BF19" si="119">BC8/BC3</f>
+        <v>0.13826868794641711</v>
+      </c>
+      <c r="BD19" s="10">
+        <f t="shared" si="119"/>
+        <v>0.13826868794641711</v>
+      </c>
+      <c r="BE19" s="10">
+        <f t="shared" si="119"/>
+        <v>0.13826868794641708</v>
+      </c>
       <c r="BF19" s="10">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>0.13826868794641706</v>
       </c>
       <c r="BH19" t="s">
@@ -4961,19 +4960,19 @@
         <v>42</v>
       </c>
       <c r="C20" s="10">
-        <f t="shared" ref="C20:F20" si="119">C6/C3</f>
+        <f t="shared" ref="C20:F20" si="120">C6/C3</f>
         <v>9.4266813671444322E-2</v>
       </c>
       <c r="D20" s="10">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>0.10252513444002806</v>
       </c>
       <c r="E20" s="10">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>9.5948352626892247E-2</v>
       </c>
       <c r="F20" s="10">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>0.1004188374706303</v>
       </c>
       <c r="G20" s="10">
@@ -4981,203 +4980,203 @@
         <v>9.6903900281463617E-2</v>
       </c>
       <c r="H20" s="10">
-        <f t="shared" ref="H20:S20" si="120">H6/H3</f>
+        <f t="shared" ref="H20:S20" si="121">H6/H3</f>
         <v>9.707702154896522E-2</v>
       </c>
       <c r="I20" s="10">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>9.0001040474456354E-2</v>
       </c>
       <c r="J20" s="10">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>9.9567949725058918E-2</v>
       </c>
       <c r="K20" s="10">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>9.5497185741088175E-2</v>
       </c>
       <c r="L20" s="10">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>8.5318613209374394E-2</v>
       </c>
       <c r="M20" s="10">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>8.6104513064133012E-2</v>
       </c>
       <c r="N20" s="10">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.1303659116109615</v>
       </c>
       <c r="O20" s="10">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>6.390409665848594E-2</v>
       </c>
       <c r="P20" s="10">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>6.4840345103620037E-2</v>
       </c>
       <c r="Q20" s="10">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>6.8649222747899974E-2</v>
       </c>
       <c r="R20" s="10">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>8.0767984445884636E-2</v>
       </c>
       <c r="S20" s="10">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>7.4951012410189422E-2</v>
       </c>
       <c r="T20" s="10">
-        <f t="shared" ref="T20:U20" si="121">T6/T3</f>
+        <f t="shared" ref="T20:U20" si="122">T6/T3</f>
         <v>8.954829620498371E-2</v>
       </c>
       <c r="U20" s="10">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>7.8557630392788153E-2</v>
       </c>
       <c r="V20" s="10">
-        <f t="shared" ref="V20:W20" si="122">V6/V3</f>
+        <f t="shared" ref="V20:W20" si="123">V6/V3</f>
         <v>8.6725519045283639E-2</v>
       </c>
       <c r="W20" s="10">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>7.4328052337037917E-2</v>
       </c>
       <c r="X20" s="10">
-        <f t="shared" ref="X20" si="123">X6/X3</f>
+        <f t="shared" ref="X20" si="124">X6/X3</f>
         <v>8.2763800225309797E-2</v>
       </c>
       <c r="Y20" s="10">
-        <f t="shared" ref="Y20:AA20" si="124">Y6/Y3</f>
+        <f t="shared" ref="Y20:AA20" si="125">Y6/Y3</f>
         <v>7.4495560936238908E-2</v>
       </c>
       <c r="Z20" s="10">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>8.5146198830409359E-2</v>
       </c>
       <c r="AA20" s="10">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>8.2618440374062907E-2</v>
       </c>
       <c r="AB20" s="10">
-        <f t="shared" ref="AB20" si="125">AB6/AB3</f>
+        <f t="shared" ref="AB20" si="126">AB6/AB3</f>
         <v>8.3208843740663285E-2</v>
       </c>
       <c r="AC20" s="10">
-        <f t="shared" ref="AC20:AD20" si="126">AC6/AC3</f>
+        <f t="shared" ref="AC20:AD20" si="127">AC6/AC3</f>
         <v>8.1342022688872792E-2</v>
       </c>
       <c r="AD20" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>8.6546089163890214E-2</v>
       </c>
       <c r="AE20" s="10">
-        <f t="shared" ref="AE20:AH20" si="127">AE6/AE3</f>
+        <f t="shared" ref="AE20:AH20" si="128">AE6/AE3</f>
         <v>0.10578997325049616</v>
       </c>
       <c r="AF20" s="10">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>9.0820786789703734E-2</v>
       </c>
       <c r="AG20" s="10">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>9.6548052178542912E-2</v>
       </c>
       <c r="AH20" s="10">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0.11291340001802289</v>
       </c>
       <c r="AI20" s="10">
-        <f t="shared" ref="AI20:AL20" si="128">AI6/AI3</f>
+        <f t="shared" ref="AI20:AL20" si="129">AI6/AI3</f>
         <v>0.10136518771331059</v>
       </c>
       <c r="AJ20" s="10">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
       <c r="AK20" s="10">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
       <c r="AL20" s="10">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="AN20" s="10">
-        <f t="shared" ref="AN20" si="129">AN6/AN3</f>
+        <f t="shared" ref="AN20" si="130">AN6/AN3</f>
         <v>9.726346433770014E-2</v>
       </c>
       <c r="AO20" s="10">
-        <f t="shared" ref="AO20" si="130">AO6/AO3</f>
+        <f t="shared" ref="AO20" si="131">AO6/AO3</f>
         <v>9.8277330549221095E-2</v>
       </c>
       <c r="AP20" s="10">
-        <f t="shared" ref="AP20:BB20" si="131">AP6/AP3</f>
+        <f t="shared" ref="AP20:BB20" si="132">AP6/AP3</f>
         <v>9.5942940409540614E-2</v>
       </c>
       <c r="AQ20" s="10">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>9.6035077400208543E-2</v>
       </c>
       <c r="AR20" s="10">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>6.9917822982621586E-2</v>
       </c>
       <c r="AS20" s="10">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>8.2423463926354093E-2</v>
       </c>
       <c r="AT20" s="10">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>7.9270554698635212E-2</v>
       </c>
       <c r="AU20" s="10">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>8.3427436626299603E-2</v>
       </c>
       <c r="AV20" s="10">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.10125461573344274</v>
       </c>
       <c r="AW20" s="10">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.10034034689005902</v>
       </c>
       <c r="AX20" s="10">
-        <f t="shared" si="131"/>
-        <v>0.09</v>
-      </c>
-      <c r="AY20" s="10">
-        <f t="shared" si="131"/>
-        <v>0.09</v>
-      </c>
-      <c r="AZ20" s="10">
-        <f t="shared" si="131"/>
-        <v>0.09</v>
-      </c>
-      <c r="BA20" s="10">
-        <f t="shared" si="131"/>
-        <v>0.09</v>
-      </c>
-      <c r="BB20" s="10">
-        <f t="shared" si="131"/>
-        <v>8.9999999999999983E-2</v>
-      </c>
-      <c r="BC20" s="10">
-        <f t="shared" ref="BC20:BF20" si="132">BC6/BC3</f>
-        <v>0.09</v>
-      </c>
-      <c r="BD20" s="10">
         <f t="shared" si="132"/>
         <v>0.09</v>
       </c>
-      <c r="BE20" s="10">
+      <c r="AY20" s="10">
         <f t="shared" si="132"/>
         <v>0.09</v>
       </c>
+      <c r="AZ20" s="10">
+        <f t="shared" si="132"/>
+        <v>0.09</v>
+      </c>
+      <c r="BA20" s="10">
+        <f t="shared" si="132"/>
+        <v>0.09</v>
+      </c>
+      <c r="BB20" s="10">
+        <f t="shared" si="132"/>
+        <v>8.9999999999999983E-2</v>
+      </c>
+      <c r="BC20" s="10">
+        <f t="shared" ref="BC20:BF20" si="133">BC6/BC3</f>
+        <v>0.09</v>
+      </c>
+      <c r="BD20" s="10">
+        <f t="shared" si="133"/>
+        <v>0.09</v>
+      </c>
+      <c r="BE20" s="10">
+        <f t="shared" si="133"/>
+        <v>0.09</v>
+      </c>
       <c r="BF20" s="10">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>8.9999999999999983E-2</v>
       </c>
       <c r="BH20" t="s">
@@ -5196,204 +5195,204 @@
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
       <c r="G21" s="10">
-        <f t="shared" ref="G21" si="133">G7/C7-1</f>
+        <f t="shared" ref="G21" si="134">G7/C7-1</f>
         <v>4.8975512243877972E-2</v>
       </c>
       <c r="H21" s="10">
-        <f t="shared" ref="H21" si="134">H7/D7-1</f>
+        <f t="shared" ref="H21" si="135">H7/D7-1</f>
         <v>0.18032786885245899</v>
       </c>
       <c r="I21" s="10">
-        <f t="shared" ref="I21" si="135">I7/E7-1</f>
+        <f t="shared" ref="I21" si="136">I7/E7-1</f>
         <v>0.16850393700787403</v>
       </c>
       <c r="J21" s="10">
-        <f t="shared" ref="J21" si="136">J7/F7-1</f>
+        <f t="shared" ref="J21" si="137">J7/F7-1</f>
         <v>0.11932615816565284</v>
       </c>
       <c r="K21" s="10">
-        <f t="shared" ref="K21" si="137">K7/G7-1</f>
+        <f t="shared" ref="K21" si="138">K7/G7-1</f>
         <v>0.10052405907575035</v>
       </c>
       <c r="L21" s="10">
-        <f t="shared" ref="L21" si="138">L7/H7-1</f>
+        <f t="shared" ref="L21" si="139">L7/H7-1</f>
         <v>9.4534050179211571E-2</v>
       </c>
       <c r="M21" s="10">
-        <f t="shared" ref="M21" si="139">M7/I7-1</f>
+        <f t="shared" ref="M21" si="140">M7/I7-1</f>
         <v>8.4007187780772652E-2</v>
       </c>
       <c r="N21" s="10">
-        <f t="shared" ref="N21" si="140">N7/J7-1</f>
+        <f t="shared" ref="N21" si="141">N7/J7-1</f>
         <v>-1.0033444816053505E-2</v>
       </c>
       <c r="O21" s="10">
-        <f t="shared" ref="O21" si="141">O7/K7-1</f>
+        <f t="shared" ref="O21" si="142">O7/K7-1</f>
         <v>-5.1948051948051965E-3</v>
       </c>
       <c r="P21" s="10">
-        <f t="shared" ref="P21" si="142">P7/L7-1</f>
+        <f t="shared" ref="P21" si="143">P7/L7-1</f>
         <v>3.8886614817846832E-2</v>
       </c>
       <c r="Q21" s="10">
-        <f t="shared" ref="Q21:R21" si="143">Q7/M7-1</f>
+        <f t="shared" ref="Q21:R21" si="144">Q7/M7-1</f>
         <v>-3.4397016162453387E-2</v>
       </c>
       <c r="R21" s="10">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>0.15920608108108114</v>
       </c>
       <c r="S21" s="10">
-        <f t="shared" ref="S21:AA21" si="144">S7/O7-1</f>
+        <f t="shared" ref="S21:AA21" si="145">S7/O7-1</f>
         <v>0.15491731940818099</v>
       </c>
       <c r="T21" s="10">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>8.0378250591016442E-2</v>
       </c>
       <c r="U21" s="10">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>0.10901287553648076</v>
       </c>
       <c r="V21" s="10">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>8.3424408014571849E-2</v>
       </c>
       <c r="W21" s="10">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>0.12170308967596077</v>
       </c>
       <c r="X21" s="10">
-        <f t="shared" ref="X21" si="145">X7/T7-1</f>
+        <f t="shared" ref="X21" si="146">X7/T7-1</f>
         <v>0.10211524434719177</v>
       </c>
       <c r="Y21" s="10">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>0.17492260061919507</v>
       </c>
       <c r="Z21" s="10">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>0.10356422326832559</v>
       </c>
       <c r="AA21" s="10">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>2.3513604299630453E-2</v>
       </c>
       <c r="AB21" s="10">
-        <f t="shared" ref="AB21:AE21" si="146">AB7/X7-1</f>
+        <f t="shared" ref="AB21:AE21" si="147">AB7/X7-1</f>
         <v>3.3090668431501324E-3</v>
       </c>
       <c r="AC21" s="10">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>5.895915678524366E-2</v>
       </c>
       <c r="AD21" s="10">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>-8.6837294332723913E-2</v>
       </c>
       <c r="AE21" s="10">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>-7.3843124384640579E-2</v>
       </c>
       <c r="AF21" s="10">
-        <f t="shared" ref="AF21" si="147">AF7/AB7-1</f>
+        <f t="shared" ref="AF21" si="148">AF7/AB7-1</f>
         <v>-4.9142480211081807E-2</v>
       </c>
       <c r="AG21" s="10">
-        <f t="shared" ref="AG21:AI21" si="148">AG7/AC7-1</f>
+        <f t="shared" ref="AG21:AI21" si="149">AG7/AC7-1</f>
         <v>-0.12939346811819596</v>
       </c>
       <c r="AH21" s="10">
-        <f t="shared" ref="AH21:AI21" si="149">AH7/AD7-1</f>
+        <f t="shared" ref="AH21" si="150">AH7/AD7-1</f>
         <v>-3.4034034034034044E-2</v>
       </c>
       <c r="AI21" s="10">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>2.1261516654855761E-3</v>
       </c>
       <c r="AJ21" s="10">
-        <f t="shared" ref="AJ21" si="150">AJ7/AF7-1</f>
+        <f t="shared" ref="AJ21" si="151">AJ7/AF7-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AK21" s="10">
-        <f t="shared" ref="AK21" si="151">AK7/AG7-1</f>
+        <f t="shared" ref="AK21" si="152">AK7/AG7-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL21" s="10">
-        <f t="shared" ref="AL21" si="152">AL7/AH7-1</f>
+        <f t="shared" ref="AL21" si="153">AL7/AH7-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN21" s="10"/>
       <c r="AO21" s="10">
-        <f t="shared" ref="AO21" si="153">AO7/AN7-1</f>
+        <f t="shared" ref="AO21" si="154">AO7/AN7-1</f>
         <v>9.8587648850733789E-2</v>
       </c>
       <c r="AP21" s="10">
-        <f t="shared" ref="AP21:BB21" si="154">AP7/AO7-1</f>
+        <f t="shared" ref="AP21:BB21" si="155">AP7/AO7-1</f>
         <v>0.12793042601462057</v>
       </c>
       <c r="AQ21" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>6.5370432450553073E-2</v>
       </c>
       <c r="AR21" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>3.9542689322425106E-2</v>
       </c>
       <c r="AS21" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>0.10523660579154481</v>
       </c>
       <c r="AT21" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>0.12442943217089653</v>
       </c>
       <c r="AU21" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>-2.1109036291304673E-3</v>
       </c>
       <c r="AV21" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>-7.257342771133346E-2</v>
       </c>
       <c r="AW21" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>8.0507062022985298E-3</v>
       </c>
       <c r="AX21" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY21" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ21" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BA21" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BB21" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BC21" s="10">
-        <f t="shared" ref="BC21" si="155">BC7/BB7-1</f>
+        <f t="shared" ref="BC21" si="156">BC7/BB7-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BD21" s="10">
-        <f t="shared" ref="BD21" si="156">BD7/BC7-1</f>
+        <f t="shared" ref="BD21" si="157">BD7/BC7-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BE21" s="10">
-        <f t="shared" ref="BE21" si="157">BE7/BD7-1</f>
+        <f t="shared" ref="BE21" si="158">BE7/BD7-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BF21" s="10">
-        <f t="shared" ref="BF21" si="158">BF7/BE7-1</f>
+        <f t="shared" ref="BF21" si="159">BF7/BE7-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BH21" t="s">
@@ -5409,19 +5408,19 @@
         <v>32</v>
       </c>
       <c r="C22" s="10">
-        <f t="shared" ref="C22:F22" si="159">C12/C11</f>
+        <f t="shared" ref="C22:F22" si="160">C12/C11</f>
         <v>0.11380597014925373</v>
       </c>
       <c r="D22" s="10">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>0.12741751990898748</v>
       </c>
       <c r="E22" s="10">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>1.7931034482758621</v>
       </c>
       <c r="F22" s="10">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>6.4197530864197536E-2</v>
       </c>
       <c r="G22" s="10">
@@ -5429,203 +5428,203 @@
         <v>0.14015748031496064</v>
       </c>
       <c r="H22" s="10">
-        <f t="shared" ref="H22:S22" si="160">H12/H11</f>
+        <f t="shared" ref="H22:S22" si="161">H12/H11</f>
         <v>0.15045135406218657</v>
       </c>
       <c r="I22" s="10">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>0.14717273431448488</v>
       </c>
       <c r="J22" s="10">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>0.20434432823813356</v>
       </c>
       <c r="K22" s="10">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>0.12427930813581038</v>
       </c>
       <c r="L22" s="10">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>0.10728582866293035</v>
       </c>
       <c r="M22" s="10">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>3.8592508513053347E-2</v>
       </c>
       <c r="N22" s="10">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>1.7412935323383085E-2</v>
       </c>
       <c r="O22" s="10">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>0.11486880466472303</v>
       </c>
       <c r="P22" s="10">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>0.1407967032967033</v>
       </c>
       <c r="Q22" s="10">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>0.11430317848410758</v>
       </c>
       <c r="R22" s="10">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>0.18608414239482202</v>
       </c>
       <c r="S22" s="10">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>0.11016144349477683</v>
       </c>
       <c r="T22" s="10">
-        <f t="shared" ref="T22:U22" si="161">T12/T11</f>
+        <f t="shared" ref="T22:U22" si="162">T12/T11</f>
         <v>0.10926049300466356</v>
       </c>
       <c r="U22" s="10">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v>0.16407185628742516</v>
       </c>
       <c r="V22" s="10">
-        <f t="shared" ref="V22:W22" si="162">V12/V11</f>
+        <f t="shared" ref="V22:W22" si="163">V12/V11</f>
         <v>-4.730713245997089E-2</v>
       </c>
       <c r="W22" s="10">
-        <f t="shared" si="162"/>
+        <f t="shared" si="163"/>
         <v>0.19693654266958424</v>
       </c>
       <c r="X22" s="10">
-        <f t="shared" ref="X22" si="163">X12/X11</f>
+        <f t="shared" ref="X22" si="164">X12/X11</f>
         <v>0.19333333333333333</v>
       </c>
       <c r="Y22" s="10">
-        <f t="shared" ref="Y22:AA22" si="164">Y12/Y11</f>
+        <f t="shared" ref="Y22:AA22" si="165">Y12/Y11</f>
         <v>0.16046039268788084</v>
       </c>
       <c r="Z22" s="10">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>0.1725521669341894</v>
       </c>
       <c r="AA22" s="10">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>0.12014563106796117</v>
       </c>
       <c r="AB22" s="10">
-        <f t="shared" ref="AB22" si="165">AB12/AB11</f>
+        <f t="shared" ref="AB22" si="166">AB12/AB11</f>
         <v>0.17898022892819979</v>
       </c>
       <c r="AC22" s="10">
-        <f t="shared" ref="AC22:AD22" si="166">AC12/AC11</f>
+        <f t="shared" ref="AC22:AD22" si="167">AC12/AC11</f>
         <v>0.16524216524216523</v>
       </c>
       <c r="AD22" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>0.13093858632676708</v>
       </c>
       <c r="AE22" s="10">
-        <f t="shared" ref="AE22:AH22" si="167">AE12/AE11</f>
+        <f t="shared" ref="AE22:AH22" si="168">AE12/AE11</f>
         <v>0.19586840091813312</v>
       </c>
       <c r="AF22" s="10">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>0.1786723163841808</v>
       </c>
       <c r="AG22" s="10">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>5.9241706161137442E-2</v>
       </c>
       <c r="AH22" s="10">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>0.33647798742138363</v>
       </c>
       <c r="AI22" s="10">
-        <f t="shared" ref="AI22:AL22" si="168">AI12/AI11</f>
+        <f t="shared" ref="AI22:AL22" si="169">AI12/AI11</f>
         <v>0.21149674620390455</v>
       </c>
       <c r="AJ22" s="10">
-        <f t="shared" si="168"/>
+        <f t="shared" si="169"/>
         <v>0.17</v>
       </c>
       <c r="AK22" s="10">
-        <f t="shared" si="168"/>
+        <f t="shared" si="169"/>
         <v>0.17</v>
       </c>
       <c r="AL22" s="10">
-        <f t="shared" si="168"/>
+        <f t="shared" si="169"/>
         <v>0.17</v>
       </c>
       <c r="AN22" s="10">
-        <f t="shared" ref="AN22" si="169">AN12/AN11</f>
+        <f t="shared" ref="AN22" si="170">AN12/AN11</f>
         <v>0.13221449038067951</v>
       </c>
       <c r="AO22" s="10">
-        <f t="shared" ref="AO22" si="170">AO12/AO11</f>
+        <f t="shared" ref="AO22" si="171">AO12/AO11</f>
         <v>0.55293573740175683</v>
       </c>
       <c r="AP22" s="10">
-        <f t="shared" ref="AP22:BB22" si="171">AP12/AP11</f>
+        <f t="shared" ref="AP22:BB22" si="172">AP12/AP11</f>
         <v>0.16079983336804832</v>
       </c>
       <c r="AQ22" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>0.12054035330793211</v>
       </c>
       <c r="AR22" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>0.14021918630836211</v>
       </c>
       <c r="AS22" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>9.0963764847391368E-2</v>
       </c>
       <c r="AT22" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>0.18238993710691823</v>
       </c>
       <c r="AU22" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>0.14925373134328357</v>
       </c>
       <c r="AV22" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>0.17142857142857143</v>
       </c>
       <c r="AW22" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>0.17900969552504029</v>
       </c>
       <c r="AX22" s="10">
-        <f t="shared" si="171"/>
-        <v>0.17</v>
-      </c>
-      <c r="AY22" s="10">
-        <f t="shared" si="171"/>
-        <v>0.17</v>
-      </c>
-      <c r="AZ22" s="10">
-        <f t="shared" si="171"/>
-        <v>0.17</v>
-      </c>
-      <c r="BA22" s="10">
-        <f t="shared" si="171"/>
-        <v>0.17</v>
-      </c>
-      <c r="BB22" s="10">
-        <f t="shared" si="171"/>
-        <v>0.16999999999999998</v>
-      </c>
-      <c r="BC22" s="10">
-        <f t="shared" ref="BC22:BF22" si="172">BC12/BC11</f>
-        <v>0.17</v>
-      </c>
-      <c r="BD22" s="10">
         <f t="shared" si="172"/>
         <v>0.17</v>
       </c>
-      <c r="BE22" s="10">
+      <c r="AY22" s="10">
         <f t="shared" si="172"/>
         <v>0.17</v>
       </c>
+      <c r="AZ22" s="10">
+        <f t="shared" si="172"/>
+        <v>0.17</v>
+      </c>
+      <c r="BA22" s="10">
+        <f t="shared" si="172"/>
+        <v>0.17</v>
+      </c>
+      <c r="BB22" s="10">
+        <f t="shared" si="172"/>
+        <v>0.16999999999999998</v>
+      </c>
+      <c r="BC22" s="10">
+        <f t="shared" ref="BC22:BF22" si="173">BC12/BC11</f>
+        <v>0.17</v>
+      </c>
+      <c r="BD22" s="10">
+        <f t="shared" si="173"/>
+        <v>0.17</v>
+      </c>
+      <c r="BE22" s="10">
+        <f t="shared" si="173"/>
+        <v>0.17</v>
+      </c>
       <c r="BF22" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>0.16999999999999998</v>
       </c>
       <c r="BH22" t="s">
@@ -5641,19 +5640,19 @@
         <v>44</v>
       </c>
       <c r="C23" s="10">
-        <f t="shared" ref="C23:F23" si="173">C13/C3</f>
+        <f t="shared" ref="C23:F23" si="174">C13/C3</f>
         <v>0.10474090407938258</v>
       </c>
       <c r="D23" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>8.9665653495440728E-2</v>
       </c>
       <c r="E23" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>-0.10240427426536064</v>
       </c>
       <c r="F23" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>0.11615078148942691</v>
       </c>
       <c r="G23" s="10">
@@ -5661,203 +5660,203 @@
         <v>0.10977080820265379</v>
       </c>
       <c r="H23" s="10">
-        <f t="shared" ref="H23:S23" si="174">H13/H3</f>
+        <f t="shared" ref="H23:S23" si="175">H13/H3</f>
         <v>9.0356304672498403E-2</v>
       </c>
       <c r="I23" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>0.11455623764436583</v>
       </c>
       <c r="J23" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>9.7113118617439126E-2</v>
       </c>
       <c r="K23" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>0.12823639774859288</v>
       </c>
       <c r="L23" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>0.10797985667247724</v>
       </c>
       <c r="M23" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>8.3828186856690426E-2</v>
       </c>
       <c r="N23" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>-0.12513860288293996</v>
       </c>
       <c r="O23" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>0.1432886539550689</v>
       </c>
       <c r="P23" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>0.11126923419016277</v>
       </c>
       <c r="Q23" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>0.13990537800521385</v>
       </c>
       <c r="R23" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>0.12224562540505508</v>
       </c>
       <c r="S23" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>0.15300457217504898</v>
       </c>
       <c r="T23" s="10">
-        <f t="shared" ref="T23:U23" si="175">T13/T3</f>
+        <f t="shared" ref="T23:U23" si="176">T13/T3</f>
         <v>0.11772475125473277</v>
       </c>
       <c r="U23" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>0.12841504921350383</v>
       </c>
       <c r="V23" s="10">
-        <f t="shared" ref="V23:W23" si="176">V13/V3</f>
+        <f t="shared" ref="V23:W23" si="177">V13/V3</f>
         <v>0.11762301781919242</v>
       </c>
       <c r="W23" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0.11570899345787027</v>
       </c>
       <c r="X23" s="10">
-        <f t="shared" ref="X23" si="177">X13/X3</f>
+        <f t="shared" ref="X23" si="178">X13/X3</f>
         <v>9.9962448366503948E-2</v>
       </c>
       <c r="Y23" s="10">
-        <f t="shared" ref="Y23:AA23" si="178">Y13/Y3</f>
+        <f t="shared" ref="Y23:AA23" si="179">Y13/Y3</f>
         <v>0.10008071025020178</v>
       </c>
       <c r="Z23" s="10">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>8.0389863547758289E-2</v>
       </c>
       <c r="AA23" s="10">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>0.11206430172347168</v>
       </c>
       <c r="AB23" s="10">
-        <f t="shared" ref="AB23" si="179">AB13/AB3</f>
+        <f t="shared" ref="AB23" si="180">AB13/AB3</f>
         <v>0.11786674634000598</v>
       </c>
       <c r="AC23" s="10">
-        <f t="shared" ref="AC23:AD23" si="180">AC13/AC3</f>
+        <f t="shared" ref="AC23:AD23" si="181">AC13/AC3</f>
         <v>9.4295599002333252E-2</v>
       </c>
       <c r="AD23" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>0.11899095668729176</v>
       </c>
       <c r="AE23" s="10">
-        <f t="shared" ref="AE23:AH23" si="181">AE13/AE3</f>
+        <f t="shared" ref="AE23:AH23" si="182">AE13/AE3</f>
         <v>9.0689446889291564E-2</v>
       </c>
       <c r="AF23" s="10">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>9.4139549943338188E-2</v>
       </c>
       <c r="AG23" s="10">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>7.045878072588517E-2</v>
       </c>
       <c r="AH23" s="10">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>1.9014147967919257E-2</v>
       </c>
       <c r="AI23" s="10">
-        <f t="shared" ref="AI23:AL23" si="182">AI13/AI3</f>
+        <f t="shared" ref="AI23:AL23" si="183">AI13/AI3</f>
         <v>6.2030716723549491E-2</v>
       </c>
       <c r="AJ23" s="10">
-        <f t="shared" si="182"/>
+        <f t="shared" si="183"/>
         <v>8.0206459446333173E-2</v>
       </c>
       <c r="AK23" s="10">
-        <f t="shared" si="182"/>
+        <f t="shared" si="183"/>
         <v>7.8065309829673288E-2</v>
       </c>
       <c r="AL23" s="10">
-        <f t="shared" si="182"/>
+        <f t="shared" si="183"/>
         <v>7.6091362795456113E-2</v>
       </c>
       <c r="AN23" s="10">
-        <f t="shared" ref="AN23" si="183">AN13/AN3</f>
+        <f t="shared" ref="AN23" si="184">AN13/AN3</f>
         <v>0.12343522561863174</v>
       </c>
       <c r="AO23" s="10">
-        <f t="shared" ref="AO23" si="184">AO13/AO3</f>
+        <f t="shared" ref="AO23" si="185">AO13/AO3</f>
         <v>5.313624749292524E-2</v>
       </c>
       <c r="AP23" s="10">
-        <f t="shared" ref="AP23:BB23" si="185">AP13/AP3</f>
+        <f t="shared" ref="AP23:BB23" si="186">AP13/AP3</f>
         <v>0.10299869621903521</v>
       </c>
       <c r="AQ23" s="10">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>6.7882255434056085E-2</v>
       </c>
       <c r="AR23" s="10">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>0.12858682473393507</v>
       </c>
       <c r="AS23" s="10">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>0.12943695140226932</v>
       </c>
       <c r="AT23" s="10">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>9.8990569537458259E-2</v>
       </c>
       <c r="AU23" s="10">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>0.11097698687745804</v>
       </c>
       <c r="AV23" s="10">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>6.9511326092120324E-2</v>
       </c>
       <c r="AW23" s="10">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>7.4160847344634767E-2</v>
       </c>
       <c r="AX23" s="10">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>0.10256900853186721</v>
       </c>
       <c r="AY23" s="10">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>0.11467931904581161</v>
       </c>
       <c r="AZ23" s="10">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>0.11467931904581163</v>
       </c>
       <c r="BA23" s="10">
-        <f t="shared" si="185"/>
-        <v>0.11467931904581152</v>
-      </c>
-      <c r="BB23" s="10">
-        <f t="shared" si="185"/>
-        <v>0.11467931904581151</v>
-      </c>
-      <c r="BC23" s="10">
-        <f t="shared" ref="BC23:BF23" si="186">BC13/BC3</f>
-        <v>0.11467931904581158</v>
-      </c>
-      <c r="BD23" s="10">
-        <f t="shared" si="186"/>
-        <v>0.11467931904581156</v>
-      </c>
-      <c r="BE23" s="10">
         <f t="shared" si="186"/>
         <v>0.11467931904581152</v>
       </c>
+      <c r="BB23" s="10">
+        <f t="shared" si="186"/>
+        <v>0.11467931904581151</v>
+      </c>
+      <c r="BC23" s="10">
+        <f t="shared" ref="BC23:BF23" si="187">BC13/BC3</f>
+        <v>0.11467931904581158</v>
+      </c>
+      <c r="BD23" s="10">
+        <f t="shared" si="187"/>
+        <v>0.11467931904581156</v>
+      </c>
+      <c r="BE23" s="10">
+        <f t="shared" si="187"/>
+        <v>0.11467931904581152</v>
+      </c>
       <c r="BF23" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>0.11467931904581152</v>
       </c>
       <c r="BH23" t="s">
@@ -5883,7 +5882,7 @@
       </c>
       <c r="BI25" s="6">
         <f>Main!D3</f>
-        <v>74.84</v>
+        <v>62.31</v>
       </c>
     </row>
     <row r="26" spans="2:61" x14ac:dyDescent="0.3">
@@ -5892,7 +5891,7 @@
       </c>
       <c r="BI26" s="11">
         <f>BI24/BI25-1</f>
-        <v>-0.30866786966606552</v>
+        <v>-0.16964698067418293</v>
       </c>
     </row>
     <row r="27" spans="2:61" x14ac:dyDescent="0.3">
